--- a/docs/plan-2027.xlsx
+++ b/docs/plan-2027.xlsx
@@ -649,6 +649,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4" ht="26" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -773,6 +774,7 @@
         </is>
       </c>
     </row>
+    <row r="12"/>
     <row r="13">
       <c r="A13" s="7" t="inlineStr">
         <is>
@@ -864,6 +866,7 @@
         </is>
       </c>
     </row>
+    <row r="21"/>
     <row r="22">
       <c r="A22" s="7" t="inlineStr">
         <is>
@@ -907,6 +910,7 @@
         </is>
       </c>
     </row>
+    <row r="26"/>
     <row r="27">
       <c r="A27" s="9" t="inlineStr">
         <is>
@@ -1071,7 +1075,7 @@
       <c r="L2" s="15" t="n"/>
       <c r="M2" s="15" t="n"/>
       <c r="N2" s="16">
-        <f>IF(N(L2)=0,"",M2/L2)</f>
+        <f>IFERROR(M2/L2,"")</f>
         <v/>
       </c>
       <c r="O2" s="12" t="inlineStr"/>
@@ -1132,7 +1136,7 @@
         <v>4</v>
       </c>
       <c r="N3" s="16">
-        <f>IF(N(L3)=0,"",M3/L3)</f>
+        <f>IFERROR(M3/L3,"")</f>
         <v/>
       </c>
       <c r="O3" s="12" t="inlineStr"/>
@@ -1197,7 +1201,7 @@
         <v>8.25</v>
       </c>
       <c r="N4" s="16">
-        <f>IF(N(L4)=0,"",M4/L4)</f>
+        <f>IFERROR(M4/L4,"")</f>
         <v/>
       </c>
       <c r="O4" s="12" t="inlineStr"/>
@@ -1258,7 +1262,7 @@
         <v>11</v>
       </c>
       <c r="N5" s="16">
-        <f>IF(N(L5)=0,"",M5/L5)</f>
+        <f>IFERROR(M5/L5,"")</f>
         <v/>
       </c>
       <c r="O5" s="12" t="inlineStr"/>
@@ -1323,7 +1327,7 @@
         <v>9.5</v>
       </c>
       <c r="N6" s="16">
-        <f>IF(N(L6)=0,"",M6/L6)</f>
+        <f>IFERROR(M6/L6,"")</f>
         <v/>
       </c>
       <c r="O6" s="12" t="inlineStr"/>
@@ -1380,7 +1384,7 @@
       <c r="L7" s="15" t="n"/>
       <c r="M7" s="15" t="n"/>
       <c r="N7" s="16">
-        <f>IF(N(L7)=0,"",M7/L7)</f>
+        <f>IFERROR(M7/L7,"")</f>
         <v/>
       </c>
       <c r="O7" s="12" t="inlineStr">
@@ -1449,7 +1453,7 @@
         <v>11</v>
       </c>
       <c r="N8" s="16">
-        <f>IF(N(L8)=0,"",M8/L8)</f>
+        <f>IFERROR(M8/L8,"")</f>
         <v/>
       </c>
       <c r="O8" s="12" t="inlineStr">
@@ -1506,7 +1510,7 @@
       <c r="L9" s="15" t="n"/>
       <c r="M9" s="15" t="n"/>
       <c r="N9" s="16">
-        <f>IF(N(L9)=0,"",M9/L9)</f>
+        <f>IFERROR(M9/L9,"")</f>
         <v/>
       </c>
       <c r="O9" s="12" t="inlineStr"/>
@@ -1567,7 +1571,7 @@
         <v>3.25</v>
       </c>
       <c r="N10" s="16">
-        <f>IF(N(L10)=0,"",M10/L10)</f>
+        <f>IFERROR(M10/L10,"")</f>
         <v/>
       </c>
       <c r="O10" s="12" t="inlineStr"/>
@@ -1632,7 +1636,7 @@
         <v>10.5</v>
       </c>
       <c r="N11" s="16">
-        <f>IF(N(L11)=0,"",M11/L11)</f>
+        <f>IFERROR(M11/L11,"")</f>
         <v/>
       </c>
       <c r="O11" s="12" t="inlineStr"/>
@@ -1693,7 +1697,7 @@
         <v>8</v>
       </c>
       <c r="N12" s="16">
-        <f>IF(N(L12)=0,"",M12/L12)</f>
+        <f>IFERROR(M12/L12,"")</f>
         <v/>
       </c>
       <c r="O12" s="12" t="inlineStr">
@@ -1752,7 +1756,7 @@
       <c r="L13" s="15" t="n"/>
       <c r="M13" s="15" t="n"/>
       <c r="N13" s="16">
-        <f>IF(N(L13)=0,"",M13/L13)</f>
+        <f>IFERROR(M13/L13,"")</f>
         <v/>
       </c>
       <c r="O13" s="12" t="inlineStr">
@@ -1817,7 +1821,7 @@
         <v>5.933333333333334</v>
       </c>
       <c r="N14" s="16">
-        <f>IF(N(L14)=0,"",M14/L14)</f>
+        <f>IFERROR(M14/L14,"")</f>
         <v/>
       </c>
       <c r="O14" s="12" t="inlineStr">
@@ -1882,7 +1886,7 @@
         <v>3.047619047619047</v>
       </c>
       <c r="N15" s="16">
-        <f>IF(N(L15)=0,"",M15/L15)</f>
+        <f>IFERROR(M15/L15,"")</f>
         <v/>
       </c>
       <c r="O15" s="12" t="inlineStr">
@@ -1947,7 +1951,7 @@
         <v>0.75</v>
       </c>
       <c r="N16" s="16">
-        <f>IF(N(L16)=0,"",M16/L16)</f>
+        <f>IFERROR(M16/L16,"")</f>
         <v/>
       </c>
       <c r="O16" s="12" t="inlineStr"/>
@@ -2004,7 +2008,7 @@
       <c r="L17" s="15" t="n"/>
       <c r="M17" s="15" t="n"/>
       <c r="N17" s="16">
-        <f>IF(N(L17)=0,"",M17/L17)</f>
+        <f>IFERROR(M17/L17,"")</f>
         <v/>
       </c>
       <c r="O17" s="12" t="inlineStr"/>
@@ -2065,7 +2069,7 @@
         <v>3.25</v>
       </c>
       <c r="N18" s="16">
-        <f>IF(N(L18)=0,"",M18/L18)</f>
+        <f>IFERROR(M18/L18,"")</f>
         <v/>
       </c>
       <c r="O18" s="12" t="inlineStr"/>
@@ -2126,7 +2130,7 @@
         <v>2.866666666666667</v>
       </c>
       <c r="N19" s="16">
-        <f>IF(N(L19)=0,"",M19/L19)</f>
+        <f>IFERROR(M19/L19,"")</f>
         <v/>
       </c>
       <c r="O19" s="12" t="inlineStr"/>
@@ -2187,7 +2191,7 @@
         <v>1.333333333333333</v>
       </c>
       <c r="N20" s="16">
-        <f>IF(N(L20)=0,"",M20/L20)</f>
+        <f>IFERROR(M20/L20,"")</f>
         <v/>
       </c>
       <c r="O20" s="12" t="inlineStr"/>
@@ -2248,7 +2252,7 @@
         <v>0.6666666666666666</v>
       </c>
       <c r="N21" s="16">
-        <f>IF(N(L21)=0,"",M21/L21)</f>
+        <f>IFERROR(M21/L21,"")</f>
         <v/>
       </c>
       <c r="O21" s="12" t="inlineStr"/>
@@ -2309,7 +2313,7 @@
         <v>2</v>
       </c>
       <c r="N22" s="16">
-        <f>IF(N(L22)=0,"",M22/L22)</f>
+        <f>IFERROR(M22/L22,"")</f>
         <v/>
       </c>
       <c r="O22" s="12" t="inlineStr">
@@ -2374,7 +2378,7 @@
         <v>1.75</v>
       </c>
       <c r="N23" s="16">
-        <f>IF(N(L23)=0,"",M23/L23)</f>
+        <f>IFERROR(M23/L23,"")</f>
         <v/>
       </c>
       <c r="O23" s="12" t="inlineStr">
@@ -2439,7 +2443,7 @@
         <v>1.25</v>
       </c>
       <c r="N24" s="16">
-        <f>IF(N(L24)=0,"",M24/L24)</f>
+        <f>IFERROR(M24/L24,"")</f>
         <v/>
       </c>
       <c r="O24" s="12" t="inlineStr"/>
@@ -2500,7 +2504,7 @@
         <v>1</v>
       </c>
       <c r="N25" s="16">
-        <f>IF(N(L25)=0,"",M25/L25)</f>
+        <f>IFERROR(M25/L25,"")</f>
         <v/>
       </c>
       <c r="O25" s="12" t="inlineStr"/>
@@ -2561,7 +2565,7 @@
         <v>0.8571428571428571</v>
       </c>
       <c r="N26" s="16">
-        <f>IF(N(L26)=0,"",M26/L26)</f>
+        <f>IFERROR(M26/L26,"")</f>
         <v/>
       </c>
       <c r="O26" s="12" t="inlineStr"/>
@@ -2622,7 +2626,7 @@
         <v>0</v>
       </c>
       <c r="N27" s="16">
-        <f>IF(N(L27)=0,"",M27/L27)</f>
+        <f>IFERROR(M27/L27,"")</f>
         <v/>
       </c>
       <c r="O27" s="12" t="inlineStr"/>
@@ -2679,7 +2683,7 @@
       <c r="L28" s="15" t="n"/>
       <c r="M28" s="15" t="n"/>
       <c r="N28" s="16">
-        <f>IF(N(L28)=0,"",M28/L28)</f>
+        <f>IFERROR(M28/L28,"")</f>
         <v/>
       </c>
       <c r="O28" s="12" t="inlineStr">
@@ -2736,7 +2740,7 @@
       <c r="L29" s="15" t="n"/>
       <c r="M29" s="15" t="n"/>
       <c r="N29" s="16">
-        <f>IF(N(L29)=0,"",M29/L29)</f>
+        <f>IFERROR(M29/L29,"")</f>
         <v/>
       </c>
       <c r="O29" s="12" t="inlineStr"/>
@@ -2797,7 +2801,7 @@
         <v>8.4</v>
       </c>
       <c r="N30" s="16">
-        <f>IF(N(L30)=0,"",M30/L30)</f>
+        <f>IFERROR(M30/L30,"")</f>
         <v/>
       </c>
       <c r="O30" s="12" t="inlineStr"/>
@@ -2858,7 +2862,7 @@
       <c r="L31" s="15" t="n"/>
       <c r="M31" s="15" t="n"/>
       <c r="N31" s="16">
-        <f>IF(N(L31)=0,"",M31/L31)</f>
+        <f>IFERROR(M31/L31,"")</f>
         <v/>
       </c>
       <c r="O31" s="12" t="inlineStr"/>
@@ -2923,7 +2927,7 @@
         <v>8.142857142857142</v>
       </c>
       <c r="N32" s="16">
-        <f>IF(N(L32)=0,"",M32/L32)</f>
+        <f>IFERROR(M32/L32,"")</f>
         <v/>
       </c>
       <c r="O32" s="12" t="inlineStr"/>
@@ -2984,7 +2988,7 @@
         <v>2.714285714285714</v>
       </c>
       <c r="N33" s="16">
-        <f>IF(N(L33)=0,"",M33/L33)</f>
+        <f>IFERROR(M33/L33,"")</f>
         <v/>
       </c>
       <c r="O33" s="12" t="inlineStr">
@@ -3049,7 +3053,7 @@
         <v>2.333333333333333</v>
       </c>
       <c r="N34" s="16">
-        <f>IF(N(L34)=0,"",M34/L34)</f>
+        <f>IFERROR(M34/L34,"")</f>
         <v/>
       </c>
       <c r="O34" s="12" t="inlineStr"/>
@@ -3110,7 +3114,7 @@
         <v>2.258064516129032</v>
       </c>
       <c r="N35" s="16">
-        <f>IF(N(L35)=0,"",M35/L35)</f>
+        <f>IFERROR(M35/L35,"")</f>
         <v/>
       </c>
       <c r="O35" s="12" t="inlineStr"/>
@@ -3171,7 +3175,7 @@
         <v>2</v>
       </c>
       <c r="N36" s="16">
-        <f>IF(N(L36)=0,"",M36/L36)</f>
+        <f>IFERROR(M36/L36,"")</f>
         <v/>
       </c>
       <c r="O36" s="12" t="inlineStr"/>
@@ -3232,7 +3236,7 @@
         <v>1.75</v>
       </c>
       <c r="N37" s="16">
-        <f>IF(N(L37)=0,"",M37/L37)</f>
+        <f>IFERROR(M37/L37,"")</f>
         <v/>
       </c>
       <c r="O37" s="12" t="inlineStr">
@@ -3297,7 +3301,7 @@
         <v>0.8333333333333334</v>
       </c>
       <c r="N38" s="16">
-        <f>IF(N(L38)=0,"",M38/L38)</f>
+        <f>IFERROR(M38/L38,"")</f>
         <v/>
       </c>
       <c r="O38" s="12" t="inlineStr"/>
@@ -3358,7 +3362,7 @@
         <v>5.461538461538462</v>
       </c>
       <c r="N39" s="16">
-        <f>IF(N(L39)=0,"",M39/L39)</f>
+        <f>IFERROR(M39/L39,"")</f>
         <v/>
       </c>
       <c r="O39" s="12" t="inlineStr"/>
@@ -3419,7 +3423,7 @@
         <v>7.4</v>
       </c>
       <c r="N40" s="16">
-        <f>IF(N(L40)=0,"",M40/L40)</f>
+        <f>IFERROR(M40/L40,"")</f>
         <v/>
       </c>
       <c r="O40" s="12" t="inlineStr"/>
@@ -3484,7 +3488,7 @@
         <v>5</v>
       </c>
       <c r="N41" s="16">
-        <f>IF(N(L41)=0,"",M41/L41)</f>
+        <f>IFERROR(M41/L41,"")</f>
         <v/>
       </c>
       <c r="O41" s="12" t="inlineStr"/>
@@ -3545,7 +3549,7 @@
         <v>13.09090909090909</v>
       </c>
       <c r="N42" s="16">
-        <f>IF(N(L42)=0,"",M42/L42)</f>
+        <f>IFERROR(M42/L42,"")</f>
         <v/>
       </c>
       <c r="O42" s="12" t="inlineStr"/>
@@ -3610,7 +3614,7 @@
         <v>7.5</v>
       </c>
       <c r="N43" s="16">
-        <f>IF(N(L43)=0,"",M43/L43)</f>
+        <f>IFERROR(M43/L43,"")</f>
         <v/>
       </c>
       <c r="O43" s="12" t="inlineStr"/>
@@ -3671,7 +3675,7 @@
         <v>0</v>
       </c>
       <c r="N44" s="16">
-        <f>IF(N(L44)=0,"",M44/L44)</f>
+        <f>IFERROR(M44/L44,"")</f>
         <v/>
       </c>
       <c r="O44" s="12" t="inlineStr"/>
@@ -3732,7 +3736,7 @@
         <v>3.16</v>
       </c>
       <c r="N45" s="16">
-        <f>IF(N(L45)=0,"",M45/L45)</f>
+        <f>IFERROR(M45/L45,"")</f>
         <v/>
       </c>
       <c r="O45" s="12" t="inlineStr"/>
@@ -3793,7 +3797,7 @@
         <v>2.4</v>
       </c>
       <c r="N46" s="16">
-        <f>IF(N(L46)=0,"",M46/L46)</f>
+        <f>IFERROR(M46/L46,"")</f>
         <v/>
       </c>
       <c r="O46" s="12" t="inlineStr"/>
@@ -3854,7 +3858,7 @@
         <v>1.958333333333333</v>
       </c>
       <c r="N47" s="16">
-        <f>IF(N(L47)=0,"",M47/L47)</f>
+        <f>IFERROR(M47/L47,"")</f>
         <v/>
       </c>
       <c r="O47" s="12" t="inlineStr"/>
@@ -3915,7 +3919,7 @@
         <v>1.333333333333333</v>
       </c>
       <c r="N48" s="16">
-        <f>IF(N(L48)=0,"",M48/L48)</f>
+        <f>IFERROR(M48/L48,"")</f>
         <v/>
       </c>
       <c r="O48" s="12" t="inlineStr"/>
@@ -3976,7 +3980,7 @@
         <v>1</v>
       </c>
       <c r="N49" s="16">
-        <f>IF(N(L49)=0,"",M49/L49)</f>
+        <f>IFERROR(M49/L49,"")</f>
         <v/>
       </c>
       <c r="O49" s="12" t="inlineStr"/>
@@ -4033,7 +4037,7 @@
       <c r="L50" s="15" t="n"/>
       <c r="M50" s="15" t="n"/>
       <c r="N50" s="16">
-        <f>IF(N(L50)=0,"",M50/L50)</f>
+        <f>IFERROR(M50/L50,"")</f>
         <v/>
       </c>
       <c r="O50" s="12" t="inlineStr"/>
@@ -4094,7 +4098,7 @@
         <v>1.96551724137931</v>
       </c>
       <c r="N51" s="16">
-        <f>IF(N(L51)=0,"",M51/L51)</f>
+        <f>IFERROR(M51/L51,"")</f>
         <v/>
       </c>
       <c r="O51" s="12" t="inlineStr"/>
@@ -4155,7 +4159,7 @@
         <v>1.925</v>
       </c>
       <c r="N52" s="16">
-        <f>IF(N(L52)=0,"",M52/L52)</f>
+        <f>IFERROR(M52/L52,"")</f>
         <v/>
       </c>
       <c r="O52" s="12" t="inlineStr"/>
@@ -4216,7 +4220,7 @@
         <v>1.166666666666667</v>
       </c>
       <c r="N53" s="16">
-        <f>IF(N(L53)=0,"",M53/L53)</f>
+        <f>IFERROR(M53/L53,"")</f>
         <v/>
       </c>
       <c r="O53" s="12" t="inlineStr"/>
@@ -4277,7 +4281,7 @@
         <v>1.111111111111111</v>
       </c>
       <c r="N54" s="16">
-        <f>IF(N(L54)=0,"",M54/L54)</f>
+        <f>IFERROR(M54/L54,"")</f>
         <v/>
       </c>
       <c r="O54" s="12" t="inlineStr"/>
@@ -4338,7 +4342,7 @@
         <v>2.111111111111111</v>
       </c>
       <c r="N55" s="16">
-        <f>IF(N(L55)=0,"",M55/L55)</f>
+        <f>IFERROR(M55/L55,"")</f>
         <v/>
       </c>
       <c r="O55" s="12" t="inlineStr"/>
@@ -4399,7 +4403,7 @@
         <v>2.066666666666667</v>
       </c>
       <c r="N56" s="16">
-        <f>IF(N(L56)=0,"",M56/L56)</f>
+        <f>IFERROR(M56/L56,"")</f>
         <v/>
       </c>
       <c r="O56" s="12" t="inlineStr"/>
@@ -4460,7 +4464,7 @@
         <v>0</v>
       </c>
       <c r="N57" s="16">
-        <f>IF(N(L57)=0,"",M57/L57)</f>
+        <f>IFERROR(M57/L57,"")</f>
         <v/>
       </c>
       <c r="O57" s="12" t="inlineStr"/>
@@ -4521,7 +4525,7 @@
         <v>5</v>
       </c>
       <c r="N58" s="16">
-        <f>IF(N(L58)=0,"",M58/L58)</f>
+        <f>IFERROR(M58/L58,"")</f>
         <v/>
       </c>
       <c r="O58" s="12" t="inlineStr"/>
@@ -4582,7 +4586,7 @@
         <v>2.727272727272727</v>
       </c>
       <c r="N59" s="16">
-        <f>IF(N(L59)=0,"",M59/L59)</f>
+        <f>IFERROR(M59/L59,"")</f>
         <v/>
       </c>
       <c r="O59" s="12" t="inlineStr"/>
@@ -4643,7 +4647,7 @@
         <v>0</v>
       </c>
       <c r="N60" s="16">
-        <f>IF(N(L60)=0,"",M60/L60)</f>
+        <f>IFERROR(M60/L60,"")</f>
         <v/>
       </c>
       <c r="O60" s="12" t="inlineStr"/>
@@ -4704,7 +4708,7 @@
         <v>7</v>
       </c>
       <c r="N61" s="16">
-        <f>IF(N(L61)=0,"",M61/L61)</f>
+        <f>IFERROR(M61/L61,"")</f>
         <v/>
       </c>
       <c r="O61" s="12" t="inlineStr"/>
@@ -4769,7 +4773,7 @@
         <v>5</v>
       </c>
       <c r="N62" s="16">
-        <f>IF(N(L62)=0,"",M62/L62)</f>
+        <f>IFERROR(M62/L62,"")</f>
         <v/>
       </c>
       <c r="O62" s="12" t="inlineStr"/>
@@ -4830,7 +4834,7 @@
         <v>1.8125</v>
       </c>
       <c r="N63" s="16">
-        <f>IF(N(L63)=0,"",M63/L63)</f>
+        <f>IFERROR(M63/L63,"")</f>
         <v/>
       </c>
       <c r="O63" s="12" t="inlineStr"/>
@@ -4887,7 +4891,7 @@
       <c r="L64" s="15" t="n"/>
       <c r="M64" s="15" t="n"/>
       <c r="N64" s="16">
-        <f>IF(N(L64)=0,"",M64/L64)</f>
+        <f>IFERROR(M64/L64,"")</f>
         <v/>
       </c>
       <c r="O64" s="12" t="inlineStr"/>
@@ -4897,6 +4901,7 @@
         </is>
       </c>
     </row>
+    <row r="65"/>
     <row r="66">
       <c r="A66" s="9" t="inlineStr">
         <is>
@@ -5288,6 +5293,7 @@
         </is>
       </c>
     </row>
+    <row r="8"/>
     <row r="9">
       <c r="A9" s="9" t="inlineStr">
         <is>
@@ -5437,7 +5443,7 @@
         <v>3.333333333333333</v>
       </c>
       <c r="K2" s="20">
-        <f>IF(N(I2)=0,"",J2/I2)</f>
+        <f>IFERROR(J2/I2,"")</f>
         <v/>
       </c>
       <c r="L2" s="12" t="n">
@@ -5487,7 +5493,7 @@
         <v>3.75</v>
       </c>
       <c r="K3" s="20">
-        <f>IF(N(I3)=0,"",J3/I3)</f>
+        <f>IFERROR(J3/I3,"")</f>
         <v/>
       </c>
       <c r="L3" s="12" t="n">
@@ -5537,7 +5543,7 @@
         <v>4.285714285714286</v>
       </c>
       <c r="K4" s="20">
-        <f>IF(N(I4)=0,"",J4/I4)</f>
+        <f>IFERROR(J4/I4,"")</f>
         <v/>
       </c>
       <c r="L4" s="12" t="n">
@@ -5587,7 +5593,7 @@
         <v>5</v>
       </c>
       <c r="K5" s="20">
-        <f>IF(N(I5)=0,"",J5/I5)</f>
+        <f>IFERROR(J5/I5,"")</f>
         <v/>
       </c>
       <c r="L5" s="12" t="n">
@@ -5637,7 +5643,7 @@
         <v>3.833333333333333</v>
       </c>
       <c r="K6" s="20">
-        <f>IF(N(I6)=0,"",J6/I6)</f>
+        <f>IFERROR(J6/I6,"")</f>
         <v/>
       </c>
       <c r="L6" s="12" t="n">
@@ -5687,7 +5693,7 @@
         <v>6.6</v>
       </c>
       <c r="K7" s="20">
-        <f>IF(N(I7)=0,"",J7/I7)</f>
+        <f>IFERROR(J7/I7,"")</f>
         <v/>
       </c>
       <c r="L7" s="12" t="n">
@@ -5737,7 +5743,7 @@
         <v>3.25</v>
       </c>
       <c r="K8" s="20">
-        <f>IF(N(I8)=0,"",J8/I8)</f>
+        <f>IFERROR(J8/I8,"")</f>
         <v/>
       </c>
       <c r="L8" s="12" t="n">
@@ -5787,7 +5793,7 @@
         <v>6</v>
       </c>
       <c r="K9" s="20">
-        <f>IF(N(I9)=0,"",J9/I9)</f>
+        <f>IFERROR(J9/I9,"")</f>
         <v/>
       </c>
       <c r="L9" s="12" t="n">
@@ -5837,7 +5843,7 @@
         <v>5</v>
       </c>
       <c r="K10" s="20">
-        <f>IF(N(I10)=0,"",J10/I10)</f>
+        <f>IFERROR(J10/I10,"")</f>
         <v/>
       </c>
       <c r="L10" s="12" t="n">
@@ -5883,7 +5889,7 @@
       <c r="I11" s="18" t="n"/>
       <c r="J11" s="18" t="n"/>
       <c r="K11" s="20">
-        <f>IF(N(I11)=0,"",J11/I11)</f>
+        <f>IFERROR(J11/I11,"")</f>
         <v/>
       </c>
       <c r="L11" s="12" t="n">
@@ -5933,7 +5939,7 @@
         <v>9</v>
       </c>
       <c r="K12" s="20">
-        <f>IF(N(I12)=0,"",J12/I12)</f>
+        <f>IFERROR(J12/I12,"")</f>
         <v/>
       </c>
       <c r="L12" s="12" t="n">
@@ -5983,7 +5989,7 @@
         <v>2.25</v>
       </c>
       <c r="K13" s="20">
-        <f>IF(N(I13)=0,"",J13/I13)</f>
+        <f>IFERROR(J13/I13,"")</f>
         <v/>
       </c>
       <c r="L13" s="12" t="n">
@@ -6033,7 +6039,7 @@
         <v>5</v>
       </c>
       <c r="K14" s="20">
-        <f>IF(N(I14)=0,"",J14/I14)</f>
+        <f>IFERROR(J14/I14,"")</f>
         <v/>
       </c>
       <c r="L14" s="12" t="n">
@@ -6083,7 +6089,7 @@
         <v>0</v>
       </c>
       <c r="K15" s="20">
-        <f>IF(N(I15)=0,"",J15/I15)</f>
+        <f>IFERROR(J15/I15,"")</f>
         <v/>
       </c>
       <c r="L15" s="12" t="n">
@@ -6133,7 +6139,7 @@
         <v>6</v>
       </c>
       <c r="K16" s="20">
-        <f>IF(N(I16)=0,"",J16/I16)</f>
+        <f>IFERROR(J16/I16,"")</f>
         <v/>
       </c>
       <c r="L16" s="12" t="n">
@@ -6179,7 +6185,7 @@
       <c r="I17" s="18" t="n"/>
       <c r="J17" s="18" t="n"/>
       <c r="K17" s="20">
-        <f>IF(N(I17)=0,"",J17/I17)</f>
+        <f>IFERROR(J17/I17,"")</f>
         <v/>
       </c>
       <c r="L17" s="12" t="n">
@@ -6225,7 +6231,7 @@
       <c r="I18" s="18" t="n"/>
       <c r="J18" s="18" t="n"/>
       <c r="K18" s="20">
-        <f>IF(N(I18)=0,"",J18/I18)</f>
+        <f>IFERROR(J18/I18,"")</f>
         <v/>
       </c>
       <c r="L18" s="12" t="n">
@@ -6271,7 +6277,7 @@
       <c r="I19" s="18" t="n"/>
       <c r="J19" s="18" t="n"/>
       <c r="K19" s="20">
-        <f>IF(N(I19)=0,"",J19/I19)</f>
+        <f>IFERROR(J19/I19,"")</f>
         <v/>
       </c>
       <c r="L19" s="12" t="n">
@@ -6283,6 +6289,7 @@
         </is>
       </c>
     </row>
+    <row r="20"/>
     <row r="21">
       <c r="A21" s="9" t="inlineStr">
         <is>
@@ -6526,6 +6533,7 @@
         <v/>
       </c>
     </row>
+    <row r="8"/>
     <row r="9">
       <c r="A9" s="9" t="inlineStr">
         <is>

--- a/docs/plan-2027.xlsx
+++ b/docs/plan-2027.xlsx
@@ -255,8 +255,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Calendar2027" displayName="Calendar2027" ref="A1:P64" headerRowCount="1">
-  <autoFilter ref="A1:P64"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="SeasonCalendar" displayName="SeasonCalendar" ref="A1:P80" headerRowCount="1">
+  <autoFilter ref="A1:P80"/>
   <tableColumns count="16">
     <tableColumn id="1" name="Date"/>
     <tableColumn id="2" name="Date is"/>
@@ -280,8 +280,8 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="WeekendPairs" displayName="WeekendPairs" ref="A1:L7" headerRowCount="1">
-  <autoFilter ref="A1:L7"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="WeekendPairs" displayName="WeekendPairs" ref="A1:L8" headerRowCount="1">
+  <autoFilter ref="A1:L8"/>
   <tableColumns count="12">
     <tableColumn id="1" name="Saturday"/>
     <tableColumn id="2" name="Saturday event"/>
@@ -638,14 +638,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Haisley 2027 · competition options</t>
+          <t>Haisley · competition options, November 2026 to December 2027</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Built 13 October 2026 from the Volleyball Life crawl and CBVA’s tournament database.</t>
+          <t>Built 17 October 2026 from the Volleyball Life crawl and CBVA’s tournament database.</t>
         </is>
       </c>
     </row>
@@ -721,7 +721,7 @@
         </is>
       </c>
       <c r="B8" s="6" t="n">
-        <v>63</v>
+        <v>79</v>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
@@ -736,7 +736,7 @@
         </is>
       </c>
       <c r="B9" s="6" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
@@ -929,7 +929,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P68"/>
+  <dimension ref="A1:P84"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -1034,7 +1034,7 @@
     </row>
     <row r="2">
       <c r="A2" s="11" t="n">
-        <v>46396</v>
+        <v>46327</v>
       </c>
       <c r="B2" s="12" t="inlineStr">
         <is>
@@ -1046,17 +1046,17 @@
       </c>
       <c r="D2" s="12" t="inlineStr">
         <is>
-          <t>p1440 1X Ranking Event</t>
+          <t>America’s Challenge (p1440)</t>
         </is>
       </c>
       <c r="E2" s="12" t="inlineStr">
         <is>
-          <t>Arizona Athletic Grounds, Phoenix</t>
+          <t>Hermosa Beach Pier</t>
         </is>
       </c>
       <c r="F2" s="12" t="inlineStr">
         <is>
-          <t>AZ</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="G2" s="12" t="inlineStr">
@@ -1081,13 +1081,13 @@
       <c r="O2" s="12" t="inlineStr"/>
       <c r="P2" s="17" t="inlineStr">
         <is>
-          <t>https://volleyballlife.com/tournament/41165</t>
+          <t>https://volleyballlife.com/tournament/35287</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="11" t="n">
-        <v>46397</v>
+        <v>46333</v>
       </c>
       <c r="B3" s="12" t="inlineStr">
         <is>
@@ -1095,16 +1095,16 @@
         </is>
       </c>
       <c r="C3" s="13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D3" s="12" t="inlineStr">
         <is>
-          <t>IBVL Winter Classic (Girls p1440)</t>
+          <t>AVP Juniors West Coast Championships</t>
         </is>
       </c>
       <c r="E3" s="12" t="inlineStr">
         <is>
-          <t>Hermosa Beach Pier</t>
+          <t>Manhattan Beach</t>
         </is>
       </c>
       <c r="F3" s="12" t="inlineStr">
@@ -1119,21 +1119,21 @@
       </c>
       <c r="H3" s="12" t="inlineStr">
         <is>
-          <t>Junior circuit</t>
+          <t>National junior</t>
         </is>
       </c>
       <c r="I3" s="12" t="inlineStr"/>
       <c r="J3" s="14" t="n">
-        <v>9.076499999999999</v>
+        <v>9.5015</v>
       </c>
       <c r="K3" s="13" t="n">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="L3" s="15" t="n">
-        <v>7.75</v>
+        <v>14.66666666666667</v>
       </c>
       <c r="M3" s="15" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="N3" s="16">
         <f>IFERROR(M3/L3,"")</f>
@@ -1142,13 +1142,13 @@
       <c r="O3" s="12" t="inlineStr"/>
       <c r="P3" s="17" t="inlineStr">
         <is>
-          <t>https://volleyballlife.com/tournament/41069</t>
+          <t>https://volleyballlife.com/tournament/34245</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="11" t="n">
-        <v>46403</v>
+        <v>46333</v>
       </c>
       <c r="B4" s="12" t="inlineStr">
         <is>
@@ -1160,27 +1160,27 @@
       </c>
       <c r="D4" s="12" t="inlineStr">
         <is>
-          <t>Futures Tour 2X: Arizona</t>
+          <t>AVP Juniors West Coast Championships</t>
         </is>
       </c>
       <c r="E4" s="12" t="inlineStr">
         <is>
-          <t>Arizona Athletic Grounds, Phoenix</t>
+          <t>Manhattan Beach</t>
         </is>
       </c>
       <c r="F4" s="12" t="inlineStr">
         <is>
-          <t>AZ</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="G4" s="12" t="inlineStr">
         <is>
-          <t>18U</t>
+          <t>17U</t>
         </is>
       </c>
       <c r="H4" s="12" t="inlineStr">
         <is>
-          <t>Junior circuit</t>
+          <t>National junior</t>
         </is>
       </c>
       <c r="I4" s="12" t="inlineStr">
@@ -1189,16 +1189,16 @@
         </is>
       </c>
       <c r="J4" s="14" t="n">
-        <v>8.286</v>
+        <v>7.714</v>
       </c>
       <c r="K4" s="13" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="L4" s="15" t="n">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="M4" s="15" t="n">
-        <v>8.25</v>
+        <v>5</v>
       </c>
       <c r="N4" s="16">
         <f>IFERROR(M4/L4,"")</f>
@@ -1207,13 +1207,13 @@
       <c r="O4" s="12" t="inlineStr"/>
       <c r="P4" s="17" t="inlineStr">
         <is>
-          <t>https://volleyballlife.com/tournament/41707</t>
+          <t>https://volleyballlife.com/tournament/34245</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="11" t="n">
-        <v>46410</v>
+        <v>46333</v>
       </c>
       <c r="B5" s="12" t="inlineStr">
         <is>
@@ -1221,16 +1221,16 @@
         </is>
       </c>
       <c r="C5" s="13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D5" s="12" t="inlineStr">
         <is>
-          <t>IBVL Winter Nationals (Girls)</t>
+          <t>CBVA women’s open</t>
         </is>
       </c>
       <c r="E5" s="12" t="inlineStr">
         <is>
-          <t>Hermosa Beach Pier</t>
+          <t>Belmont Shore, Long Beach</t>
         </is>
       </c>
       <c r="F5" s="12" t="inlineStr">
@@ -1240,26 +1240,26 @@
       </c>
       <c r="G5" s="12" t="inlineStr">
         <is>
-          <t>18U</t>
+          <t>Open</t>
         </is>
       </c>
       <c r="H5" s="12" t="inlineStr">
         <is>
-          <t>Junior circuit</t>
+          <t>Women's open</t>
         </is>
       </c>
       <c r="I5" s="12" t="inlineStr"/>
       <c r="J5" s="14" t="n">
-        <v>9.484999999999999</v>
+        <v>8.711</v>
       </c>
       <c r="K5" s="13" t="n">
+        <v>5</v>
+      </c>
+      <c r="L5" s="15" t="n">
         <v>4</v>
       </c>
-      <c r="L5" s="15" t="n">
-        <v>16</v>
-      </c>
       <c r="M5" s="15" t="n">
-        <v>11</v>
+        <v>1.666666666666667</v>
       </c>
       <c r="N5" s="16">
         <f>IFERROR(M5/L5,"")</f>
@@ -1268,35 +1268,35 @@
       <c r="O5" s="12" t="inlineStr"/>
       <c r="P5" s="17" t="inlineStr">
         <is>
-          <t>https://volleyballlife.com/tournament/41070</t>
+          <t>https://cbva.com/venues/3</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="11" t="n">
-        <v>46416</v>
+        <v>46340</v>
       </c>
       <c r="B6" s="12" t="inlineStr">
         <is>
-          <t>estimated</t>
+          <t>posted</t>
         </is>
       </c>
       <c r="C6" s="13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D6" s="12" t="inlineStr">
         <is>
-          <t>USAV U18 Beach National Team Trials</t>
+          <t>p1440 1X Ranking Event</t>
         </is>
       </c>
       <c r="E6" s="12" t="inlineStr">
         <is>
-          <t>Manhattan Beach Pier</t>
+          <t>Arizona Athletic Grounds, Mesa</t>
         </is>
       </c>
       <c r="F6" s="12" t="inlineStr">
         <is>
-          <t>CA</t>
+          <t>AZ</t>
         </is>
       </c>
       <c r="G6" s="12" t="inlineStr">
@@ -1306,26 +1306,14 @@
       </c>
       <c r="H6" s="12" t="inlineStr">
         <is>
-          <t>Selection</t>
-        </is>
-      </c>
-      <c r="I6" s="12" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="J6" s="14" t="n">
-        <v>9.4015</v>
-      </c>
-      <c r="K6" s="13" t="n">
-        <v>4</v>
-      </c>
-      <c r="L6" s="15" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="M6" s="15" t="n">
-        <v>9.5</v>
-      </c>
+          <t>Junior circuit</t>
+        </is>
+      </c>
+      <c r="I6" s="12" t="inlineStr"/>
+      <c r="J6" s="14" t="n"/>
+      <c r="K6" s="13" t="n"/>
+      <c r="L6" s="15" t="n"/>
+      <c r="M6" s="15" t="n"/>
       <c r="N6" s="16">
         <f>IFERROR(M6/L6,"")</f>
         <v/>
@@ -1333,13 +1321,13 @@
       <c r="O6" s="12" t="inlineStr"/>
       <c r="P6" s="17" t="inlineStr">
         <is>
-          <t>https://volleyballlife.com/tournament/34180</t>
+          <t>https://volleyballlife.com/tournament/41163</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="11" t="n">
-        <v>46424</v>
+        <v>46340</v>
       </c>
       <c r="B7" s="12" t="inlineStr">
         <is>
@@ -1351,12 +1339,12 @@
       </c>
       <c r="D7" s="12" t="inlineStr">
         <is>
-          <t>Kauai Bikini Open</t>
+          <t>The National Classic (p1440)</t>
         </is>
       </c>
       <c r="E7" s="12" t="inlineStr">
         <is>
-          <t>North Beach, Santa Monica</t>
+          <t>Hermosa Beach Pier</t>
         </is>
       </c>
       <c r="F7" s="12" t="inlineStr">
@@ -1376,31 +1364,31 @@
       </c>
       <c r="I7" s="12" t="inlineStr"/>
       <c r="J7" s="14" t="n">
-        <v>7.224</v>
+        <v>8.597</v>
       </c>
       <c r="K7" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="L7" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="M7" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="L7" s="15" t="n"/>
-      <c r="M7" s="15" t="n"/>
       <c r="N7" s="16">
         <f>IFERROR(M7/L7,"")</f>
         <v/>
       </c>
-      <c r="O7" s="12" t="inlineStr">
-        <is>
-          <t>6 Feb + 7 Feb</t>
-        </is>
-      </c>
+      <c r="O7" s="12" t="inlineStr"/>
       <c r="P7" s="17" t="inlineStr">
         <is>
-          <t>https://volleyballlife.com/tournament/41121</t>
+          <t>https://volleyballlife.com/tournament/35286</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="11" t="n">
-        <v>46425</v>
+        <v>46340</v>
       </c>
       <c r="B8" s="12" t="inlineStr">
         <is>
@@ -1412,12 +1400,12 @@
       </c>
       <c r="D8" s="12" t="inlineStr">
         <is>
-          <t>IBVL Winter Nationals (School Event) — ISF trial</t>
+          <t>CBVA women’s open</t>
         </is>
       </c>
       <c r="E8" s="12" t="inlineStr">
         <is>
-          <t>Hermosa Beach Pier</t>
+          <t>Newland, Huntington Beach</t>
         </is>
       </c>
       <c r="F8" s="12" t="inlineStr">
@@ -1427,49 +1415,41 @@
       </c>
       <c r="G8" s="12" t="inlineStr">
         <is>
-          <t>18U</t>
+          <t>Open</t>
         </is>
       </c>
       <c r="H8" s="12" t="inlineStr">
         <is>
-          <t>Selection</t>
-        </is>
-      </c>
-      <c r="I8" s="12" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+          <t>Women's open</t>
+        </is>
+      </c>
+      <c r="I8" s="12" t="inlineStr"/>
       <c r="J8" s="14" t="n">
-        <v>9.484999999999999</v>
+        <v>8.769</v>
       </c>
       <c r="K8" s="13" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="L8" s="15" t="n">
-        <v>16</v>
+        <v>4.0625</v>
       </c>
       <c r="M8" s="15" t="n">
-        <v>11</v>
+        <v>1.8125</v>
       </c>
       <c r="N8" s="16">
         <f>IFERROR(M8/L8,"")</f>
         <v/>
       </c>
-      <c r="O8" s="12" t="inlineStr">
-        <is>
-          <t>6 Feb + 7 Feb</t>
-        </is>
-      </c>
+      <c r="O8" s="12" t="inlineStr"/>
       <c r="P8" s="17" t="inlineStr">
         <is>
-          <t>https://volleyballlife.com/tournament/41071</t>
+          <t>https://cbva.com/venues/4</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="11" t="n">
-        <v>46431</v>
+        <v>46347</v>
       </c>
       <c r="B9" s="12" t="inlineStr">
         <is>
@@ -1477,21 +1457,21 @@
         </is>
       </c>
       <c r="C9" s="13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D9" s="12" t="inlineStr">
         <is>
-          <t>p1440 1X Ranking Event</t>
+          <t>Futures Tour 3X: Fall Championships</t>
         </is>
       </c>
       <c r="E9" s="12" t="inlineStr">
         <is>
-          <t>Arizona Athletic Grounds, Phoenix</t>
+          <t>Manhattan Beach</t>
         </is>
       </c>
       <c r="F9" s="12" t="inlineStr">
         <is>
-          <t>AZ</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="G9" s="12" t="inlineStr">
@@ -1501,10 +1481,14 @@
       </c>
       <c r="H9" s="12" t="inlineStr">
         <is>
-          <t>Junior circuit</t>
-        </is>
-      </c>
-      <c r="I9" s="12" t="inlineStr"/>
+          <t>National junior</t>
+        </is>
+      </c>
+      <c r="I9" s="12" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
       <c r="J9" s="14" t="n"/>
       <c r="K9" s="13" t="n"/>
       <c r="L9" s="15" t="n"/>
@@ -1516,17 +1500,17 @@
       <c r="O9" s="12" t="inlineStr"/>
       <c r="P9" s="17" t="inlineStr">
         <is>
-          <t>https://volleyballlife.com/tournament/41166</t>
+          <t>https://volleyballlife.com/tournament/41692</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="11" t="n">
-        <v>46445</v>
+        <v>46347</v>
       </c>
       <c r="B10" s="12" t="inlineStr">
         <is>
-          <t>estimated</t>
+          <t>posted</t>
         </is>
       </c>
       <c r="C10" s="13" t="n">
@@ -1534,12 +1518,12 @@
       </c>
       <c r="D10" s="12" t="inlineStr">
         <is>
-          <t>Highline Sponsorship Open ($5K)</t>
+          <t>MAVERICKS AVP Qualifier</t>
         </is>
       </c>
       <c r="E10" s="12" t="inlineStr">
         <is>
-          <t>Ocean Park North, Santa Monica</t>
+          <t>Main Beach, Santa Cruz</t>
         </is>
       </c>
       <c r="F10" s="12" t="inlineStr">
@@ -1549,27 +1533,23 @@
       </c>
       <c r="G10" s="12" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>18U</t>
         </is>
       </c>
       <c r="H10" s="12" t="inlineStr">
         <is>
-          <t>Out of reach</t>
+          <t>Junior circuit</t>
         </is>
       </c>
       <c r="I10" s="12" t="inlineStr"/>
       <c r="J10" s="14" t="n">
-        <v>10.0125</v>
+        <v>6.429</v>
       </c>
       <c r="K10" s="13" t="n">
-        <v>17</v>
-      </c>
-      <c r="L10" s="15" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="M10" s="15" t="n">
-        <v>3.25</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="L10" s="15" t="n"/>
+      <c r="M10" s="15" t="n"/>
       <c r="N10" s="16">
         <f>IFERROR(M10/L10,"")</f>
         <v/>
@@ -1577,13 +1557,13 @@
       <c r="O10" s="12" t="inlineStr"/>
       <c r="P10" s="17" t="inlineStr">
         <is>
-          <t>https://volleyballlife.com/tournament/36177</t>
+          <t>https://volleyballlife.com/tournament/35628</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="11" t="n">
-        <v>46445</v>
+        <v>46347</v>
       </c>
       <c r="B11" s="12" t="inlineStr">
         <is>
@@ -1591,16 +1571,16 @@
         </is>
       </c>
       <c r="C11" s="13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D11" s="12" t="inlineStr">
         <is>
-          <t>Futures Tour 3X: Spring Championships</t>
+          <t>CBVA women’s open</t>
         </is>
       </c>
       <c r="E11" s="12" t="inlineStr">
         <is>
-          <t>California</t>
+          <t>North Beach, Santa Monica</t>
         </is>
       </c>
       <c r="F11" s="12" t="inlineStr">
@@ -1610,45 +1590,39 @@
       </c>
       <c r="G11" s="12" t="inlineStr">
         <is>
-          <t>18U</t>
+          <t>Open</t>
         </is>
       </c>
       <c r="H11" s="12" t="inlineStr">
         <is>
-          <t>National junior</t>
-        </is>
-      </c>
-      <c r="I11" s="12" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="J11" s="14" t="n">
-        <v>8.7705</v>
-      </c>
+          <t>Women's open</t>
+        </is>
+      </c>
+      <c r="I11" s="12" t="inlineStr"/>
+      <c r="J11" s="14" t="n"/>
       <c r="K11" s="13" t="n">
-        <v>15</v>
-      </c>
-      <c r="L11" s="15" t="n">
-        <v>20.57142857142857</v>
-      </c>
-      <c r="M11" s="15" t="n">
-        <v>10.5</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="L11" s="15" t="n"/>
+      <c r="M11" s="15" t="n"/>
       <c r="N11" s="16">
         <f>IFERROR(M11/L11,"")</f>
         <v/>
       </c>
-      <c r="O11" s="12" t="inlineStr"/>
+      <c r="O11" s="12" t="inlineStr">
+        <is>
+          <t>21 Nov + 22 Nov</t>
+        </is>
+      </c>
       <c r="P11" s="17" t="inlineStr">
         <is>
-          <t>https://volleyballlife.com/tournament/41709</t>
+          <t>https://cbva.com/venues/16</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="11" t="n">
-        <v>46453</v>
+        <v>46348</v>
       </c>
       <c r="B12" s="12" t="inlineStr">
         <is>
@@ -1660,12 +1634,12 @@
       </c>
       <c r="D12" s="12" t="inlineStr">
         <is>
-          <t>California IBVL Winter Series Championships (p1440)</t>
+          <t>CBVA women’s open</t>
         </is>
       </c>
       <c r="E12" s="12" t="inlineStr">
         <is>
-          <t>Hermosa Beach Pier</t>
+          <t>Main Beach, Laguna Beach</t>
         </is>
       </c>
       <c r="F12" s="12" t="inlineStr">
@@ -1675,26 +1649,26 @@
       </c>
       <c r="G12" s="12" t="inlineStr">
         <is>
-          <t>18U</t>
+          <t>Open</t>
         </is>
       </c>
       <c r="H12" s="12" t="inlineStr">
         <is>
-          <t>Junior circuit</t>
+          <t>Women's open</t>
         </is>
       </c>
       <c r="I12" s="12" t="inlineStr"/>
       <c r="J12" s="14" t="n">
-        <v>8.922000000000001</v>
+        <v>8.929</v>
       </c>
       <c r="K12" s="13" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="L12" s="15" t="n">
-        <v>8.333333333333334</v>
+        <v>6.5</v>
       </c>
       <c r="M12" s="15" t="n">
-        <v>8</v>
+        <v>5.5</v>
       </c>
       <c r="N12" s="16">
         <f>IFERROR(M12/L12,"")</f>
@@ -1702,18 +1676,18 @@
       </c>
       <c r="O12" s="12" t="inlineStr">
         <is>
-          <t>6 Mar + 7 Mar</t>
+          <t>21 Nov + 22 Nov</t>
         </is>
       </c>
       <c r="P12" s="17" t="inlineStr">
         <is>
-          <t>https://volleyballlife.com/tournament/41072</t>
+          <t>https://cbva.com/venues/5</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="11" t="n">
-        <v>46467</v>
+        <v>46368</v>
       </c>
       <c r="B13" s="12" t="inlineStr">
         <is>
@@ -1725,17 +1699,17 @@
       </c>
       <c r="D13" s="12" t="inlineStr">
         <is>
-          <t>Marine Open (Girls p1440)</t>
+          <t>AVP Winter Las Vegas</t>
         </is>
       </c>
       <c r="E13" s="12" t="inlineStr">
         <is>
-          <t>Manhattan Beach Lifeguard HQ</t>
+          <t>Sunset Park, Las Vegas</t>
         </is>
       </c>
       <c r="F13" s="12" t="inlineStr">
         <is>
-          <t>CA</t>
+          <t>NV</t>
         </is>
       </c>
       <c r="G13" s="12" t="inlineStr">
@@ -1749,7 +1723,9 @@
         </is>
       </c>
       <c r="I13" s="12" t="inlineStr"/>
-      <c r="J13" s="14" t="n"/>
+      <c r="J13" s="14" t="n">
+        <v>6.2515</v>
+      </c>
       <c r="K13" s="13" t="n">
         <v>0</v>
       </c>
@@ -1759,24 +1735,20 @@
         <f>IFERROR(M13/L13,"")</f>
         <v/>
       </c>
-      <c r="O13" s="12" t="inlineStr">
-        <is>
-          <t>20 Mar + 21 Mar</t>
-        </is>
-      </c>
+      <c r="O13" s="12" t="inlineStr"/>
       <c r="P13" s="17" t="inlineStr">
         <is>
-          <t>https://volleyballlife.com/tournament/41074</t>
+          <t>https://volleyballlife.com/tournament/41138</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="11" t="n">
-        <v>46452</v>
+        <v>46368</v>
       </c>
       <c r="B14" s="12" t="inlineStr">
         <is>
-          <t>projected</t>
+          <t>posted</t>
         </is>
       </c>
       <c r="C14" s="13" t="n">
@@ -1784,64 +1756,52 @@
       </c>
       <c r="D14" s="12" t="inlineStr">
         <is>
-          <t>CBVA women’s open</t>
+          <t>p1440 1X Ranking Event</t>
         </is>
       </c>
       <c r="E14" s="12" t="inlineStr">
         <is>
-          <t>Manhattan Pier, Manhattan Beach</t>
+          <t>Arizona Athletic Grounds, Mesa</t>
         </is>
       </c>
       <c r="F14" s="12" t="inlineStr">
         <is>
-          <t>CA</t>
+          <t>AZ</t>
         </is>
       </c>
       <c r="G14" s="12" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>18U</t>
         </is>
       </c>
       <c r="H14" s="12" t="inlineStr">
         <is>
-          <t>Women's open</t>
+          <t>Junior circuit</t>
         </is>
       </c>
       <c r="I14" s="12" t="inlineStr"/>
-      <c r="J14" s="14" t="n">
-        <v>9.166499999999999</v>
-      </c>
-      <c r="K14" s="13" t="n">
-        <v>6</v>
-      </c>
-      <c r="L14" s="15" t="n">
-        <v>9.266666666666667</v>
-      </c>
-      <c r="M14" s="15" t="n">
-        <v>5.933333333333334</v>
-      </c>
+      <c r="J14" s="14" t="n"/>
+      <c r="K14" s="13" t="n"/>
+      <c r="L14" s="15" t="n"/>
+      <c r="M14" s="15" t="n"/>
       <c r="N14" s="16">
         <f>IFERROR(M14/L14,"")</f>
         <v/>
       </c>
-      <c r="O14" s="12" t="inlineStr">
-        <is>
-          <t>6 Mar + 7 Mar</t>
-        </is>
-      </c>
+      <c r="O14" s="12" t="inlineStr"/>
       <c r="P14" s="17" t="inlineStr">
         <is>
-          <t>https://cbva.com/venues/2</t>
+          <t>https://volleyballlife.com/tournament/41164</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="11" t="n">
-        <v>46466</v>
+        <v>46369</v>
       </c>
       <c r="B15" s="12" t="inlineStr">
         <is>
-          <t>projected</t>
+          <t>posted</t>
         </is>
       </c>
       <c r="C15" s="13" t="n">
@@ -1849,12 +1809,12 @@
       </c>
       <c r="D15" s="12" t="inlineStr">
         <is>
-          <t>CBVA women’s open</t>
+          <t>Los Angeles Grand Prix (p1440)</t>
         </is>
       </c>
       <c r="E15" s="12" t="inlineStr">
         <is>
-          <t>Newland, Huntington Beach</t>
+          <t>Hermosa Beach Pier</t>
         </is>
       </c>
       <c r="F15" s="12" t="inlineStr">
@@ -1864,49 +1824,45 @@
       </c>
       <c r="G15" s="12" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>18U</t>
         </is>
       </c>
       <c r="H15" s="12" t="inlineStr">
         <is>
-          <t>Women's open</t>
+          <t>Junior circuit</t>
         </is>
       </c>
       <c r="I15" s="12" t="inlineStr"/>
       <c r="J15" s="14" t="n">
-        <v>9.088000000000001</v>
+        <v>9.130500000000001</v>
       </c>
       <c r="K15" s="13" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="L15" s="15" t="n">
-        <v>4.523809523809524</v>
+        <v>2.5</v>
       </c>
       <c r="M15" s="15" t="n">
-        <v>3.047619047619047</v>
+        <v>1</v>
       </c>
       <c r="N15" s="16">
         <f>IFERROR(M15/L15,"")</f>
         <v/>
       </c>
-      <c r="O15" s="12" t="inlineStr">
-        <is>
-          <t>20 Mar + 21 Mar</t>
-        </is>
-      </c>
+      <c r="O15" s="12" t="inlineStr"/>
       <c r="P15" s="17" t="inlineStr">
         <is>
-          <t>https://cbva.com/venues/4</t>
+          <t>https://volleyballlife.com/tournament/32937</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="11" t="n">
-        <v>46474</v>
+        <v>46369</v>
       </c>
       <c r="B16" s="12" t="inlineStr">
         <is>
-          <t>projected</t>
+          <t>posted</t>
         </is>
       </c>
       <c r="C16" s="13" t="n">
@@ -1914,12 +1870,12 @@
       </c>
       <c r="D16" s="12" t="inlineStr">
         <is>
-          <t>CBVA women’s open</t>
+          <t>Pan Pacific Championships (p1440)</t>
         </is>
       </c>
       <c r="E16" s="12" t="inlineStr">
         <is>
-          <t>Dockweiler, Los Angeles</t>
+          <t>Hermosa Beach Pier</t>
         </is>
       </c>
       <c r="F16" s="12" t="inlineStr">
@@ -1929,26 +1885,26 @@
       </c>
       <c r="G16" s="12" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>18U</t>
         </is>
       </c>
       <c r="H16" s="12" t="inlineStr">
         <is>
-          <t>Women's open</t>
+          <t>Junior circuit</t>
         </is>
       </c>
       <c r="I16" s="12" t="inlineStr"/>
       <c r="J16" s="14" t="n">
-        <v>8.755000000000001</v>
+        <v>8.743</v>
       </c>
       <c r="K16" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="L16" s="15" t="n">
         <v>2</v>
       </c>
-      <c r="L16" s="15" t="n">
-        <v>5.25</v>
-      </c>
       <c r="M16" s="15" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="N16" s="16">
         <f>IFERROR(M16/L16,"")</f>
@@ -1957,13 +1913,13 @@
       <c r="O16" s="12" t="inlineStr"/>
       <c r="P16" s="17" t="inlineStr">
         <is>
-          <t>https://cbva.com/venues/1</t>
+          <t>https://volleyballlife.com/tournament/35288</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="11" t="n">
-        <v>46480</v>
+        <v>46386</v>
       </c>
       <c r="B17" s="12" t="inlineStr">
         <is>
@@ -1971,16 +1927,16 @@
         </is>
       </c>
       <c r="C17" s="13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D17" s="12" t="inlineStr">
         <is>
-          <t>Futures Tour 2X: California</t>
+          <t>IBVL Winter Series #1 (Girls)</t>
         </is>
       </c>
       <c r="E17" s="12" t="inlineStr">
         <is>
-          <t>North Beach, Santa Monica</t>
+          <t>Hermosa Beach Pier</t>
         </is>
       </c>
       <c r="F17" s="12" t="inlineStr">
@@ -1998,15 +1954,19 @@
           <t>Junior circuit</t>
         </is>
       </c>
-      <c r="I17" s="12" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="J17" s="14" t="n"/>
-      <c r="K17" s="13" t="n"/>
-      <c r="L17" s="15" t="n"/>
-      <c r="M17" s="15" t="n"/>
+      <c r="I17" s="12" t="inlineStr"/>
+      <c r="J17" s="14" t="n">
+        <v>9.076499999999999</v>
+      </c>
+      <c r="K17" s="13" t="n">
+        <v>8</v>
+      </c>
+      <c r="L17" s="15" t="n">
+        <v>7.75</v>
+      </c>
+      <c r="M17" s="15" t="n">
+        <v>4</v>
+      </c>
       <c r="N17" s="16">
         <f>IFERROR(M17/L17,"")</f>
         <v/>
@@ -2014,13 +1974,13 @@
       <c r="O17" s="12" t="inlineStr"/>
       <c r="P17" s="17" t="inlineStr">
         <is>
-          <t>https://volleyballlife.com/tournament/41882</t>
+          <t>https://volleyballlife.com/tournament/41068</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="11" t="n">
-        <v>46495</v>
+        <v>46396</v>
       </c>
       <c r="B18" s="12" t="inlineStr">
         <is>
@@ -2032,17 +1992,17 @@
       </c>
       <c r="D18" s="12" t="inlineStr">
         <is>
-          <t>p1440 Hermosa Beach Circuit Championships (2X)</t>
+          <t>p1440 1X Ranking Event</t>
         </is>
       </c>
       <c r="E18" s="12" t="inlineStr">
         <is>
-          <t>Hermosa Beach Pier</t>
+          <t>Arizona Athletic Grounds, Phoenix</t>
         </is>
       </c>
       <c r="F18" s="12" t="inlineStr">
         <is>
-          <t>CA</t>
+          <t>AZ</t>
         </is>
       </c>
       <c r="G18" s="12" t="inlineStr">
@@ -2056,18 +2016,10 @@
         </is>
       </c>
       <c r="I18" s="12" t="inlineStr"/>
-      <c r="J18" s="14" t="n">
-        <v>9.414</v>
-      </c>
-      <c r="K18" s="13" t="n">
-        <v>7</v>
-      </c>
-      <c r="L18" s="15" t="n">
-        <v>5.25</v>
-      </c>
-      <c r="M18" s="15" t="n">
-        <v>3.25</v>
-      </c>
+      <c r="J18" s="14" t="n"/>
+      <c r="K18" s="13" t="n"/>
+      <c r="L18" s="15" t="n"/>
+      <c r="M18" s="15" t="n"/>
       <c r="N18" s="16">
         <f>IFERROR(M18/L18,"")</f>
         <v/>
@@ -2075,17 +2027,17 @@
       <c r="O18" s="12" t="inlineStr"/>
       <c r="P18" s="17" t="inlineStr">
         <is>
-          <t>https://volleyballlife.com/tournament/41075</t>
+          <t>https://volleyballlife.com/tournament/41165</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="11" t="n">
-        <v>46488</v>
+        <v>46397</v>
       </c>
       <c r="B19" s="12" t="inlineStr">
         <is>
-          <t>projected</t>
+          <t>posted</t>
         </is>
       </c>
       <c r="C19" s="13" t="n">
@@ -2093,12 +2045,12 @@
       </c>
       <c r="D19" s="12" t="inlineStr">
         <is>
-          <t>CBVA women’s open</t>
+          <t>IBVL Winter Classic (Girls p1440)</t>
         </is>
       </c>
       <c r="E19" s="12" t="inlineStr">
         <is>
-          <t>Ocean Park, Santa Monica</t>
+          <t>Hermosa Beach Pier</t>
         </is>
       </c>
       <c r="F19" s="12" t="inlineStr">
@@ -2108,26 +2060,26 @@
       </c>
       <c r="G19" s="12" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>18U</t>
         </is>
       </c>
       <c r="H19" s="12" t="inlineStr">
         <is>
-          <t>Women's open</t>
+          <t>Junior circuit</t>
         </is>
       </c>
       <c r="I19" s="12" t="inlineStr"/>
       <c r="J19" s="14" t="n">
-        <v>9.015000000000001</v>
+        <v>9.076499999999999</v>
       </c>
       <c r="K19" s="13" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="L19" s="15" t="n">
-        <v>4.266666666666667</v>
+        <v>7.75</v>
       </c>
       <c r="M19" s="15" t="n">
-        <v>2.866666666666667</v>
+        <v>4</v>
       </c>
       <c r="N19" s="16">
         <f>IFERROR(M19/L19,"")</f>
@@ -2136,59 +2088,63 @@
       <c r="O19" s="12" t="inlineStr"/>
       <c r="P19" s="17" t="inlineStr">
         <is>
-          <t>https://cbva.com/venues/7</t>
+          <t>https://volleyballlife.com/tournament/41069</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="11" t="n">
-        <v>46501</v>
+        <v>46403</v>
       </c>
       <c r="B20" s="12" t="inlineStr">
         <is>
-          <t>projected</t>
+          <t>posted</t>
         </is>
       </c>
       <c r="C20" s="13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D20" s="12" t="inlineStr">
         <is>
-          <t>CBVA women’s open</t>
+          <t>Futures Tour 2X: Arizona</t>
         </is>
       </c>
       <c r="E20" s="12" t="inlineStr">
         <is>
-          <t>Manhattan Pier, Manhattan Beach</t>
+          <t>Arizona Athletic Grounds, Phoenix</t>
         </is>
       </c>
       <c r="F20" s="12" t="inlineStr">
         <is>
-          <t>CA</t>
+          <t>AZ</t>
         </is>
       </c>
       <c r="G20" s="12" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>18U</t>
         </is>
       </c>
       <c r="H20" s="12" t="inlineStr">
         <is>
-          <t>Women's open</t>
-        </is>
-      </c>
-      <c r="I20" s="12" t="inlineStr"/>
+          <t>Junior circuit</t>
+        </is>
+      </c>
+      <c r="I20" s="12" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
       <c r="J20" s="14" t="n">
-        <v>8.885</v>
+        <v>8.286</v>
       </c>
       <c r="K20" s="13" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="L20" s="15" t="n">
-        <v>3.533333333333333</v>
+        <v>21</v>
       </c>
       <c r="M20" s="15" t="n">
-        <v>1.333333333333333</v>
+        <v>8.25</v>
       </c>
       <c r="N20" s="16">
         <f>IFERROR(M20/L20,"")</f>
@@ -2197,30 +2153,30 @@
       <c r="O20" s="12" t="inlineStr"/>
       <c r="P20" s="17" t="inlineStr">
         <is>
-          <t>https://cbva.com/venues/2</t>
+          <t>https://volleyballlife.com/tournament/41707</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="11" t="n">
-        <v>46501</v>
+        <v>46410</v>
       </c>
       <c r="B21" s="12" t="inlineStr">
         <is>
-          <t>projected</t>
+          <t>posted</t>
         </is>
       </c>
       <c r="C21" s="13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D21" s="12" t="inlineStr">
         <is>
-          <t>CBVA women’s open</t>
+          <t>IBVL Winter Nationals (Girls)</t>
         </is>
       </c>
       <c r="E21" s="12" t="inlineStr">
         <is>
-          <t>Main Beach, Santa Cruz</t>
+          <t>Hermosa Beach Pier</t>
         </is>
       </c>
       <c r="F21" s="12" t="inlineStr">
@@ -2230,26 +2186,26 @@
       </c>
       <c r="G21" s="12" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>18U</t>
         </is>
       </c>
       <c r="H21" s="12" t="inlineStr">
         <is>
-          <t>Women's open</t>
+          <t>Junior circuit</t>
         </is>
       </c>
       <c r="I21" s="12" t="inlineStr"/>
       <c r="J21" s="14" t="n">
-        <v>7.68</v>
+        <v>9.484999999999999</v>
       </c>
       <c r="K21" s="13" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="L21" s="15" t="n">
-        <v>3.666666666666667</v>
+        <v>16</v>
       </c>
       <c r="M21" s="15" t="n">
-        <v>0.6666666666666666</v>
+        <v>11</v>
       </c>
       <c r="N21" s="16">
         <f>IFERROR(M21/L21,"")</f>
@@ -2258,30 +2214,30 @@
       <c r="O21" s="12" t="inlineStr"/>
       <c r="P21" s="17" t="inlineStr">
         <is>
-          <t>https://cbva.com/venues/8</t>
+          <t>https://volleyballlife.com/tournament/41070</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="11" t="n">
-        <v>46522</v>
+        <v>46416</v>
       </c>
       <c r="B22" s="12" t="inlineStr">
         <is>
-          <t>projected</t>
+          <t>estimated</t>
         </is>
       </c>
       <c r="C22" s="13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D22" s="12" t="inlineStr">
         <is>
-          <t>CBVA women’s open</t>
+          <t>USAV U18 Beach National Team Trials</t>
         </is>
       </c>
       <c r="E22" s="12" t="inlineStr">
         <is>
-          <t>Ocean Park, Santa Monica</t>
+          <t>Manhattan Beach Pier</t>
         </is>
       </c>
       <c r="F22" s="12" t="inlineStr">
@@ -2291,49 +2247,49 @@
       </c>
       <c r="G22" s="12" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>18U</t>
         </is>
       </c>
       <c r="H22" s="12" t="inlineStr">
         <is>
-          <t>Women's open</t>
-        </is>
-      </c>
-      <c r="I22" s="12" t="inlineStr"/>
+          <t>Selection</t>
+        </is>
+      </c>
+      <c r="I22" s="12" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
       <c r="J22" s="14" t="n">
-        <v>8.757</v>
+        <v>9.4015</v>
       </c>
       <c r="K22" s="13" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L22" s="15" t="n">
-        <v>3.777777777777778</v>
+        <v>12.5</v>
       </c>
       <c r="M22" s="15" t="n">
-        <v>2</v>
+        <v>9.5</v>
       </c>
       <c r="N22" s="16">
         <f>IFERROR(M22/L22,"")</f>
         <v/>
       </c>
-      <c r="O22" s="12" t="inlineStr">
-        <is>
-          <t>15 May + 16 May</t>
-        </is>
-      </c>
+      <c r="O22" s="12" t="inlineStr"/>
       <c r="P22" s="17" t="inlineStr">
         <is>
-          <t>https://cbva.com/venues/7</t>
+          <t>https://volleyballlife.com/tournament/34180</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="11" t="n">
-        <v>46523</v>
+        <v>46424</v>
       </c>
       <c r="B23" s="12" t="inlineStr">
         <is>
-          <t>projected</t>
+          <t>posted</t>
         </is>
       </c>
       <c r="C23" s="13" t="n">
@@ -2341,12 +2297,12 @@
       </c>
       <c r="D23" s="12" t="inlineStr">
         <is>
-          <t>CBVA women’s open</t>
+          <t>Kauai Bikini Open</t>
         </is>
       </c>
       <c r="E23" s="12" t="inlineStr">
         <is>
-          <t>Belmont Shore, Long Beach</t>
+          <t>North Beach, Santa Monica</t>
         </is>
       </c>
       <c r="F23" s="12" t="inlineStr">
@@ -2356,49 +2312,45 @@
       </c>
       <c r="G23" s="12" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>18U</t>
         </is>
       </c>
       <c r="H23" s="12" t="inlineStr">
         <is>
-          <t>Women's open</t>
+          <t>Junior circuit</t>
         </is>
       </c>
       <c r="I23" s="12" t="inlineStr"/>
       <c r="J23" s="14" t="n">
-        <v>8.757</v>
+        <v>7.224</v>
       </c>
       <c r="K23" s="13" t="n">
-        <v>4</v>
-      </c>
-      <c r="L23" s="15" t="n">
-        <v>4.25</v>
-      </c>
-      <c r="M23" s="15" t="n">
-        <v>1.75</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="L23" s="15" t="n"/>
+      <c r="M23" s="15" t="n"/>
       <c r="N23" s="16">
         <f>IFERROR(M23/L23,"")</f>
         <v/>
       </c>
       <c r="O23" s="12" t="inlineStr">
         <is>
-          <t>15 May + 16 May</t>
+          <t>6 Feb + 7 Feb</t>
         </is>
       </c>
       <c r="P23" s="17" t="inlineStr">
         <is>
-          <t>https://cbva.com/venues/3</t>
+          <t>https://volleyballlife.com/tournament/41121</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="11" t="n">
-        <v>46508</v>
+        <v>46425</v>
       </c>
       <c r="B24" s="12" t="inlineStr">
         <is>
-          <t>projected</t>
+          <t>posted</t>
         </is>
       </c>
       <c r="C24" s="13" t="n">
@@ -2406,12 +2358,12 @@
       </c>
       <c r="D24" s="12" t="inlineStr">
         <is>
-          <t>CBVA women’s open</t>
+          <t>IBVL Winter Nationals (School Event) — ISF trial</t>
         </is>
       </c>
       <c r="E24" s="12" t="inlineStr">
         <is>
-          <t>Manhattan Pier, Manhattan Beach</t>
+          <t>Hermosa Beach Pier</t>
         </is>
       </c>
       <c r="F24" s="12" t="inlineStr">
@@ -2421,45 +2373,53 @@
       </c>
       <c r="G24" s="12" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>18U</t>
         </is>
       </c>
       <c r="H24" s="12" t="inlineStr">
         <is>
-          <t>Women's open</t>
-        </is>
-      </c>
-      <c r="I24" s="12" t="inlineStr"/>
+          <t>Selection</t>
+        </is>
+      </c>
+      <c r="I24" s="12" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
       <c r="J24" s="14" t="n">
-        <v>8.826000000000001</v>
+        <v>9.484999999999999</v>
       </c>
       <c r="K24" s="13" t="n">
         <v>4</v>
       </c>
       <c r="L24" s="15" t="n">
-        <v>3.75</v>
+        <v>16</v>
       </c>
       <c r="M24" s="15" t="n">
-        <v>1.25</v>
+        <v>11</v>
       </c>
       <c r="N24" s="16">
         <f>IFERROR(M24/L24,"")</f>
         <v/>
       </c>
-      <c r="O24" s="12" t="inlineStr"/>
+      <c r="O24" s="12" t="inlineStr">
+        <is>
+          <t>6 Feb + 7 Feb</t>
+        </is>
+      </c>
       <c r="P24" s="17" t="inlineStr">
         <is>
-          <t>https://cbva.com/venues/2</t>
+          <t>https://volleyballlife.com/tournament/41071</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="11" t="n">
-        <v>46536</v>
+        <v>46431</v>
       </c>
       <c r="B25" s="12" t="inlineStr">
         <is>
-          <t>projected</t>
+          <t>posted</t>
         </is>
       </c>
       <c r="C25" s="13" t="n">
@@ -2467,42 +2427,34 @@
       </c>
       <c r="D25" s="12" t="inlineStr">
         <is>
-          <t>CBVA women’s open</t>
+          <t>p1440 1X Ranking Event</t>
         </is>
       </c>
       <c r="E25" s="12" t="inlineStr">
         <is>
-          <t>Ocean Beach, San Diego</t>
+          <t>Arizona Athletic Grounds, Phoenix</t>
         </is>
       </c>
       <c r="F25" s="12" t="inlineStr">
         <is>
-          <t>CA</t>
+          <t>AZ</t>
         </is>
       </c>
       <c r="G25" s="12" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>18U</t>
         </is>
       </c>
       <c r="H25" s="12" t="inlineStr">
         <is>
-          <t>Women's open</t>
+          <t>Junior circuit</t>
         </is>
       </c>
       <c r="I25" s="12" t="inlineStr"/>
-      <c r="J25" s="14" t="n">
-        <v>7.783</v>
-      </c>
-      <c r="K25" s="13" t="n">
-        <v>3</v>
-      </c>
-      <c r="L25" s="15" t="n">
-        <v>3</v>
-      </c>
-      <c r="M25" s="15" t="n">
-        <v>1</v>
-      </c>
+      <c r="J25" s="14" t="n"/>
+      <c r="K25" s="13" t="n"/>
+      <c r="L25" s="15" t="n"/>
+      <c r="M25" s="15" t="n"/>
       <c r="N25" s="16">
         <f>IFERROR(M25/L25,"")</f>
         <v/>
@@ -2510,17 +2462,17 @@
       <c r="O25" s="12" t="inlineStr"/>
       <c r="P25" s="17" t="inlineStr">
         <is>
-          <t>https://cbva.com/venues/13</t>
+          <t>https://volleyballlife.com/tournament/41166</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="11" t="n">
-        <v>46529</v>
+        <v>46445</v>
       </c>
       <c r="B26" s="12" t="inlineStr">
         <is>
-          <t>projected</t>
+          <t>estimated</t>
         </is>
       </c>
       <c r="C26" s="13" t="n">
@@ -2528,12 +2480,12 @@
       </c>
       <c r="D26" s="12" t="inlineStr">
         <is>
-          <t>CBVA women’s open</t>
+          <t>Highline Sponsorship Open ($5K)</t>
         </is>
       </c>
       <c r="E26" s="12" t="inlineStr">
         <is>
-          <t>Hermosa Pier, Hermosa Beach</t>
+          <t>Ocean Park North, Santa Monica</t>
         </is>
       </c>
       <c r="F26" s="12" t="inlineStr">
@@ -2548,21 +2500,21 @@
       </c>
       <c r="H26" s="12" t="inlineStr">
         <is>
-          <t>Women's open</t>
+          <t>Out of reach</t>
         </is>
       </c>
       <c r="I26" s="12" t="inlineStr"/>
       <c r="J26" s="14" t="n">
-        <v>9.109999999999999</v>
+        <v>10.0125</v>
       </c>
       <c r="K26" s="13" t="n">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="L26" s="15" t="n">
-        <v>2.714285714285714</v>
+        <v>5.5</v>
       </c>
       <c r="M26" s="15" t="n">
-        <v>0.8571428571428571</v>
+        <v>3.25</v>
       </c>
       <c r="N26" s="16">
         <f>IFERROR(M26/L26,"")</f>
@@ -2571,30 +2523,30 @@
       <c r="O26" s="12" t="inlineStr"/>
       <c r="P26" s="17" t="inlineStr">
         <is>
-          <t>https://cbva.com/venues/6</t>
+          <t>https://volleyballlife.com/tournament/36177</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="11" t="n">
-        <v>46529</v>
+        <v>46445</v>
       </c>
       <c r="B27" s="12" t="inlineStr">
         <is>
-          <t>projected</t>
+          <t>posted</t>
         </is>
       </c>
       <c r="C27" s="13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D27" s="12" t="inlineStr">
         <is>
-          <t>CBVA women’s open</t>
+          <t>Futures Tour 3X: Spring Championships</t>
         </is>
       </c>
       <c r="E27" s="12" t="inlineStr">
         <is>
-          <t>Main Beach, Santa Cruz</t>
+          <t>California</t>
         </is>
       </c>
       <c r="F27" s="12" t="inlineStr">
@@ -2604,26 +2556,30 @@
       </c>
       <c r="G27" s="12" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>18U</t>
         </is>
       </c>
       <c r="H27" s="12" t="inlineStr">
         <is>
-          <t>Women's open</t>
-        </is>
-      </c>
-      <c r="I27" s="12" t="inlineStr"/>
+          <t>National junior</t>
+        </is>
+      </c>
+      <c r="I27" s="12" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
       <c r="J27" s="14" t="n">
-        <v>7.668</v>
+        <v>8.7705</v>
       </c>
       <c r="K27" s="13" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="L27" s="15" t="n">
-        <v>4</v>
+        <v>20.57142857142857</v>
       </c>
       <c r="M27" s="15" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="N27" s="16">
         <f>IFERROR(M27/L27,"")</f>
@@ -2632,13 +2588,13 @@
       <c r="O27" s="12" t="inlineStr"/>
       <c r="P27" s="17" t="inlineStr">
         <is>
-          <t>https://cbva.com/venues/8</t>
+          <t>https://volleyballlife.com/tournament/41709</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="11" t="n">
-        <v>46543</v>
+        <v>46453</v>
       </c>
       <c r="B28" s="12" t="inlineStr">
         <is>
@@ -2650,12 +2606,12 @@
       </c>
       <c r="D28" s="12" t="inlineStr">
         <is>
-          <t>Kauai Bikini Open</t>
+          <t>California IBVL Winter Series Championships (p1440)</t>
         </is>
       </c>
       <c r="E28" s="12" t="inlineStr">
         <is>
-          <t>North Beach, Santa Monica</t>
+          <t>Hermosa Beach Pier</t>
         </is>
       </c>
       <c r="F28" s="12" t="inlineStr">
@@ -2675,48 +2631,52 @@
       </c>
       <c r="I28" s="12" t="inlineStr"/>
       <c r="J28" s="14" t="n">
-        <v>6.8205</v>
+        <v>8.922000000000001</v>
       </c>
       <c r="K28" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="L28" s="15" t="n"/>
-      <c r="M28" s="15" t="n"/>
+        <v>1</v>
+      </c>
+      <c r="L28" s="15" t="n">
+        <v>8.333333333333334</v>
+      </c>
+      <c r="M28" s="15" t="n">
+        <v>8</v>
+      </c>
       <c r="N28" s="16">
         <f>IFERROR(M28/L28,"")</f>
         <v/>
       </c>
       <c r="O28" s="12" t="inlineStr">
         <is>
-          <t>5 Jun + 6 Jun</t>
+          <t>6 Mar + 7 Mar</t>
         </is>
       </c>
       <c r="P28" s="17" t="inlineStr">
         <is>
-          <t>https://volleyballlife.com/tournament/41127</t>
+          <t>https://volleyballlife.com/tournament/41072</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="11" t="n">
-        <v>46552</v>
+        <v>46467</v>
       </c>
       <c r="B29" s="12" t="inlineStr">
         <is>
-          <t>estimated</t>
+          <t>posted</t>
         </is>
       </c>
       <c r="C29" s="13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D29" s="12" t="inlineStr">
         <is>
-          <t>USAV U19 / U21 Worlds Trials — if the cycle runs</t>
+          <t>Marine Open (Girls p1440)</t>
         </is>
       </c>
       <c r="E29" s="12" t="inlineStr">
         <is>
-          <t>Hermosa Beach Pier</t>
+          <t>Manhattan Beach Lifeguard HQ</t>
         </is>
       </c>
       <c r="F29" s="12" t="inlineStr">
@@ -2726,50 +2686,56 @@
       </c>
       <c r="G29" s="12" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>18U</t>
         </is>
       </c>
       <c r="H29" s="12" t="inlineStr">
         <is>
-          <t>Selection</t>
+          <t>Junior circuit</t>
         </is>
       </c>
       <c r="I29" s="12" t="inlineStr"/>
       <c r="J29" s="14" t="n"/>
-      <c r="K29" s="13" t="n"/>
+      <c r="K29" s="13" t="n">
+        <v>0</v>
+      </c>
       <c r="L29" s="15" t="n"/>
       <c r="M29" s="15" t="n"/>
       <c r="N29" s="16">
         <f>IFERROR(M29/L29,"")</f>
         <v/>
       </c>
-      <c r="O29" s="12" t="inlineStr"/>
+      <c r="O29" s="12" t="inlineStr">
+        <is>
+          <t>20 Mar + 21 Mar</t>
+        </is>
+      </c>
       <c r="P29" s="17" t="inlineStr">
         <is>
-          <t>https://usavolleyball.org/events/</t>
+          <t>https://volleyballlife.com/tournament/41074</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="11" t="n">
-        <v>46566</v>
+        <v>46452</v>
       </c>
       <c r="B30" s="12" t="inlineStr">
         <is>
-          <t>estimated</t>
+          <t>projected</t>
         </is>
       </c>
       <c r="C30" s="13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D30" s="12" t="inlineStr">
         <is>
-          <t>BVCA Pairs West Coast Championships</t>
+          <t>CBVA women’s open</t>
         </is>
       </c>
       <c r="E30" s="12" t="inlineStr">
         <is>
-          <t>Newland, Huntington Beach</t>
+          <t>Manhattan Pier, Manhattan Beach</t>
         </is>
       </c>
       <c r="F30" s="12" t="inlineStr">
@@ -2779,53 +2745,57 @@
       </c>
       <c r="G30" s="12" t="inlineStr">
         <is>
-          <t>18U</t>
+          <t>Open</t>
         </is>
       </c>
       <c r="H30" s="12" t="inlineStr">
         <is>
-          <t>Junior circuit</t>
+          <t>Women's open</t>
         </is>
       </c>
       <c r="I30" s="12" t="inlineStr"/>
       <c r="J30" s="14" t="n">
-        <v>8.1805</v>
+        <v>9.166499999999999</v>
       </c>
       <c r="K30" s="13" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="L30" s="15" t="n">
-        <v>17.4</v>
+        <v>9.266666666666667</v>
       </c>
       <c r="M30" s="15" t="n">
-        <v>8.4</v>
+        <v>5.933333333333334</v>
       </c>
       <c r="N30" s="16">
         <f>IFERROR(M30/L30,"")</f>
         <v/>
       </c>
-      <c r="O30" s="12" t="inlineStr"/>
+      <c r="O30" s="12" t="inlineStr">
+        <is>
+          <t>6 Mar + 7 Mar</t>
+        </is>
+      </c>
       <c r="P30" s="17" t="inlineStr">
         <is>
-          <t>https://volleyballlife.com/tournament/35588</t>
+          <t>https://cbva.com/venues/2</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="11" t="n">
-        <v>46566</v>
+        <v>46466</v>
       </c>
       <c r="B31" s="12" t="inlineStr">
         <is>
-          <t>estimated</t>
+          <t>projected</t>
         </is>
       </c>
       <c r="C31" s="13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D31" s="12" t="inlineStr">
         <is>
-          <t>BVCA Pairs West Coast Championships</t>
+          <t>CBVA women’s open</t>
         </is>
       </c>
       <c r="E31" s="12" t="inlineStr">
@@ -2840,91 +2810,91 @@
       </c>
       <c r="G31" s="12" t="inlineStr">
         <is>
-          <t>17U</t>
+          <t>Open</t>
         </is>
       </c>
       <c r="H31" s="12" t="inlineStr">
         <is>
-          <t>Junior circuit</t>
-        </is>
-      </c>
-      <c r="I31" s="12" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+          <t>Women's open</t>
+        </is>
+      </c>
+      <c r="I31" s="12" t="inlineStr"/>
       <c r="J31" s="14" t="n">
-        <v>7.398</v>
+        <v>9.088000000000001</v>
       </c>
       <c r="K31" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="L31" s="15" t="n"/>
-      <c r="M31" s="15" t="n"/>
+        <v>8</v>
+      </c>
+      <c r="L31" s="15" t="n">
+        <v>4.523809523809524</v>
+      </c>
+      <c r="M31" s="15" t="n">
+        <v>3.047619047619047</v>
+      </c>
       <c r="N31" s="16">
         <f>IFERROR(M31/L31,"")</f>
         <v/>
       </c>
-      <c r="O31" s="12" t="inlineStr"/>
+      <c r="O31" s="12" t="inlineStr">
+        <is>
+          <t>20 Mar + 21 Mar</t>
+        </is>
+      </c>
       <c r="P31" s="17" t="inlineStr">
         <is>
-          <t>https://volleyballlife.com/tournament/35588</t>
+          <t>https://cbva.com/venues/4</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="11" t="n">
-        <v>46566</v>
+        <v>46474</v>
       </c>
       <c r="B32" s="12" t="inlineStr">
         <is>
-          <t>posted</t>
+          <t>projected</t>
         </is>
       </c>
       <c r="C32" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="D32" s="12" t="inlineStr">
+        <is>
+          <t>CBVA women’s open</t>
+        </is>
+      </c>
+      <c r="E32" s="12" t="inlineStr">
+        <is>
+          <t>Dockweiler, Los Angeles</t>
+        </is>
+      </c>
+      <c r="F32" s="12" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
+      <c r="G32" s="12" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="H32" s="12" t="inlineStr">
+        <is>
+          <t>Women's open</t>
+        </is>
+      </c>
+      <c r="I32" s="12" t="inlineStr"/>
+      <c r="J32" s="14" t="n">
+        <v>8.755000000000001</v>
+      </c>
+      <c r="K32" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="D32" s="12" t="inlineStr">
-        <is>
-          <t>2027 Futures Tour National Championships</t>
-        </is>
-      </c>
-      <c r="E32" s="12" t="inlineStr">
-        <is>
-          <t>California</t>
-        </is>
-      </c>
-      <c r="F32" s="12" t="inlineStr">
-        <is>
-          <t>CA</t>
-        </is>
-      </c>
-      <c r="G32" s="12" t="inlineStr">
-        <is>
-          <t>18U</t>
-        </is>
-      </c>
-      <c r="H32" s="12" t="inlineStr">
-        <is>
-          <t>National junior</t>
-        </is>
-      </c>
-      <c r="I32" s="12" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="J32" s="14" t="n">
-        <v>8.694500000000001</v>
-      </c>
-      <c r="K32" s="13" t="n">
-        <v>6</v>
-      </c>
       <c r="L32" s="15" t="n">
-        <v>15.42857142857143</v>
+        <v>5.25</v>
       </c>
       <c r="M32" s="15" t="n">
-        <v>8.142857142857142</v>
+        <v>0.75</v>
       </c>
       <c r="N32" s="16">
         <f>IFERROR(M32/L32,"")</f>
@@ -2933,30 +2903,30 @@
       <c r="O32" s="12" t="inlineStr"/>
       <c r="P32" s="17" t="inlineStr">
         <is>
-          <t>https://volleyballlife.com/tournament/39825</t>
+          <t>https://cbva.com/venues/1</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="11" t="n">
-        <v>46544</v>
+        <v>46480</v>
       </c>
       <c r="B33" s="12" t="inlineStr">
         <is>
-          <t>projected</t>
+          <t>posted</t>
         </is>
       </c>
       <c r="C33" s="13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D33" s="12" t="inlineStr">
         <is>
-          <t>CBVA women’s open</t>
+          <t>Futures Tour 2X: California</t>
         </is>
       </c>
       <c r="E33" s="12" t="inlineStr">
         <is>
-          <t>Dockweiler, Los Angeles</t>
+          <t>North Beach, Santa Monica</t>
         </is>
       </c>
       <c r="F33" s="12" t="inlineStr">
@@ -2966,49 +2936,41 @@
       </c>
       <c r="G33" s="12" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>18U</t>
         </is>
       </c>
       <c r="H33" s="12" t="inlineStr">
         <is>
-          <t>Women's open</t>
-        </is>
-      </c>
-      <c r="I33" s="12" t="inlineStr"/>
-      <c r="J33" s="14" t="n">
-        <v>8.880000000000001</v>
-      </c>
-      <c r="K33" s="13" t="n">
-        <v>6</v>
-      </c>
-      <c r="L33" s="15" t="n">
-        <v>4.428571428571429</v>
-      </c>
-      <c r="M33" s="15" t="n">
-        <v>2.714285714285714</v>
-      </c>
+          <t>Junior circuit</t>
+        </is>
+      </c>
+      <c r="I33" s="12" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="J33" s="14" t="n"/>
+      <c r="K33" s="13" t="n"/>
+      <c r="L33" s="15" t="n"/>
+      <c r="M33" s="15" t="n"/>
       <c r="N33" s="16">
         <f>IFERROR(M33/L33,"")</f>
         <v/>
       </c>
-      <c r="O33" s="12" t="inlineStr">
-        <is>
-          <t>5 Jun + 6 Jun</t>
-        </is>
-      </c>
+      <c r="O33" s="12" t="inlineStr"/>
       <c r="P33" s="17" t="inlineStr">
         <is>
-          <t>https://cbva.com/venues/1</t>
+          <t>https://volleyballlife.com/tournament/41882</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="11" t="n">
-        <v>46550</v>
+        <v>46495</v>
       </c>
       <c r="B34" s="12" t="inlineStr">
         <is>
-          <t>projected</t>
+          <t>posted</t>
         </is>
       </c>
       <c r="C34" s="13" t="n">
@@ -3016,12 +2978,12 @@
       </c>
       <c r="D34" s="12" t="inlineStr">
         <is>
-          <t>CBVA women’s open</t>
+          <t>p1440 Hermosa Beach Circuit Championships (2X)</t>
         </is>
       </c>
       <c r="E34" s="12" t="inlineStr">
         <is>
-          <t>Mission Beach, San Diego</t>
+          <t>Hermosa Beach Pier</t>
         </is>
       </c>
       <c r="F34" s="12" t="inlineStr">
@@ -3031,26 +2993,26 @@
       </c>
       <c r="G34" s="12" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>18U</t>
         </is>
       </c>
       <c r="H34" s="12" t="inlineStr">
         <is>
-          <t>Women's open</t>
+          <t>Junior circuit</t>
         </is>
       </c>
       <c r="I34" s="12" t="inlineStr"/>
       <c r="J34" s="14" t="n">
-        <v>7.92</v>
+        <v>9.414</v>
       </c>
       <c r="K34" s="13" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="L34" s="15" t="n">
-        <v>4.5</v>
+        <v>5.25</v>
       </c>
       <c r="M34" s="15" t="n">
-        <v>2.333333333333333</v>
+        <v>3.25</v>
       </c>
       <c r="N34" s="16">
         <f>IFERROR(M34/L34,"")</f>
@@ -3059,13 +3021,13 @@
       <c r="O34" s="12" t="inlineStr"/>
       <c r="P34" s="17" t="inlineStr">
         <is>
-          <t>https://cbva.com/venues/15</t>
+          <t>https://volleyballlife.com/tournament/41075</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="11" t="n">
-        <v>46565</v>
+        <v>46488</v>
       </c>
       <c r="B35" s="12" t="inlineStr">
         <is>
@@ -3082,7 +3044,7 @@
       </c>
       <c r="E35" s="12" t="inlineStr">
         <is>
-          <t>Santa Monica Pier, Santa Monica</t>
+          <t>Ocean Park, Santa Monica</t>
         </is>
       </c>
       <c r="F35" s="12" t="inlineStr">
@@ -3102,16 +3064,16 @@
       </c>
       <c r="I35" s="12" t="inlineStr"/>
       <c r="J35" s="14" t="n">
-        <v>9.332000000000001</v>
+        <v>9.015000000000001</v>
       </c>
       <c r="K35" s="13" t="n">
-        <v>22</v>
+        <v>6</v>
       </c>
       <c r="L35" s="15" t="n">
-        <v>3.935483870967742</v>
+        <v>4.266666666666667</v>
       </c>
       <c r="M35" s="15" t="n">
-        <v>2.258064516129032</v>
+        <v>2.866666666666667</v>
       </c>
       <c r="N35" s="16">
         <f>IFERROR(M35/L35,"")</f>
@@ -3120,13 +3082,13 @@
       <c r="O35" s="12" t="inlineStr"/>
       <c r="P35" s="17" t="inlineStr">
         <is>
-          <t>https://cbva.com/venues/17</t>
+          <t>https://cbva.com/venues/7</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="11" t="n">
-        <v>46550</v>
+        <v>46501</v>
       </c>
       <c r="B36" s="12" t="inlineStr">
         <is>
@@ -3163,16 +3125,16 @@
       </c>
       <c r="I36" s="12" t="inlineStr"/>
       <c r="J36" s="14" t="n">
-        <v>9.210000000000001</v>
+        <v>8.885</v>
       </c>
       <c r="K36" s="13" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="L36" s="15" t="n">
-        <v>3.611111111111111</v>
+        <v>3.533333333333333</v>
       </c>
       <c r="M36" s="15" t="n">
-        <v>2</v>
+        <v>1.333333333333333</v>
       </c>
       <c r="N36" s="16">
         <f>IFERROR(M36/L36,"")</f>
@@ -3187,7 +3149,7 @@
     </row>
     <row r="37">
       <c r="A37" s="11" t="n">
-        <v>46544</v>
+        <v>46501</v>
       </c>
       <c r="B37" s="12" t="inlineStr">
         <is>
@@ -3204,7 +3166,7 @@
       </c>
       <c r="E37" s="12" t="inlineStr">
         <is>
-          <t>Ocean Park, Santa Monica</t>
+          <t>Main Beach, Santa Cruz</t>
         </is>
       </c>
       <c r="F37" s="12" t="inlineStr">
@@ -3224,35 +3186,31 @@
       </c>
       <c r="I37" s="12" t="inlineStr"/>
       <c r="J37" s="14" t="n">
-        <v>8.798999999999999</v>
+        <v>7.68</v>
       </c>
       <c r="K37" s="13" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="L37" s="15" t="n">
-        <v>4.375</v>
+        <v>3.666666666666667</v>
       </c>
       <c r="M37" s="15" t="n">
-        <v>1.75</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="N37" s="16">
         <f>IFERROR(M37/L37,"")</f>
         <v/>
       </c>
-      <c r="O37" s="12" t="inlineStr">
-        <is>
-          <t>5 Jun + 6 Jun</t>
-        </is>
-      </c>
+      <c r="O37" s="12" t="inlineStr"/>
       <c r="P37" s="17" t="inlineStr">
         <is>
-          <t>https://cbva.com/venues/7</t>
+          <t>https://cbva.com/venues/8</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="11" t="n">
-        <v>46557</v>
+        <v>46522</v>
       </c>
       <c r="B38" s="12" t="inlineStr">
         <is>
@@ -3269,7 +3227,7 @@
       </c>
       <c r="E38" s="12" t="inlineStr">
         <is>
-          <t>Main Beach, Santa Cruz</t>
+          <t>Ocean Park, Santa Monica</t>
         </is>
       </c>
       <c r="F38" s="12" t="inlineStr">
@@ -3289,48 +3247,52 @@
       </c>
       <c r="I38" s="12" t="inlineStr"/>
       <c r="J38" s="14" t="n">
-        <v>7.668</v>
+        <v>8.757</v>
       </c>
       <c r="K38" s="13" t="n">
         <v>3</v>
       </c>
       <c r="L38" s="15" t="n">
-        <v>5.833333333333333</v>
+        <v>3.777777777777778</v>
       </c>
       <c r="M38" s="15" t="n">
-        <v>0.8333333333333334</v>
+        <v>2</v>
       </c>
       <c r="N38" s="16">
         <f>IFERROR(M38/L38,"")</f>
         <v/>
       </c>
-      <c r="O38" s="12" t="inlineStr"/>
+      <c r="O38" s="12" t="inlineStr">
+        <is>
+          <t>15 May + 16 May</t>
+        </is>
+      </c>
       <c r="P38" s="17" t="inlineStr">
         <is>
-          <t>https://cbva.com/venues/8</t>
+          <t>https://cbva.com/venues/7</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="11" t="n">
-        <v>46574</v>
+        <v>46523</v>
       </c>
       <c r="B39" s="12" t="inlineStr">
         <is>
-          <t>estimated</t>
+          <t>projected</t>
         </is>
       </c>
       <c r="C39" s="13" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D39" s="12" t="inlineStr">
         <is>
-          <t>BVCA Individual Pairs National Championship</t>
+          <t>CBVA women’s open</t>
         </is>
       </c>
       <c r="E39" s="12" t="inlineStr">
         <is>
-          <t>Hermosa Beach</t>
+          <t>Belmont Shore, Long Beach</t>
         </is>
       </c>
       <c r="F39" s="12" t="inlineStr">
@@ -3340,58 +3302,62 @@
       </c>
       <c r="G39" s="12" t="inlineStr">
         <is>
-          <t>18U</t>
+          <t>Open</t>
         </is>
       </c>
       <c r="H39" s="12" t="inlineStr">
         <is>
-          <t>National junior</t>
+          <t>Women's open</t>
         </is>
       </c>
       <c r="I39" s="12" t="inlineStr"/>
       <c r="J39" s="14" t="n">
-        <v>7.49</v>
+        <v>8.757</v>
       </c>
       <c r="K39" s="13" t="n">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="L39" s="15" t="n">
-        <v>17.69230769230769</v>
+        <v>4.25</v>
       </c>
       <c r="M39" s="15" t="n">
-        <v>5.461538461538462</v>
+        <v>1.75</v>
       </c>
       <c r="N39" s="16">
         <f>IFERROR(M39/L39,"")</f>
         <v/>
       </c>
-      <c r="O39" s="12" t="inlineStr"/>
+      <c r="O39" s="12" t="inlineStr">
+        <is>
+          <t>15 May + 16 May</t>
+        </is>
+      </c>
       <c r="P39" s="17" t="inlineStr">
         <is>
-          <t>https://volleyballlife.com/tournament/38087</t>
+          <t>https://cbva.com/venues/3</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="11" t="n">
-        <v>46582</v>
+        <v>46508</v>
       </c>
       <c r="B40" s="12" t="inlineStr">
         <is>
-          <t>posted</t>
+          <t>projected</t>
         </is>
       </c>
       <c r="C40" s="13" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D40" s="12" t="inlineStr">
         <is>
-          <t>34th AAU Hermosa Beach National Pairs Championships</t>
+          <t>CBVA women’s open</t>
         </is>
       </c>
       <c r="E40" s="12" t="inlineStr">
         <is>
-          <t>Hermosa Beach Pier</t>
+          <t>Manhattan Pier, Manhattan Beach</t>
         </is>
       </c>
       <c r="F40" s="12" t="inlineStr">
@@ -3401,26 +3367,26 @@
       </c>
       <c r="G40" s="12" t="inlineStr">
         <is>
-          <t>18U</t>
+          <t>Open</t>
         </is>
       </c>
       <c r="H40" s="12" t="inlineStr">
         <is>
-          <t>National junior</t>
+          <t>Women's open</t>
         </is>
       </c>
       <c r="I40" s="12" t="inlineStr"/>
       <c r="J40" s="14" t="n">
-        <v>8.285</v>
+        <v>8.826000000000001</v>
       </c>
       <c r="K40" s="13" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="L40" s="15" t="n">
-        <v>19.4</v>
+        <v>3.75</v>
       </c>
       <c r="M40" s="15" t="n">
-        <v>7.4</v>
+        <v>1.25</v>
       </c>
       <c r="N40" s="16">
         <f>IFERROR(M40/L40,"")</f>
@@ -3429,63 +3395,59 @@
       <c r="O40" s="12" t="inlineStr"/>
       <c r="P40" s="17" t="inlineStr">
         <is>
-          <t>https://volleyballlife.com/tournament/40248</t>
+          <t>https://cbva.com/venues/2</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="11" t="n">
-        <v>46582</v>
+        <v>46536</v>
       </c>
       <c r="B41" s="12" t="inlineStr">
         <is>
-          <t>posted</t>
+          <t>projected</t>
         </is>
       </c>
       <c r="C41" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="D41" s="12" t="inlineStr">
+        <is>
+          <t>CBVA women’s open</t>
+        </is>
+      </c>
+      <c r="E41" s="12" t="inlineStr">
+        <is>
+          <t>Ocean Beach, San Diego</t>
+        </is>
+      </c>
+      <c r="F41" s="12" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
+      <c r="G41" s="12" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="H41" s="12" t="inlineStr">
+        <is>
+          <t>Women's open</t>
+        </is>
+      </c>
+      <c r="I41" s="12" t="inlineStr"/>
+      <c r="J41" s="14" t="n">
+        <v>7.783</v>
+      </c>
+      <c r="K41" s="13" t="n">
         <v>3</v>
       </c>
-      <c r="D41" s="12" t="inlineStr">
-        <is>
-          <t>34th AAU Hermosa Beach National Pairs Championships</t>
-        </is>
-      </c>
-      <c r="E41" s="12" t="inlineStr">
-        <is>
-          <t>Hermosa Beach Pier</t>
-        </is>
-      </c>
-      <c r="F41" s="12" t="inlineStr">
-        <is>
-          <t>CA</t>
-        </is>
-      </c>
-      <c r="G41" s="12" t="inlineStr">
-        <is>
-          <t>17U</t>
-        </is>
-      </c>
-      <c r="H41" s="12" t="inlineStr">
-        <is>
-          <t>National junior</t>
-        </is>
-      </c>
-      <c r="I41" s="12" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="J41" s="14" t="n">
-        <v>7.0825</v>
-      </c>
-      <c r="K41" s="13" t="n">
-        <v>0</v>
-      </c>
       <c r="L41" s="15" t="n">
-        <v>19.66666666666667</v>
+        <v>3</v>
       </c>
       <c r="M41" s="15" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="N41" s="16">
         <f>IFERROR(M41/L41,"")</f>
@@ -3494,30 +3456,30 @@
       <c r="O41" s="12" t="inlineStr"/>
       <c r="P41" s="17" t="inlineStr">
         <is>
-          <t>https://volleyballlife.com/tournament/40248</t>
+          <t>https://cbva.com/venues/13</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="11" t="n">
-        <v>46589</v>
+        <v>46529</v>
       </c>
       <c r="B42" s="12" t="inlineStr">
         <is>
-          <t>estimated</t>
+          <t>projected</t>
         </is>
       </c>
       <c r="C42" s="13" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D42" s="12" t="inlineStr">
         <is>
-          <t>AVP Juniors National Championships</t>
+          <t>CBVA women’s open</t>
         </is>
       </c>
       <c r="E42" s="12" t="inlineStr">
         <is>
-          <t>Hermosa Beach Pier</t>
+          <t>Hermosa Pier, Hermosa Beach</t>
         </is>
       </c>
       <c r="F42" s="12" t="inlineStr">
@@ -3527,26 +3489,26 @@
       </c>
       <c r="G42" s="12" t="inlineStr">
         <is>
-          <t>18U</t>
+          <t>Open</t>
         </is>
       </c>
       <c r="H42" s="12" t="inlineStr">
         <is>
-          <t>National junior</t>
+          <t>Women's open</t>
         </is>
       </c>
       <c r="I42" s="12" t="inlineStr"/>
       <c r="J42" s="14" t="n">
-        <v>8.503499999999999</v>
+        <v>9.109999999999999</v>
       </c>
       <c r="K42" s="13" t="n">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="L42" s="15" t="n">
-        <v>24.27272727272727</v>
+        <v>2.714285714285714</v>
       </c>
       <c r="M42" s="15" t="n">
-        <v>13.09090909090909</v>
+        <v>0.8571428571428571</v>
       </c>
       <c r="N42" s="16">
         <f>IFERROR(M42/L42,"")</f>
@@ -3555,30 +3517,30 @@
       <c r="O42" s="12" t="inlineStr"/>
       <c r="P42" s="17" t="inlineStr">
         <is>
-          <t>https://volleyballlife.com/tournament/34243</t>
+          <t>https://cbva.com/venues/6</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="11" t="n">
-        <v>46589</v>
+        <v>46529</v>
       </c>
       <c r="B43" s="12" t="inlineStr">
         <is>
-          <t>estimated</t>
+          <t>projected</t>
         </is>
       </c>
       <c r="C43" s="13" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D43" s="12" t="inlineStr">
         <is>
-          <t>AVP Juniors National Championships</t>
+          <t>CBVA women’s open</t>
         </is>
       </c>
       <c r="E43" s="12" t="inlineStr">
         <is>
-          <t>Hermosa Beach Pier</t>
+          <t>Main Beach, Santa Cruz</t>
         </is>
       </c>
       <c r="F43" s="12" t="inlineStr">
@@ -3588,30 +3550,26 @@
       </c>
       <c r="G43" s="12" t="inlineStr">
         <is>
-          <t>17U</t>
+          <t>Open</t>
         </is>
       </c>
       <c r="H43" s="12" t="inlineStr">
         <is>
-          <t>National junior</t>
-        </is>
-      </c>
-      <c r="I43" s="12" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+          <t>Women's open</t>
+        </is>
+      </c>
+      <c r="I43" s="12" t="inlineStr"/>
       <c r="J43" s="14" t="n">
-        <v>7.146000000000001</v>
+        <v>7.668</v>
       </c>
       <c r="K43" s="13" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L43" s="15" t="n">
-        <v>22.5</v>
+        <v>4</v>
       </c>
       <c r="M43" s="15" t="n">
-        <v>7.5</v>
+        <v>0</v>
       </c>
       <c r="N43" s="16">
         <f>IFERROR(M43/L43,"")</f>
@@ -3620,17 +3578,17 @@
       <c r="O43" s="12" t="inlineStr"/>
       <c r="P43" s="17" t="inlineStr">
         <is>
-          <t>https://volleyballlife.com/tournament/34243</t>
+          <t>https://cbva.com/venues/8</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="11" t="n">
-        <v>46592</v>
+        <v>46543</v>
       </c>
       <c r="B44" s="12" t="inlineStr">
         <is>
-          <t>estimated</t>
+          <t>posted</t>
         </is>
       </c>
       <c r="C44" s="13" t="n">
@@ -3638,73 +3596,73 @@
       </c>
       <c r="D44" s="12" t="inlineStr">
         <is>
-          <t>Tahoe Championships — grass, separate rating</t>
+          <t>Kauai Bikini Open</t>
         </is>
       </c>
       <c r="E44" s="12" t="inlineStr">
         <is>
-          <t>Kahle Park, South Lake Tahoe</t>
+          <t>North Beach, Santa Monica</t>
         </is>
       </c>
       <c r="F44" s="12" t="inlineStr">
         <is>
-          <t>NV</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="G44" s="12" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>18U</t>
         </is>
       </c>
       <c r="H44" s="12" t="inlineStr">
         <is>
-          <t>Grass</t>
+          <t>Junior circuit</t>
         </is>
       </c>
       <c r="I44" s="12" t="inlineStr"/>
       <c r="J44" s="14" t="n">
-        <v>7.509</v>
+        <v>6.8205</v>
       </c>
       <c r="K44" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="L44" s="15" t="n">
-        <v>3</v>
-      </c>
-      <c r="M44" s="15" t="n">
         <v>0</v>
       </c>
+      <c r="L44" s="15" t="n"/>
+      <c r="M44" s="15" t="n"/>
       <c r="N44" s="16">
         <f>IFERROR(M44/L44,"")</f>
         <v/>
       </c>
-      <c r="O44" s="12" t="inlineStr"/>
+      <c r="O44" s="12" t="inlineStr">
+        <is>
+          <t>5 Jun + 6 Jun</t>
+        </is>
+      </c>
       <c r="P44" s="17" t="inlineStr">
         <is>
-          <t>https://volleyballlife.com/tournament/30456</t>
+          <t>https://volleyballlife.com/tournament/41127</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="11" t="n">
-        <v>46592</v>
+        <v>46552</v>
       </c>
       <c r="B45" s="12" t="inlineStr">
         <is>
-          <t>projected</t>
+          <t>estimated</t>
         </is>
       </c>
       <c r="C45" s="13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D45" s="12" t="inlineStr">
         <is>
-          <t>CBVA women’s open</t>
+          <t>USAV U19 / U21 Worlds Trials — if the cycle runs</t>
         </is>
       </c>
       <c r="E45" s="12" t="inlineStr">
         <is>
-          <t>Manhattan Pier, Manhattan Beach</t>
+          <t>Hermosa Beach Pier</t>
         </is>
       </c>
       <c r="F45" s="12" t="inlineStr">
@@ -3719,22 +3677,14 @@
       </c>
       <c r="H45" s="12" t="inlineStr">
         <is>
-          <t>Women's open</t>
+          <t>Selection</t>
         </is>
       </c>
       <c r="I45" s="12" t="inlineStr"/>
-      <c r="J45" s="14" t="n">
-        <v>9.1815</v>
-      </c>
-      <c r="K45" s="13" t="n">
-        <v>20</v>
-      </c>
-      <c r="L45" s="15" t="n">
-        <v>5.52</v>
-      </c>
-      <c r="M45" s="15" t="n">
-        <v>3.16</v>
-      </c>
+      <c r="J45" s="14" t="n"/>
+      <c r="K45" s="13" t="n"/>
+      <c r="L45" s="15" t="n"/>
+      <c r="M45" s="15" t="n"/>
       <c r="N45" s="16">
         <f>IFERROR(M45/L45,"")</f>
         <v/>
@@ -3742,30 +3692,30 @@
       <c r="O45" s="12" t="inlineStr"/>
       <c r="P45" s="17" t="inlineStr">
         <is>
-          <t>https://cbva.com/venues/2</t>
+          <t>https://usavolleyball.org/events/</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="11" t="n">
-        <v>46579</v>
+        <v>46566</v>
       </c>
       <c r="B46" s="12" t="inlineStr">
         <is>
-          <t>projected</t>
+          <t>estimated</t>
         </is>
       </c>
       <c r="C46" s="13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D46" s="12" t="inlineStr">
         <is>
-          <t>CBVA women’s open</t>
+          <t>BVCA Pairs West Coast Championships</t>
         </is>
       </c>
       <c r="E46" s="12" t="inlineStr">
         <is>
-          <t>Beach Blvd, Huntington Beach</t>
+          <t>Newland, Huntington Beach</t>
         </is>
       </c>
       <c r="F46" s="12" t="inlineStr">
@@ -3775,26 +3725,26 @@
       </c>
       <c r="G46" s="12" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>18U</t>
         </is>
       </c>
       <c r="H46" s="12" t="inlineStr">
         <is>
-          <t>Women's open</t>
+          <t>Junior circuit</t>
         </is>
       </c>
       <c r="I46" s="12" t="inlineStr"/>
       <c r="J46" s="14" t="n">
-        <v>8.887</v>
+        <v>8.1805</v>
       </c>
       <c r="K46" s="13" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="L46" s="15" t="n">
-        <v>5.133333333333334</v>
+        <v>17.4</v>
       </c>
       <c r="M46" s="15" t="n">
-        <v>2.4</v>
+        <v>8.4</v>
       </c>
       <c r="N46" s="16">
         <f>IFERROR(M46/L46,"")</f>
@@ -3803,30 +3753,30 @@
       <c r="O46" s="12" t="inlineStr"/>
       <c r="P46" s="17" t="inlineStr">
         <is>
-          <t>https://cbva.com/venues/21</t>
+          <t>https://volleyballlife.com/tournament/35588</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="11" t="n">
-        <v>46586</v>
+        <v>46566</v>
       </c>
       <c r="B47" s="12" t="inlineStr">
         <is>
-          <t>projected</t>
+          <t>estimated</t>
         </is>
       </c>
       <c r="C47" s="13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D47" s="12" t="inlineStr">
         <is>
-          <t>CBVA women’s open</t>
+          <t>BVCA Pairs West Coast Championships</t>
         </is>
       </c>
       <c r="E47" s="12" t="inlineStr">
         <is>
-          <t>Ocean Park, Santa Monica</t>
+          <t>Newland, Huntington Beach</t>
         </is>
       </c>
       <c r="F47" s="12" t="inlineStr">
@@ -3836,27 +3786,27 @@
       </c>
       <c r="G47" s="12" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>17U</t>
         </is>
       </c>
       <c r="H47" s="12" t="inlineStr">
         <is>
-          <t>Women's open</t>
-        </is>
-      </c>
-      <c r="I47" s="12" t="inlineStr"/>
+          <t>Junior circuit</t>
+        </is>
+      </c>
+      <c r="I47" s="12" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
       <c r="J47" s="14" t="n">
-        <v>9.269</v>
+        <v>7.398</v>
       </c>
       <c r="K47" s="13" t="n">
-        <v>11</v>
-      </c>
-      <c r="L47" s="15" t="n">
-        <v>4</v>
-      </c>
-      <c r="M47" s="15" t="n">
-        <v>1.958333333333333</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="L47" s="15" t="n"/>
+      <c r="M47" s="15" t="n"/>
       <c r="N47" s="16">
         <f>IFERROR(M47/L47,"")</f>
         <v/>
@@ -3864,30 +3814,30 @@
       <c r="O47" s="12" t="inlineStr"/>
       <c r="P47" s="17" t="inlineStr">
         <is>
-          <t>https://cbva.com/venues/7</t>
+          <t>https://volleyballlife.com/tournament/35588</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="11" t="n">
-        <v>46579</v>
+        <v>46566</v>
       </c>
       <c r="B48" s="12" t="inlineStr">
         <is>
-          <t>projected</t>
+          <t>posted</t>
         </is>
       </c>
       <c r="C48" s="13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D48" s="12" t="inlineStr">
         <is>
-          <t>CBVA women’s open</t>
+          <t>2027 Futures Tour National Championships</t>
         </is>
       </c>
       <c r="E48" s="12" t="inlineStr">
         <is>
-          <t>East Beach, Santa Barbara</t>
+          <t>California</t>
         </is>
       </c>
       <c r="F48" s="12" t="inlineStr">
@@ -3897,26 +3847,30 @@
       </c>
       <c r="G48" s="12" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>18U</t>
         </is>
       </c>
       <c r="H48" s="12" t="inlineStr">
         <is>
-          <t>Women's open</t>
-        </is>
-      </c>
-      <c r="I48" s="12" t="inlineStr"/>
+          <t>National junior</t>
+        </is>
+      </c>
+      <c r="I48" s="12" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
       <c r="J48" s="14" t="n">
-        <v>8.298</v>
+        <v>8.694500000000001</v>
       </c>
       <c r="K48" s="13" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="L48" s="15" t="n">
-        <v>4.555555555555555</v>
+        <v>15.42857142857143</v>
       </c>
       <c r="M48" s="15" t="n">
-        <v>1.333333333333333</v>
+        <v>8.142857142857142</v>
       </c>
       <c r="N48" s="16">
         <f>IFERROR(M48/L48,"")</f>
@@ -3925,13 +3879,13 @@
       <c r="O48" s="12" t="inlineStr"/>
       <c r="P48" s="17" t="inlineStr">
         <is>
-          <t>https://cbva.com/venues/18</t>
+          <t>https://volleyballlife.com/tournament/39825</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="11" t="n">
-        <v>46585</v>
+        <v>46544</v>
       </c>
       <c r="B49" s="12" t="inlineStr">
         <is>
@@ -3948,7 +3902,7 @@
       </c>
       <c r="E49" s="12" t="inlineStr">
         <is>
-          <t>Main Beach, Santa Cruz</t>
+          <t>Dockweiler, Los Angeles</t>
         </is>
       </c>
       <c r="F49" s="12" t="inlineStr">
@@ -3968,48 +3922,52 @@
       </c>
       <c r="I49" s="12" t="inlineStr"/>
       <c r="J49" s="14" t="n">
-        <v>7.8485</v>
+        <v>8.880000000000001</v>
       </c>
       <c r="K49" s="13" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="L49" s="15" t="n">
-        <v>6</v>
+        <v>4.428571428571429</v>
       </c>
       <c r="M49" s="15" t="n">
-        <v>1</v>
+        <v>2.714285714285714</v>
       </c>
       <c r="N49" s="16">
         <f>IFERROR(M49/L49,"")</f>
         <v/>
       </c>
-      <c r="O49" s="12" t="inlineStr"/>
+      <c r="O49" s="12" t="inlineStr">
+        <is>
+          <t>5 Jun + 6 Jun</t>
+        </is>
+      </c>
       <c r="P49" s="17" t="inlineStr">
         <is>
-          <t>https://cbva.com/venues/8</t>
+          <t>https://cbva.com/venues/1</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="11" t="n">
-        <v>46621</v>
+        <v>46550</v>
       </c>
       <c r="B50" s="12" t="inlineStr">
         <is>
-          <t>estimated</t>
+          <t>projected</t>
         </is>
       </c>
       <c r="C50" s="13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D50" s="12" t="inlineStr">
         <is>
-          <t>Super Girl Pro Invitational</t>
+          <t>CBVA women’s open</t>
         </is>
       </c>
       <c r="E50" s="12" t="inlineStr">
         <is>
-          <t>Oceanside Pier</t>
+          <t>Mission Beach, San Diego</t>
         </is>
       </c>
       <c r="F50" s="12" t="inlineStr">
@@ -4019,23 +3977,27 @@
       </c>
       <c r="G50" s="12" t="inlineStr">
         <is>
-          <t>18U</t>
+          <t>Open</t>
         </is>
       </c>
       <c r="H50" s="12" t="inlineStr">
         <is>
-          <t>Junior circuit</t>
+          <t>Women's open</t>
         </is>
       </c>
       <c r="I50" s="12" t="inlineStr"/>
       <c r="J50" s="14" t="n">
-        <v>7.351</v>
+        <v>7.92</v>
       </c>
       <c r="K50" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="L50" s="15" t="n"/>
-      <c r="M50" s="15" t="n"/>
+        <v>3</v>
+      </c>
+      <c r="L50" s="15" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="M50" s="15" t="n">
+        <v>2.333333333333333</v>
+      </c>
       <c r="N50" s="16">
         <f>IFERROR(M50/L50,"")</f>
         <v/>
@@ -4043,13 +4005,13 @@
       <c r="O50" s="12" t="inlineStr"/>
       <c r="P50" s="17" t="inlineStr">
         <is>
-          <t>https://volleyballlife.com/tournament/40465</t>
+          <t>https://cbva.com/venues/15</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="11" t="n">
-        <v>46607</v>
+        <v>46565</v>
       </c>
       <c r="B51" s="12" t="inlineStr">
         <is>
@@ -4066,7 +4028,7 @@
       </c>
       <c r="E51" s="12" t="inlineStr">
         <is>
-          <t>Ocean Park, Santa Monica</t>
+          <t>Santa Monica Pier, Santa Monica</t>
         </is>
       </c>
       <c r="F51" s="12" t="inlineStr">
@@ -4086,16 +4048,16 @@
       </c>
       <c r="I51" s="12" t="inlineStr"/>
       <c r="J51" s="14" t="n">
-        <v>9.487</v>
+        <v>9.332000000000001</v>
       </c>
       <c r="K51" s="13" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="L51" s="15" t="n">
-        <v>3.586206896551724</v>
+        <v>3.935483870967742</v>
       </c>
       <c r="M51" s="15" t="n">
-        <v>1.96551724137931</v>
+        <v>2.258064516129032</v>
       </c>
       <c r="N51" s="16">
         <f>IFERROR(M51/L51,"")</f>
@@ -4104,13 +4066,13 @@
       <c r="O51" s="12" t="inlineStr"/>
       <c r="P51" s="17" t="inlineStr">
         <is>
-          <t>https://cbva.com/venues/7</t>
+          <t>https://cbva.com/venues/17</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="11" t="n">
-        <v>46614</v>
+        <v>46550</v>
       </c>
       <c r="B52" s="12" t="inlineStr">
         <is>
@@ -4127,7 +4089,7 @@
       </c>
       <c r="E52" s="12" t="inlineStr">
         <is>
-          <t>Hermosa Pier, Hermosa Beach</t>
+          <t>Manhattan Pier, Manhattan Beach</t>
         </is>
       </c>
       <c r="F52" s="12" t="inlineStr">
@@ -4147,16 +4109,16 @@
       </c>
       <c r="I52" s="12" t="inlineStr"/>
       <c r="J52" s="14" t="n">
-        <v>9.536</v>
+        <v>9.210000000000001</v>
       </c>
       <c r="K52" s="13" t="n">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="L52" s="15" t="n">
-        <v>4.025</v>
+        <v>3.611111111111111</v>
       </c>
       <c r="M52" s="15" t="n">
-        <v>1.925</v>
+        <v>2</v>
       </c>
       <c r="N52" s="16">
         <f>IFERROR(M52/L52,"")</f>
@@ -4165,13 +4127,13 @@
       <c r="O52" s="12" t="inlineStr"/>
       <c r="P52" s="17" t="inlineStr">
         <is>
-          <t>https://cbva.com/venues/6</t>
+          <t>https://cbva.com/venues/2</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="11" t="n">
-        <v>46613</v>
+        <v>46544</v>
       </c>
       <c r="B53" s="12" t="inlineStr">
         <is>
@@ -4188,7 +4150,7 @@
       </c>
       <c r="E53" s="12" t="inlineStr">
         <is>
-          <t>Main Beach, Santa Cruz</t>
+          <t>Ocean Park, Santa Monica</t>
         </is>
       </c>
       <c r="F53" s="12" t="inlineStr">
@@ -4208,31 +4170,35 @@
       </c>
       <c r="I53" s="12" t="inlineStr"/>
       <c r="J53" s="14" t="n">
-        <v>7.6825</v>
+        <v>8.798999999999999</v>
       </c>
       <c r="K53" s="13" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="L53" s="15" t="n">
-        <v>5.166666666666667</v>
+        <v>4.375</v>
       </c>
       <c r="M53" s="15" t="n">
-        <v>1.166666666666667</v>
+        <v>1.75</v>
       </c>
       <c r="N53" s="16">
         <f>IFERROR(M53/L53,"")</f>
         <v/>
       </c>
-      <c r="O53" s="12" t="inlineStr"/>
+      <c r="O53" s="12" t="inlineStr">
+        <is>
+          <t>5 Jun + 6 Jun</t>
+        </is>
+      </c>
       <c r="P53" s="17" t="inlineStr">
         <is>
-          <t>https://cbva.com/venues/8</t>
+          <t>https://cbva.com/venues/7</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="11" t="n">
-        <v>46620</v>
+        <v>46557</v>
       </c>
       <c r="B54" s="12" t="inlineStr">
         <is>
@@ -4249,7 +4215,7 @@
       </c>
       <c r="E54" s="12" t="inlineStr">
         <is>
-          <t>Ocean Beach, San Diego</t>
+          <t>Main Beach, Santa Cruz</t>
         </is>
       </c>
       <c r="F54" s="12" t="inlineStr">
@@ -4269,16 +4235,16 @@
       </c>
       <c r="I54" s="12" t="inlineStr"/>
       <c r="J54" s="14" t="n">
-        <v>8.145</v>
+        <v>7.668</v>
       </c>
       <c r="K54" s="13" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="L54" s="15" t="n">
-        <v>4</v>
+        <v>5.833333333333333</v>
       </c>
       <c r="M54" s="15" t="n">
-        <v>1.111111111111111</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="N54" s="16">
         <f>IFERROR(M54/L54,"")</f>
@@ -4287,30 +4253,30 @@
       <c r="O54" s="12" t="inlineStr"/>
       <c r="P54" s="17" t="inlineStr">
         <is>
-          <t>https://cbva.com/venues/13</t>
+          <t>https://cbva.com/venues/8</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="11" t="n">
-        <v>46642</v>
+        <v>46574</v>
       </c>
       <c r="B55" s="12" t="inlineStr">
         <is>
-          <t>projected</t>
+          <t>estimated</t>
         </is>
       </c>
       <c r="C55" s="13" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D55" s="12" t="inlineStr">
         <is>
-          <t>CBVA women’s open</t>
+          <t>BVCA Individual Pairs National Championship</t>
         </is>
       </c>
       <c r="E55" s="12" t="inlineStr">
         <is>
-          <t>Ocean Park, Santa Monica</t>
+          <t>Hermosa Beach</t>
         </is>
       </c>
       <c r="F55" s="12" t="inlineStr">
@@ -4320,26 +4286,26 @@
       </c>
       <c r="G55" s="12" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>18U</t>
         </is>
       </c>
       <c r="H55" s="12" t="inlineStr">
         <is>
-          <t>Women's open</t>
+          <t>National junior</t>
         </is>
       </c>
       <c r="I55" s="12" t="inlineStr"/>
       <c r="J55" s="14" t="n">
-        <v>8.936</v>
+        <v>7.49</v>
       </c>
       <c r="K55" s="13" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="L55" s="15" t="n">
-        <v>3.888888888888889</v>
+        <v>17.69230769230769</v>
       </c>
       <c r="M55" s="15" t="n">
-        <v>2.111111111111111</v>
+        <v>5.461538461538462</v>
       </c>
       <c r="N55" s="16">
         <f>IFERROR(M55/L55,"")</f>
@@ -4348,30 +4314,30 @@
       <c r="O55" s="12" t="inlineStr"/>
       <c r="P55" s="17" t="inlineStr">
         <is>
-          <t>https://cbva.com/venues/7</t>
+          <t>https://volleyballlife.com/tournament/38087</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="11" t="n">
-        <v>46635</v>
+        <v>46582</v>
       </c>
       <c r="B56" s="12" t="inlineStr">
         <is>
-          <t>projected</t>
+          <t>posted</t>
         </is>
       </c>
       <c r="C56" s="13" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D56" s="12" t="inlineStr">
         <is>
-          <t>CBVA women’s open</t>
+          <t>34th AAU Hermosa Beach National Pairs Championships</t>
         </is>
       </c>
       <c r="E56" s="12" t="inlineStr">
         <is>
-          <t>Huntington Pier, Huntington Beach</t>
+          <t>Hermosa Beach Pier</t>
         </is>
       </c>
       <c r="F56" s="12" t="inlineStr">
@@ -4381,26 +4347,26 @@
       </c>
       <c r="G56" s="12" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>18U</t>
         </is>
       </c>
       <c r="H56" s="12" t="inlineStr">
         <is>
-          <t>Women's open</t>
+          <t>National junior</t>
         </is>
       </c>
       <c r="I56" s="12" t="inlineStr"/>
       <c r="J56" s="14" t="n">
-        <v>9.334</v>
+        <v>8.285</v>
       </c>
       <c r="K56" s="13" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="L56" s="15" t="n">
-        <v>4.4</v>
+        <v>19.4</v>
       </c>
       <c r="M56" s="15" t="n">
-        <v>2.066666666666667</v>
+        <v>7.4</v>
       </c>
       <c r="N56" s="16">
         <f>IFERROR(M56/L56,"")</f>
@@ -4409,30 +4375,30 @@
       <c r="O56" s="12" t="inlineStr"/>
       <c r="P56" s="17" t="inlineStr">
         <is>
-          <t>https://cbva.com/venues/22</t>
+          <t>https://volleyballlife.com/tournament/40248</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="11" t="n">
-        <v>46641</v>
+        <v>46582</v>
       </c>
       <c r="B57" s="12" t="inlineStr">
         <is>
-          <t>projected</t>
+          <t>posted</t>
         </is>
       </c>
       <c r="C57" s="13" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D57" s="12" t="inlineStr">
         <is>
-          <t>CBVA women’s open</t>
+          <t>34th AAU Hermosa Beach National Pairs Championships</t>
         </is>
       </c>
       <c r="E57" s="12" t="inlineStr">
         <is>
-          <t>Main Beach, Santa Cruz</t>
+          <t>Hermosa Beach Pier</t>
         </is>
       </c>
       <c r="F57" s="12" t="inlineStr">
@@ -4442,26 +4408,30 @@
       </c>
       <c r="G57" s="12" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>17U</t>
         </is>
       </c>
       <c r="H57" s="12" t="inlineStr">
         <is>
-          <t>Women's open</t>
-        </is>
-      </c>
-      <c r="I57" s="12" t="inlineStr"/>
+          <t>National junior</t>
+        </is>
+      </c>
+      <c r="I57" s="12" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
       <c r="J57" s="14" t="n">
-        <v>7.668</v>
+        <v>7.0825</v>
       </c>
       <c r="K57" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L57" s="15" t="n">
-        <v>2.5</v>
+        <v>19.66666666666667</v>
       </c>
       <c r="M57" s="15" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="N57" s="16">
         <f>IFERROR(M57/L57,"")</f>
@@ -4470,13 +4440,13 @@
       <c r="O57" s="12" t="inlineStr"/>
       <c r="P57" s="17" t="inlineStr">
         <is>
-          <t>https://cbva.com/venues/8</t>
+          <t>https://volleyballlife.com/tournament/40248</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="11" t="n">
-        <v>46661</v>
+        <v>46589</v>
       </c>
       <c r="B58" s="12" t="inlineStr">
         <is>
@@ -4484,16 +4454,16 @@
         </is>
       </c>
       <c r="C58" s="13" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D58" s="12" t="inlineStr">
         <is>
-          <t>The Santa Barbara Open (AVP Next)</t>
+          <t>AVP Juniors National Championships</t>
         </is>
       </c>
       <c r="E58" s="12" t="inlineStr">
         <is>
-          <t>East Beach, Santa Barbara</t>
+          <t>Hermosa Beach Pier</t>
         </is>
       </c>
       <c r="F58" s="12" t="inlineStr">
@@ -4503,26 +4473,26 @@
       </c>
       <c r="G58" s="12" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>18U</t>
         </is>
       </c>
       <c r="H58" s="12" t="inlineStr">
         <is>
-          <t>Pro-am open</t>
+          <t>National junior</t>
         </is>
       </c>
       <c r="I58" s="12" t="inlineStr"/>
       <c r="J58" s="14" t="n">
-        <v>9.6455</v>
+        <v>8.503499999999999</v>
       </c>
       <c r="K58" s="13" t="n">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="L58" s="15" t="n">
-        <v>11.33333333333333</v>
+        <v>24.27272727272727</v>
       </c>
       <c r="M58" s="15" t="n">
-        <v>5</v>
+        <v>13.09090909090909</v>
       </c>
       <c r="N58" s="16">
         <f>IFERROR(M58/L58,"")</f>
@@ -4531,30 +4501,30 @@
       <c r="O58" s="12" t="inlineStr"/>
       <c r="P58" s="17" t="inlineStr">
         <is>
-          <t>https://volleyballlife.com/tournament/28899</t>
+          <t>https://volleyballlife.com/tournament/34243</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="11" t="n">
-        <v>46669</v>
+        <v>46589</v>
       </c>
       <c r="B59" s="12" t="inlineStr">
         <is>
-          <t>projected</t>
+          <t>estimated</t>
         </is>
       </c>
       <c r="C59" s="13" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D59" s="12" t="inlineStr">
         <is>
-          <t>CBVA women’s open</t>
+          <t>AVP Juniors National Championships</t>
         </is>
       </c>
       <c r="E59" s="12" t="inlineStr">
         <is>
-          <t>Belmont Shore, Long Beach</t>
+          <t>Hermosa Beach Pier</t>
         </is>
       </c>
       <c r="F59" s="12" t="inlineStr">
@@ -4564,26 +4534,30 @@
       </c>
       <c r="G59" s="12" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>17U</t>
         </is>
       </c>
       <c r="H59" s="12" t="inlineStr">
         <is>
-          <t>Women's open</t>
-        </is>
-      </c>
-      <c r="I59" s="12" t="inlineStr"/>
+          <t>National junior</t>
+        </is>
+      </c>
+      <c r="I59" s="12" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
       <c r="J59" s="14" t="n">
-        <v>8.905000000000001</v>
+        <v>7.146000000000001</v>
       </c>
       <c r="K59" s="13" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L59" s="15" t="n">
-        <v>4.363636363636363</v>
+        <v>22.5</v>
       </c>
       <c r="M59" s="15" t="n">
-        <v>2.727272727272727</v>
+        <v>7.5</v>
       </c>
       <c r="N59" s="16">
         <f>IFERROR(M59/L59,"")</f>
@@ -4592,17 +4566,17 @@
       <c r="O59" s="12" t="inlineStr"/>
       <c r="P59" s="17" t="inlineStr">
         <is>
-          <t>https://cbva.com/venues/3</t>
+          <t>https://volleyballlife.com/tournament/34243</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="11" t="n">
-        <v>46683</v>
+        <v>46592</v>
       </c>
       <c r="B60" s="12" t="inlineStr">
         <is>
-          <t>projected</t>
+          <t>estimated</t>
         </is>
       </c>
       <c r="C60" s="13" t="n">
@@ -4610,17 +4584,17 @@
       </c>
       <c r="D60" s="12" t="inlineStr">
         <is>
-          <t>CBVA women’s open</t>
+          <t>Tahoe Championships — grass, separate rating</t>
         </is>
       </c>
       <c r="E60" s="12" t="inlineStr">
         <is>
-          <t>Main Beach, Santa Cruz</t>
+          <t>Kahle Park, South Lake Tahoe</t>
         </is>
       </c>
       <c r="F60" s="12" t="inlineStr">
         <is>
-          <t>CA</t>
+          <t>NV</t>
         </is>
       </c>
       <c r="G60" s="12" t="inlineStr">
@@ -4630,18 +4604,18 @@
       </c>
       <c r="H60" s="12" t="inlineStr">
         <is>
-          <t>Women's open</t>
+          <t>Grass</t>
         </is>
       </c>
       <c r="I60" s="12" t="inlineStr"/>
       <c r="J60" s="14" t="n">
-        <v>7.573</v>
+        <v>7.509</v>
       </c>
       <c r="K60" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L60" s="15" t="n">
-        <v>4.666666666666667</v>
+        <v>3</v>
       </c>
       <c r="M60" s="15" t="n">
         <v>0</v>
@@ -4653,30 +4627,30 @@
       <c r="O60" s="12" t="inlineStr"/>
       <c r="P60" s="17" t="inlineStr">
         <is>
-          <t>https://cbva.com/venues/8</t>
+          <t>https://volleyballlife.com/tournament/30456</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="11" t="n">
-        <v>46697</v>
+        <v>46592</v>
       </c>
       <c r="B61" s="12" t="inlineStr">
         <is>
-          <t>estimated</t>
+          <t>projected</t>
         </is>
       </c>
       <c r="C61" s="13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D61" s="12" t="inlineStr">
         <is>
-          <t>AVP Juniors West Coast Championships</t>
+          <t>CBVA women’s open</t>
         </is>
       </c>
       <c r="E61" s="12" t="inlineStr">
         <is>
-          <t>Manhattan Beach</t>
+          <t>Manhattan Pier, Manhattan Beach</t>
         </is>
       </c>
       <c r="F61" s="12" t="inlineStr">
@@ -4686,26 +4660,26 @@
       </c>
       <c r="G61" s="12" t="inlineStr">
         <is>
-          <t>18U</t>
+          <t>Open</t>
         </is>
       </c>
       <c r="H61" s="12" t="inlineStr">
         <is>
-          <t>National junior</t>
+          <t>Women's open</t>
         </is>
       </c>
       <c r="I61" s="12" t="inlineStr"/>
       <c r="J61" s="14" t="n">
-        <v>9.5015</v>
+        <v>9.1815</v>
       </c>
       <c r="K61" s="13" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="L61" s="15" t="n">
-        <v>14.66666666666667</v>
+        <v>5.52</v>
       </c>
       <c r="M61" s="15" t="n">
-        <v>7</v>
+        <v>3.16</v>
       </c>
       <c r="N61" s="16">
         <f>IFERROR(M61/L61,"")</f>
@@ -4714,30 +4688,30 @@
       <c r="O61" s="12" t="inlineStr"/>
       <c r="P61" s="17" t="inlineStr">
         <is>
-          <t>https://volleyballlife.com/tournament/25578</t>
+          <t>https://cbva.com/venues/2</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="11" t="n">
-        <v>46697</v>
+        <v>46579</v>
       </c>
       <c r="B62" s="12" t="inlineStr">
         <is>
-          <t>estimated</t>
+          <t>projected</t>
         </is>
       </c>
       <c r="C62" s="13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D62" s="12" t="inlineStr">
         <is>
-          <t>AVP Juniors West Coast Championships</t>
+          <t>CBVA women’s open</t>
         </is>
       </c>
       <c r="E62" s="12" t="inlineStr">
         <is>
-          <t>Manhattan Beach</t>
+          <t>Beach Blvd, Huntington Beach</t>
         </is>
       </c>
       <c r="F62" s="12" t="inlineStr">
@@ -4747,30 +4721,26 @@
       </c>
       <c r="G62" s="12" t="inlineStr">
         <is>
-          <t>17U</t>
+          <t>Open</t>
         </is>
       </c>
       <c r="H62" s="12" t="inlineStr">
         <is>
-          <t>National junior</t>
-        </is>
-      </c>
-      <c r="I62" s="12" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+          <t>Women's open</t>
+        </is>
+      </c>
+      <c r="I62" s="12" t="inlineStr"/>
       <c r="J62" s="14" t="n">
-        <v>7.714</v>
+        <v>8.887</v>
       </c>
       <c r="K62" s="13" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="L62" s="15" t="n">
-        <v>15</v>
+        <v>5.133333333333334</v>
       </c>
       <c r="M62" s="15" t="n">
-        <v>5</v>
+        <v>2.4</v>
       </c>
       <c r="N62" s="16">
         <f>IFERROR(M62/L62,"")</f>
@@ -4779,13 +4749,13 @@
       <c r="O62" s="12" t="inlineStr"/>
       <c r="P62" s="17" t="inlineStr">
         <is>
-          <t>https://volleyballlife.com/tournament/25578</t>
+          <t>https://cbva.com/venues/21</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="11" t="n">
-        <v>46697</v>
+        <v>46586</v>
       </c>
       <c r="B63" s="12" t="inlineStr">
         <is>
@@ -4802,7 +4772,7 @@
       </c>
       <c r="E63" s="12" t="inlineStr">
         <is>
-          <t>Newland, Huntington Beach</t>
+          <t>Ocean Park, Santa Monica</t>
         </is>
       </c>
       <c r="F63" s="12" t="inlineStr">
@@ -4822,16 +4792,16 @@
       </c>
       <c r="I63" s="12" t="inlineStr"/>
       <c r="J63" s="14" t="n">
-        <v>8.769</v>
+        <v>9.269</v>
       </c>
       <c r="K63" s="13" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="L63" s="15" t="n">
-        <v>4.0625</v>
+        <v>4</v>
       </c>
       <c r="M63" s="15" t="n">
-        <v>1.8125</v>
+        <v>1.958333333333333</v>
       </c>
       <c r="N63" s="16">
         <f>IFERROR(M63/L63,"")</f>
@@ -4840,17 +4810,17 @@
       <c r="O63" s="12" t="inlineStr"/>
       <c r="P63" s="17" t="inlineStr">
         <is>
-          <t>https://cbva.com/venues/4</t>
+          <t>https://cbva.com/venues/7</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="11" t="n">
-        <v>46732</v>
+        <v>46579</v>
       </c>
       <c r="B64" s="12" t="inlineStr">
         <is>
-          <t>estimated</t>
+          <t>projected</t>
         </is>
       </c>
       <c r="C64" s="13" t="n">
@@ -4858,38 +4828,42 @@
       </c>
       <c r="D64" s="12" t="inlineStr">
         <is>
-          <t>AVP Winter Las Vegas</t>
+          <t>CBVA women’s open</t>
         </is>
       </c>
       <c r="E64" s="12" t="inlineStr">
         <is>
-          <t>Sunset Park, Las Vegas</t>
+          <t>East Beach, Santa Barbara</t>
         </is>
       </c>
       <c r="F64" s="12" t="inlineStr">
         <is>
-          <t>NV</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="G64" s="12" t="inlineStr">
         <is>
-          <t>18U</t>
+          <t>Open</t>
         </is>
       </c>
       <c r="H64" s="12" t="inlineStr">
         <is>
-          <t>Junior circuit</t>
+          <t>Women's open</t>
         </is>
       </c>
       <c r="I64" s="12" t="inlineStr"/>
       <c r="J64" s="14" t="n">
-        <v>6.2515</v>
+        <v>8.298</v>
       </c>
       <c r="K64" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="L64" s="15" t="n"/>
-      <c r="M64" s="15" t="n"/>
+        <v>9</v>
+      </c>
+      <c r="L64" s="15" t="n">
+        <v>4.555555555555555</v>
+      </c>
+      <c r="M64" s="15" t="n">
+        <v>1.333333333333333</v>
+      </c>
       <c r="N64" s="16">
         <f>IFERROR(M64/L64,"")</f>
         <v/>
@@ -4897,23 +4871,995 @@
       <c r="O64" s="12" t="inlineStr"/>
       <c r="P64" s="17" t="inlineStr">
         <is>
+          <t>https://cbva.com/venues/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="11" t="n">
+        <v>46585</v>
+      </c>
+      <c r="B65" s="12" t="inlineStr">
+        <is>
+          <t>projected</t>
+        </is>
+      </c>
+      <c r="C65" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="D65" s="12" t="inlineStr">
+        <is>
+          <t>CBVA women’s open</t>
+        </is>
+      </c>
+      <c r="E65" s="12" t="inlineStr">
+        <is>
+          <t>Main Beach, Santa Cruz</t>
+        </is>
+      </c>
+      <c r="F65" s="12" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
+      <c r="G65" s="12" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="H65" s="12" t="inlineStr">
+        <is>
+          <t>Women's open</t>
+        </is>
+      </c>
+      <c r="I65" s="12" t="inlineStr"/>
+      <c r="J65" s="14" t="n">
+        <v>7.8485</v>
+      </c>
+      <c r="K65" s="13" t="n">
+        <v>3</v>
+      </c>
+      <c r="L65" s="15" t="n">
+        <v>6</v>
+      </c>
+      <c r="M65" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="N65" s="16">
+        <f>IFERROR(M65/L65,"")</f>
+        <v/>
+      </c>
+      <c r="O65" s="12" t="inlineStr"/>
+      <c r="P65" s="17" t="inlineStr">
+        <is>
+          <t>https://cbva.com/venues/8</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="11" t="n">
+        <v>46621</v>
+      </c>
+      <c r="B66" s="12" t="inlineStr">
+        <is>
+          <t>estimated</t>
+        </is>
+      </c>
+      <c r="C66" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="D66" s="12" t="inlineStr">
+        <is>
+          <t>Super Girl Pro Invitational</t>
+        </is>
+      </c>
+      <c r="E66" s="12" t="inlineStr">
+        <is>
+          <t>Oceanside Pier</t>
+        </is>
+      </c>
+      <c r="F66" s="12" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
+      <c r="G66" s="12" t="inlineStr">
+        <is>
+          <t>18U</t>
+        </is>
+      </c>
+      <c r="H66" s="12" t="inlineStr">
+        <is>
+          <t>Junior circuit</t>
+        </is>
+      </c>
+      <c r="I66" s="12" t="inlineStr"/>
+      <c r="J66" s="14" t="n">
+        <v>7.351</v>
+      </c>
+      <c r="K66" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="L66" s="15" t="n"/>
+      <c r="M66" s="15" t="n"/>
+      <c r="N66" s="16">
+        <f>IFERROR(M66/L66,"")</f>
+        <v/>
+      </c>
+      <c r="O66" s="12" t="inlineStr"/>
+      <c r="P66" s="17" t="inlineStr">
+        <is>
+          <t>https://volleyballlife.com/tournament/40465</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="11" t="n">
+        <v>46607</v>
+      </c>
+      <c r="B67" s="12" t="inlineStr">
+        <is>
+          <t>projected</t>
+        </is>
+      </c>
+      <c r="C67" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="D67" s="12" t="inlineStr">
+        <is>
+          <t>CBVA women’s open</t>
+        </is>
+      </c>
+      <c r="E67" s="12" t="inlineStr">
+        <is>
+          <t>Ocean Park, Santa Monica</t>
+        </is>
+      </c>
+      <c r="F67" s="12" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
+      <c r="G67" s="12" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="H67" s="12" t="inlineStr">
+        <is>
+          <t>Women's open</t>
+        </is>
+      </c>
+      <c r="I67" s="12" t="inlineStr"/>
+      <c r="J67" s="14" t="n">
+        <v>9.487</v>
+      </c>
+      <c r="K67" s="13" t="n">
+        <v>16</v>
+      </c>
+      <c r="L67" s="15" t="n">
+        <v>3.586206896551724</v>
+      </c>
+      <c r="M67" s="15" t="n">
+        <v>1.96551724137931</v>
+      </c>
+      <c r="N67" s="16">
+        <f>IFERROR(M67/L67,"")</f>
+        <v/>
+      </c>
+      <c r="O67" s="12" t="inlineStr"/>
+      <c r="P67" s="17" t="inlineStr">
+        <is>
+          <t>https://cbva.com/venues/7</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="11" t="n">
+        <v>46614</v>
+      </c>
+      <c r="B68" s="12" t="inlineStr">
+        <is>
+          <t>projected</t>
+        </is>
+      </c>
+      <c r="C68" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="D68" s="12" t="inlineStr">
+        <is>
+          <t>CBVA women’s open</t>
+        </is>
+      </c>
+      <c r="E68" s="12" t="inlineStr">
+        <is>
+          <t>Hermosa Pier, Hermosa Beach</t>
+        </is>
+      </c>
+      <c r="F68" s="12" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
+      <c r="G68" s="12" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="H68" s="12" t="inlineStr">
+        <is>
+          <t>Women's open</t>
+        </is>
+      </c>
+      <c r="I68" s="12" t="inlineStr"/>
+      <c r="J68" s="14" t="n">
+        <v>9.536</v>
+      </c>
+      <c r="K68" s="13" t="n">
+        <v>25</v>
+      </c>
+      <c r="L68" s="15" t="n">
+        <v>4.025</v>
+      </c>
+      <c r="M68" s="15" t="n">
+        <v>1.925</v>
+      </c>
+      <c r="N68" s="16">
+        <f>IFERROR(M68/L68,"")</f>
+        <v/>
+      </c>
+      <c r="O68" s="12" t="inlineStr"/>
+      <c r="P68" s="17" t="inlineStr">
+        <is>
+          <t>https://cbva.com/venues/6</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="11" t="n">
+        <v>46613</v>
+      </c>
+      <c r="B69" s="12" t="inlineStr">
+        <is>
+          <t>projected</t>
+        </is>
+      </c>
+      <c r="C69" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="D69" s="12" t="inlineStr">
+        <is>
+          <t>CBVA women’s open</t>
+        </is>
+      </c>
+      <c r="E69" s="12" t="inlineStr">
+        <is>
+          <t>Main Beach, Santa Cruz</t>
+        </is>
+      </c>
+      <c r="F69" s="12" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
+      <c r="G69" s="12" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="H69" s="12" t="inlineStr">
+        <is>
+          <t>Women's open</t>
+        </is>
+      </c>
+      <c r="I69" s="12" t="inlineStr"/>
+      <c r="J69" s="14" t="n">
+        <v>7.6825</v>
+      </c>
+      <c r="K69" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="L69" s="15" t="n">
+        <v>5.166666666666667</v>
+      </c>
+      <c r="M69" s="15" t="n">
+        <v>1.166666666666667</v>
+      </c>
+      <c r="N69" s="16">
+        <f>IFERROR(M69/L69,"")</f>
+        <v/>
+      </c>
+      <c r="O69" s="12" t="inlineStr"/>
+      <c r="P69" s="17" t="inlineStr">
+        <is>
+          <t>https://cbva.com/venues/8</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="11" t="n">
+        <v>46620</v>
+      </c>
+      <c r="B70" s="12" t="inlineStr">
+        <is>
+          <t>projected</t>
+        </is>
+      </c>
+      <c r="C70" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="D70" s="12" t="inlineStr">
+        <is>
+          <t>CBVA women’s open</t>
+        </is>
+      </c>
+      <c r="E70" s="12" t="inlineStr">
+        <is>
+          <t>Ocean Beach, San Diego</t>
+        </is>
+      </c>
+      <c r="F70" s="12" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
+      <c r="G70" s="12" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="H70" s="12" t="inlineStr">
+        <is>
+          <t>Women's open</t>
+        </is>
+      </c>
+      <c r="I70" s="12" t="inlineStr"/>
+      <c r="J70" s="14" t="n">
+        <v>8.145</v>
+      </c>
+      <c r="K70" s="13" t="n">
+        <v>5</v>
+      </c>
+      <c r="L70" s="15" t="n">
+        <v>4</v>
+      </c>
+      <c r="M70" s="15" t="n">
+        <v>1.111111111111111</v>
+      </c>
+      <c r="N70" s="16">
+        <f>IFERROR(M70/L70,"")</f>
+        <v/>
+      </c>
+      <c r="O70" s="12" t="inlineStr"/>
+      <c r="P70" s="17" t="inlineStr">
+        <is>
+          <t>https://cbva.com/venues/13</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="11" t="n">
+        <v>46642</v>
+      </c>
+      <c r="B71" s="12" t="inlineStr">
+        <is>
+          <t>projected</t>
+        </is>
+      </c>
+      <c r="C71" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="D71" s="12" t="inlineStr">
+        <is>
+          <t>CBVA women’s open</t>
+        </is>
+      </c>
+      <c r="E71" s="12" t="inlineStr">
+        <is>
+          <t>Ocean Park, Santa Monica</t>
+        </is>
+      </c>
+      <c r="F71" s="12" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
+      <c r="G71" s="12" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="H71" s="12" t="inlineStr">
+        <is>
+          <t>Women's open</t>
+        </is>
+      </c>
+      <c r="I71" s="12" t="inlineStr"/>
+      <c r="J71" s="14" t="n">
+        <v>8.936</v>
+      </c>
+      <c r="K71" s="13" t="n">
+        <v>6</v>
+      </c>
+      <c r="L71" s="15" t="n">
+        <v>3.888888888888889</v>
+      </c>
+      <c r="M71" s="15" t="n">
+        <v>2.111111111111111</v>
+      </c>
+      <c r="N71" s="16">
+        <f>IFERROR(M71/L71,"")</f>
+        <v/>
+      </c>
+      <c r="O71" s="12" t="inlineStr"/>
+      <c r="P71" s="17" t="inlineStr">
+        <is>
+          <t>https://cbva.com/venues/7</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="11" t="n">
+        <v>46635</v>
+      </c>
+      <c r="B72" s="12" t="inlineStr">
+        <is>
+          <t>projected</t>
+        </is>
+      </c>
+      <c r="C72" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="D72" s="12" t="inlineStr">
+        <is>
+          <t>CBVA women’s open</t>
+        </is>
+      </c>
+      <c r="E72" s="12" t="inlineStr">
+        <is>
+          <t>Huntington Pier, Huntington Beach</t>
+        </is>
+      </c>
+      <c r="F72" s="12" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
+      <c r="G72" s="12" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="H72" s="12" t="inlineStr">
+        <is>
+          <t>Women's open</t>
+        </is>
+      </c>
+      <c r="I72" s="12" t="inlineStr"/>
+      <c r="J72" s="14" t="n">
+        <v>9.334</v>
+      </c>
+      <c r="K72" s="13" t="n">
+        <v>15</v>
+      </c>
+      <c r="L72" s="15" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="M72" s="15" t="n">
+        <v>2.066666666666667</v>
+      </c>
+      <c r="N72" s="16">
+        <f>IFERROR(M72/L72,"")</f>
+        <v/>
+      </c>
+      <c r="O72" s="12" t="inlineStr"/>
+      <c r="P72" s="17" t="inlineStr">
+        <is>
+          <t>https://cbva.com/venues/22</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="11" t="n">
+        <v>46641</v>
+      </c>
+      <c r="B73" s="12" t="inlineStr">
+        <is>
+          <t>projected</t>
+        </is>
+      </c>
+      <c r="C73" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="D73" s="12" t="inlineStr">
+        <is>
+          <t>CBVA women’s open</t>
+        </is>
+      </c>
+      <c r="E73" s="12" t="inlineStr">
+        <is>
+          <t>Main Beach, Santa Cruz</t>
+        </is>
+      </c>
+      <c r="F73" s="12" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
+      <c r="G73" s="12" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="H73" s="12" t="inlineStr">
+        <is>
+          <t>Women's open</t>
+        </is>
+      </c>
+      <c r="I73" s="12" t="inlineStr"/>
+      <c r="J73" s="14" t="n">
+        <v>7.668</v>
+      </c>
+      <c r="K73" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="L73" s="15" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="M73" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="N73" s="16">
+        <f>IFERROR(M73/L73,"")</f>
+        <v/>
+      </c>
+      <c r="O73" s="12" t="inlineStr"/>
+      <c r="P73" s="17" t="inlineStr">
+        <is>
+          <t>https://cbva.com/venues/8</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="11" t="n">
+        <v>46661</v>
+      </c>
+      <c r="B74" s="12" t="inlineStr">
+        <is>
+          <t>estimated</t>
+        </is>
+      </c>
+      <c r="C74" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="D74" s="12" t="inlineStr">
+        <is>
+          <t>The Santa Barbara Open (AVP Next)</t>
+        </is>
+      </c>
+      <c r="E74" s="12" t="inlineStr">
+        <is>
+          <t>East Beach, Santa Barbara</t>
+        </is>
+      </c>
+      <c r="F74" s="12" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
+      <c r="G74" s="12" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="H74" s="12" t="inlineStr">
+        <is>
+          <t>Pro-am open</t>
+        </is>
+      </c>
+      <c r="I74" s="12" t="inlineStr"/>
+      <c r="J74" s="14" t="n">
+        <v>9.6455</v>
+      </c>
+      <c r="K74" s="13" t="n">
+        <v>27</v>
+      </c>
+      <c r="L74" s="15" t="n">
+        <v>11.33333333333333</v>
+      </c>
+      <c r="M74" s="15" t="n">
+        <v>5</v>
+      </c>
+      <c r="N74" s="16">
+        <f>IFERROR(M74/L74,"")</f>
+        <v/>
+      </c>
+      <c r="O74" s="12" t="inlineStr"/>
+      <c r="P74" s="17" t="inlineStr">
+        <is>
+          <t>https://volleyballlife.com/tournament/28899</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="11" t="n">
+        <v>46669</v>
+      </c>
+      <c r="B75" s="12" t="inlineStr">
+        <is>
+          <t>projected</t>
+        </is>
+      </c>
+      <c r="C75" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="D75" s="12" t="inlineStr">
+        <is>
+          <t>CBVA women’s open</t>
+        </is>
+      </c>
+      <c r="E75" s="12" t="inlineStr">
+        <is>
+          <t>Belmont Shore, Long Beach</t>
+        </is>
+      </c>
+      <c r="F75" s="12" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
+      <c r="G75" s="12" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="H75" s="12" t="inlineStr">
+        <is>
+          <t>Women's open</t>
+        </is>
+      </c>
+      <c r="I75" s="12" t="inlineStr"/>
+      <c r="J75" s="14" t="n">
+        <v>8.905000000000001</v>
+      </c>
+      <c r="K75" s="13" t="n">
+        <v>4</v>
+      </c>
+      <c r="L75" s="15" t="n">
+        <v>4.363636363636363</v>
+      </c>
+      <c r="M75" s="15" t="n">
+        <v>2.727272727272727</v>
+      </c>
+      <c r="N75" s="16">
+        <f>IFERROR(M75/L75,"")</f>
+        <v/>
+      </c>
+      <c r="O75" s="12" t="inlineStr"/>
+      <c r="P75" s="17" t="inlineStr">
+        <is>
+          <t>https://cbva.com/venues/3</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="11" t="n">
+        <v>46683</v>
+      </c>
+      <c r="B76" s="12" t="inlineStr">
+        <is>
+          <t>projected</t>
+        </is>
+      </c>
+      <c r="C76" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="D76" s="12" t="inlineStr">
+        <is>
+          <t>CBVA women’s open</t>
+        </is>
+      </c>
+      <c r="E76" s="12" t="inlineStr">
+        <is>
+          <t>Main Beach, Santa Cruz</t>
+        </is>
+      </c>
+      <c r="F76" s="12" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
+      <c r="G76" s="12" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="H76" s="12" t="inlineStr">
+        <is>
+          <t>Women's open</t>
+        </is>
+      </c>
+      <c r="I76" s="12" t="inlineStr"/>
+      <c r="J76" s="14" t="n">
+        <v>7.573</v>
+      </c>
+      <c r="K76" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="L76" s="15" t="n">
+        <v>4.666666666666667</v>
+      </c>
+      <c r="M76" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="N76" s="16">
+        <f>IFERROR(M76/L76,"")</f>
+        <v/>
+      </c>
+      <c r="O76" s="12" t="inlineStr"/>
+      <c r="P76" s="17" t="inlineStr">
+        <is>
+          <t>https://cbva.com/venues/8</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="11" t="n">
+        <v>46697</v>
+      </c>
+      <c r="B77" s="12" t="inlineStr">
+        <is>
+          <t>estimated</t>
+        </is>
+      </c>
+      <c r="C77" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="D77" s="12" t="inlineStr">
+        <is>
+          <t>AVP Juniors West Coast Championships</t>
+        </is>
+      </c>
+      <c r="E77" s="12" t="inlineStr">
+        <is>
+          <t>Manhattan Beach</t>
+        </is>
+      </c>
+      <c r="F77" s="12" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
+      <c r="G77" s="12" t="inlineStr">
+        <is>
+          <t>18U</t>
+        </is>
+      </c>
+      <c r="H77" s="12" t="inlineStr">
+        <is>
+          <t>National junior</t>
+        </is>
+      </c>
+      <c r="I77" s="12" t="inlineStr"/>
+      <c r="J77" s="14" t="n">
+        <v>9.5015</v>
+      </c>
+      <c r="K77" s="13" t="n">
+        <v>17</v>
+      </c>
+      <c r="L77" s="15" t="n">
+        <v>14.66666666666667</v>
+      </c>
+      <c r="M77" s="15" t="n">
+        <v>7</v>
+      </c>
+      <c r="N77" s="16">
+        <f>IFERROR(M77/L77,"")</f>
+        <v/>
+      </c>
+      <c r="O77" s="12" t="inlineStr"/>
+      <c r="P77" s="17" t="inlineStr">
+        <is>
+          <t>https://volleyballlife.com/tournament/25578</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="11" t="n">
+        <v>46697</v>
+      </c>
+      <c r="B78" s="12" t="inlineStr">
+        <is>
+          <t>estimated</t>
+        </is>
+      </c>
+      <c r="C78" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="D78" s="12" t="inlineStr">
+        <is>
+          <t>AVP Juniors West Coast Championships</t>
+        </is>
+      </c>
+      <c r="E78" s="12" t="inlineStr">
+        <is>
+          <t>Manhattan Beach</t>
+        </is>
+      </c>
+      <c r="F78" s="12" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
+      <c r="G78" s="12" t="inlineStr">
+        <is>
+          <t>17U</t>
+        </is>
+      </c>
+      <c r="H78" s="12" t="inlineStr">
+        <is>
+          <t>National junior</t>
+        </is>
+      </c>
+      <c r="I78" s="12" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="J78" s="14" t="n">
+        <v>7.714</v>
+      </c>
+      <c r="K78" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="L78" s="15" t="n">
+        <v>15</v>
+      </c>
+      <c r="M78" s="15" t="n">
+        <v>5</v>
+      </c>
+      <c r="N78" s="16">
+        <f>IFERROR(M78/L78,"")</f>
+        <v/>
+      </c>
+      <c r="O78" s="12" t="inlineStr"/>
+      <c r="P78" s="17" t="inlineStr">
+        <is>
+          <t>https://volleyballlife.com/tournament/25578</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="11" t="n">
+        <v>46697</v>
+      </c>
+      <c r="B79" s="12" t="inlineStr">
+        <is>
+          <t>projected</t>
+        </is>
+      </c>
+      <c r="C79" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="D79" s="12" t="inlineStr">
+        <is>
+          <t>CBVA women’s open</t>
+        </is>
+      </c>
+      <c r="E79" s="12" t="inlineStr">
+        <is>
+          <t>Newland, Huntington Beach</t>
+        </is>
+      </c>
+      <c r="F79" s="12" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
+      <c r="G79" s="12" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="H79" s="12" t="inlineStr">
+        <is>
+          <t>Women's open</t>
+        </is>
+      </c>
+      <c r="I79" s="12" t="inlineStr"/>
+      <c r="J79" s="14" t="n">
+        <v>8.769</v>
+      </c>
+      <c r="K79" s="13" t="n">
+        <v>6</v>
+      </c>
+      <c r="L79" s="15" t="n">
+        <v>4.0625</v>
+      </c>
+      <c r="M79" s="15" t="n">
+        <v>1.8125</v>
+      </c>
+      <c r="N79" s="16">
+        <f>IFERROR(M79/L79,"")</f>
+        <v/>
+      </c>
+      <c r="O79" s="12" t="inlineStr"/>
+      <c r="P79" s="17" t="inlineStr">
+        <is>
+          <t>https://cbva.com/venues/4</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="11" t="n">
+        <v>46732</v>
+      </c>
+      <c r="B80" s="12" t="inlineStr">
+        <is>
+          <t>estimated</t>
+        </is>
+      </c>
+      <c r="C80" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="D80" s="12" t="inlineStr">
+        <is>
+          <t>AVP Winter Las Vegas</t>
+        </is>
+      </c>
+      <c r="E80" s="12" t="inlineStr">
+        <is>
+          <t>Sunset Park, Las Vegas</t>
+        </is>
+      </c>
+      <c r="F80" s="12" t="inlineStr">
+        <is>
+          <t>NV</t>
+        </is>
+      </c>
+      <c r="G80" s="12" t="inlineStr">
+        <is>
+          <t>18U</t>
+        </is>
+      </c>
+      <c r="H80" s="12" t="inlineStr">
+        <is>
+          <t>Junior circuit</t>
+        </is>
+      </c>
+      <c r="I80" s="12" t="inlineStr"/>
+      <c r="J80" s="14" t="n">
+        <v>6.2515</v>
+      </c>
+      <c r="K80" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="L80" s="15" t="n"/>
+      <c r="M80" s="15" t="n"/>
+      <c r="N80" s="16">
+        <f>IFERROR(M80/L80,"")</f>
+        <v/>
+      </c>
+      <c r="O80" s="12" t="inlineStr"/>
+      <c r="P80" s="17" t="inlineStr">
+        <is>
           <t>https://volleyballlife.com/tournament/41138</t>
         </is>
       </c>
     </row>
-    <row r="65"/>
-    <row r="66">
-      <c r="A66" s="9" t="inlineStr">
+    <row r="81"/>
+    <row r="82">
+      <c r="A82" s="9" t="inlineStr">
         <is>
           <t>Date: a posted date is the organiser's; an estimated date is last year's edition moved into 2027; a projected date is a CBVA slot placed by its own history (exact 45% of the time, within a week 91%) -- the page shows those as a month rather than a day, because the day is a projection. Days is how long her own draw runs, counted from the dates her division actually played at the most recent edition, not how long the event around it runs. Field median, above her, sets and contested all describe that most recent edition, not the 2027 one.</t>
         </is>
       </c>
     </row>
-    <row r="67"/>
-    <row r="68"/>
+    <row r="83"/>
+    <row r="84"/>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A66:H68"/>
+    <mergeCell ref="A82:H84"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">
@@ -4928,7 +5874,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L11"/>
+  <dimension ref="A1:L12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -5009,11 +5955,11 @@
     </row>
     <row r="2">
       <c r="A2" s="11" t="n">
-        <v>46424</v>
+        <v>46347</v>
       </c>
       <c r="B2" s="12" t="inlineStr">
         <is>
-          <t>Kauai Bikini Open</t>
+          <t>CBVA women’s open</t>
         </is>
       </c>
       <c r="C2" s="12" t="inlineStr">
@@ -5022,27 +5968,27 @@
         </is>
       </c>
       <c r="D2" s="11" t="n">
-        <v>46425</v>
+        <v>46348</v>
       </c>
       <c r="E2" s="12" t="inlineStr">
         <is>
-          <t>IBVL Winter Nationals (School Event) — ISF trial</t>
+          <t>CBVA women’s open</t>
         </is>
       </c>
       <c r="F2" s="12" t="inlineStr">
         <is>
-          <t>Hermosa Beach Pier</t>
+          <t>Main Beach, Laguna Beach</t>
         </is>
       </c>
       <c r="G2" s="12" t="n">
-        <v>13</v>
+        <v>52</v>
       </c>
       <c r="H2" s="12" t="n">
-        <v>30</v>
+        <v>70</v>
       </c>
       <c r="I2" s="18" t="n"/>
       <c r="J2" s="18" t="n">
-        <v>11</v>
+        <v>5.5</v>
       </c>
       <c r="K2" s="18">
         <f>SUM(I2:J2)</f>
@@ -5056,24 +6002,24 @@
     </row>
     <row r="3">
       <c r="A3" s="11" t="n">
-        <v>46452</v>
+        <v>46424</v>
       </c>
       <c r="B3" s="12" t="inlineStr">
         <is>
-          <t>CBVA women’s open</t>
+          <t>Kauai Bikini Open</t>
         </is>
       </c>
       <c r="C3" s="12" t="inlineStr">
         <is>
-          <t>Manhattan Pier, Manhattan Beach</t>
+          <t>North Beach, Santa Monica</t>
         </is>
       </c>
       <c r="D3" s="11" t="n">
-        <v>46453</v>
+        <v>46425</v>
       </c>
       <c r="E3" s="12" t="inlineStr">
         <is>
-          <t>California IBVL Winter Series Championships (p1440)</t>
+          <t>IBVL Winter Nationals (School Event) — ISF trial</t>
         </is>
       </c>
       <c r="F3" s="12" t="inlineStr">
@@ -5082,16 +6028,14 @@
         </is>
       </c>
       <c r="G3" s="12" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="H3" s="12" t="n">
-        <v>10</v>
-      </c>
-      <c r="I3" s="18" t="n">
-        <v>5.933333333333334</v>
-      </c>
+        <v>30</v>
+      </c>
+      <c r="I3" s="18" t="n"/>
       <c r="J3" s="18" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="K3" s="18">
         <f>SUM(I3:J3)</f>
@@ -5099,13 +6043,13 @@
       </c>
       <c r="L3" s="12" t="inlineStr">
         <is>
-          <t>One posted, one projected</t>
+          <t>Both posted</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="11" t="n">
-        <v>46466</v>
+        <v>46452</v>
       </c>
       <c r="B4" s="12" t="inlineStr">
         <is>
@@ -5114,32 +6058,34 @@
       </c>
       <c r="C4" s="12" t="inlineStr">
         <is>
-          <t>Newland, Huntington Beach</t>
+          <t>Manhattan Pier, Manhattan Beach</t>
         </is>
       </c>
       <c r="D4" s="11" t="n">
-        <v>46467</v>
+        <v>46453</v>
       </c>
       <c r="E4" s="12" t="inlineStr">
         <is>
-          <t>Marine Open (Girls p1440)</t>
+          <t>California IBVL Winter Series Championships (p1440)</t>
         </is>
       </c>
       <c r="F4" s="12" t="inlineStr">
         <is>
-          <t>Manhattan Beach Lifeguard HQ</t>
+          <t>Hermosa Beach Pier</t>
         </is>
       </c>
       <c r="G4" s="12" t="n">
-        <v>33</v>
+        <v>3</v>
       </c>
       <c r="H4" s="12" t="n">
-        <v>45</v>
+        <v>10</v>
       </c>
       <c r="I4" s="18" t="n">
-        <v>3.047619047619047</v>
-      </c>
-      <c r="J4" s="18" t="n"/>
+        <v>5.933333333333334</v>
+      </c>
+      <c r="J4" s="18" t="n">
+        <v>8</v>
+      </c>
       <c r="K4" s="18">
         <f>SUM(I4:J4)</f>
         <v/>
@@ -5152,7 +6098,7 @@
     </row>
     <row r="5">
       <c r="A5" s="11" t="n">
-        <v>46522</v>
+        <v>46466</v>
       </c>
       <c r="B5" s="12" t="inlineStr">
         <is>
@@ -5161,60 +6107,58 @@
       </c>
       <c r="C5" s="12" t="inlineStr">
         <is>
-          <t>Ocean Park, Santa Monica</t>
+          <t>Newland, Huntington Beach</t>
         </is>
       </c>
       <c r="D5" s="11" t="n">
-        <v>46523</v>
+        <v>46467</v>
       </c>
       <c r="E5" s="12" t="inlineStr">
         <is>
-          <t>CBVA women’s open</t>
+          <t>Marine Open (Girls p1440)</t>
         </is>
       </c>
       <c r="F5" s="12" t="inlineStr">
         <is>
-          <t>Belmont Shore, Long Beach</t>
+          <t>Manhattan Beach Lifeguard HQ</t>
         </is>
       </c>
       <c r="G5" s="12" t="n">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="H5" s="12" t="n">
         <v>45</v>
       </c>
       <c r="I5" s="18" t="n">
-        <v>2</v>
-      </c>
-      <c r="J5" s="18" t="n">
-        <v>1.75</v>
-      </c>
+        <v>3.047619047619047</v>
+      </c>
+      <c r="J5" s="18" t="n"/>
       <c r="K5" s="18">
         <f>SUM(I5:J5)</f>
         <v/>
       </c>
       <c r="L5" s="12" t="inlineStr">
         <is>
-          <t>Both projected</t>
+          <t>One posted, one projected</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="11" t="n">
-        <v>46543</v>
+        <v>46522</v>
       </c>
       <c r="B6" s="12" t="inlineStr">
         <is>
-          <t>Kauai Bikini Open</t>
+          <t>CBVA women’s open</t>
         </is>
       </c>
       <c r="C6" s="12" t="inlineStr">
         <is>
-          <t>North Beach, Santa Monica</t>
+          <t>Ocean Park, Santa Monica</t>
         </is>
       </c>
       <c r="D6" s="11" t="n">
-        <v>46544</v>
+        <v>46523</v>
       </c>
       <c r="E6" s="12" t="inlineStr">
         <is>
@@ -5223,18 +6167,20 @@
       </c>
       <c r="F6" s="12" t="inlineStr">
         <is>
-          <t>Dockweiler, Los Angeles</t>
+          <t>Belmont Shore, Long Beach</t>
         </is>
       </c>
       <c r="G6" s="12" t="n">
-        <v>8</v>
+        <v>30</v>
       </c>
       <c r="H6" s="12" t="n">
-        <v>20</v>
-      </c>
-      <c r="I6" s="18" t="n"/>
+        <v>45</v>
+      </c>
+      <c r="I6" s="18" t="n">
+        <v>2</v>
+      </c>
       <c r="J6" s="18" t="n">
-        <v>2.714285714285714</v>
+        <v>1.75</v>
       </c>
       <c r="K6" s="18">
         <f>SUM(I6:J6)</f>
@@ -5242,7 +6188,7 @@
       </c>
       <c r="L6" s="12" t="inlineStr">
         <is>
-          <t>One posted, one projected</t>
+          <t>Both projected</t>
         </is>
       </c>
     </row>
@@ -5270,18 +6216,18 @@
       </c>
       <c r="F7" s="12" t="inlineStr">
         <is>
-          <t>Ocean Park, Santa Monica</t>
+          <t>Dockweiler, Los Angeles</t>
         </is>
       </c>
       <c r="G7" s="12" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="H7" s="12" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="I7" s="18" t="n"/>
       <c r="J7" s="18" t="n">
-        <v>1.75</v>
+        <v>2.714285714285714</v>
       </c>
       <c r="K7" s="18">
         <f>SUM(I7:J7)</f>
@@ -5293,19 +6239,66 @@
         </is>
       </c>
     </row>
-    <row r="8"/>
-    <row r="9">
-      <c r="A9" s="9" t="inlineStr">
+    <row r="8">
+      <c r="A8" s="11" t="n">
+        <v>46543</v>
+      </c>
+      <c r="B8" s="12" t="inlineStr">
+        <is>
+          <t>Kauai Bikini Open</t>
+        </is>
+      </c>
+      <c r="C8" s="12" t="inlineStr">
+        <is>
+          <t>North Beach, Santa Monica</t>
+        </is>
+      </c>
+      <c r="D8" s="11" t="n">
+        <v>46544</v>
+      </c>
+      <c r="E8" s="12" t="inlineStr">
+        <is>
+          <t>CBVA women’s open</t>
+        </is>
+      </c>
+      <c r="F8" s="12" t="inlineStr">
+        <is>
+          <t>Ocean Park, Santa Monica</t>
+        </is>
+      </c>
+      <c r="G8" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="H8" s="12" t="n">
+        <v>5</v>
+      </c>
+      <c r="I8" s="18" t="n"/>
+      <c r="J8" s="18" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="K8" s="18">
+        <f>SUM(I8:J8)</f>
+        <v/>
+      </c>
+      <c r="L8" s="12" t="inlineStr">
+        <is>
+          <t>One posted, one projected</t>
+        </is>
+      </c>
+    </row>
+    <row r="9"/>
+    <row r="10">
+      <c r="A10" s="9" t="inlineStr">
         <is>
           <t>Two one-day draws on the two days of one weekend, within reach of one hotel. A weekend total with a blank beside it is a floor: the corpus carries no bracket for the Kauai Bikini Open or the Marine Open, so their sets are unknown rather than zero. Miles and minutes are approximate road distances read off the map.</t>
         </is>
       </c>
     </row>
-    <row r="10"/>
     <row r="11"/>
+    <row r="12"/>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A9:F11"/>
+    <mergeCell ref="A10:F12"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">

--- a/docs/plan-2027.xlsx
+++ b/docs/plan-2027.xlsx
@@ -255,8 +255,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="SeasonCalendar" displayName="SeasonCalendar" ref="A1:P80" headerRowCount="1">
-  <autoFilter ref="A1:P80"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="SeasonCalendar" displayName="SeasonCalendar" ref="A1:P79" headerRowCount="1">
+  <autoFilter ref="A1:P79"/>
   <tableColumns count="16">
     <tableColumn id="1" name="Date"/>
     <tableColumn id="2" name="Date is"/>
@@ -645,7 +645,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Built 17 October 2026 from the Volleyball Life crawl and CBVA’s tournament database.</t>
+          <t>Built 20 October 2026 from the Volleyball Life crawl and CBVA’s tournament database.</t>
         </is>
       </c>
     </row>
@@ -721,7 +721,7 @@
         </is>
       </c>
       <c r="B8" s="6" t="n">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
@@ -929,7 +929,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P84"/>
+  <dimension ref="A1:P83"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -1997,7 +1997,7 @@
       </c>
       <c r="E18" s="12" t="inlineStr">
         <is>
-          <t>Arizona Athletic Grounds, Phoenix</t>
+          <t>Arizona Athletic Grounds, Mesa</t>
         </is>
       </c>
       <c r="F18" s="12" t="inlineStr">
@@ -2111,7 +2111,7 @@
       </c>
       <c r="E20" s="12" t="inlineStr">
         <is>
-          <t>Arizona Athletic Grounds, Phoenix</t>
+          <t>Arizona Athletic Grounds, Mesa</t>
         </is>
       </c>
       <c r="F20" s="12" t="inlineStr">
@@ -2432,7 +2432,7 @@
       </c>
       <c r="E25" s="12" t="inlineStr">
         <is>
-          <t>Arizona Athletic Grounds, Phoenix</t>
+          <t>Arizona Athletic Grounds, Mesa</t>
         </is>
       </c>
       <c r="F25" s="12" t="inlineStr">
@@ -2529,7 +2529,7 @@
     </row>
     <row r="27">
       <c r="A27" s="11" t="n">
-        <v>46445</v>
+        <v>46453</v>
       </c>
       <c r="B27" s="12" t="inlineStr">
         <is>
@@ -2537,16 +2537,16 @@
         </is>
       </c>
       <c r="C27" s="13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D27" s="12" t="inlineStr">
         <is>
-          <t>Futures Tour 3X: Spring Championships</t>
+          <t>California IBVL Winter Series Championships (p1440)</t>
         </is>
       </c>
       <c r="E27" s="12" t="inlineStr">
         <is>
-          <t>California</t>
+          <t>Hermosa Beach Pier</t>
         </is>
       </c>
       <c r="F27" s="12" t="inlineStr">
@@ -2561,40 +2561,40 @@
       </c>
       <c r="H27" s="12" t="inlineStr">
         <is>
-          <t>National junior</t>
-        </is>
-      </c>
-      <c r="I27" s="12" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+          <t>Junior circuit</t>
+        </is>
+      </c>
+      <c r="I27" s="12" t="inlineStr"/>
       <c r="J27" s="14" t="n">
-        <v>8.7705</v>
+        <v>8.922000000000001</v>
       </c>
       <c r="K27" s="13" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="L27" s="15" t="n">
-        <v>20.57142857142857</v>
+        <v>8.333333333333334</v>
       </c>
       <c r="M27" s="15" t="n">
-        <v>10.5</v>
+        <v>8</v>
       </c>
       <c r="N27" s="16">
         <f>IFERROR(M27/L27,"")</f>
         <v/>
       </c>
-      <c r="O27" s="12" t="inlineStr"/>
+      <c r="O27" s="12" t="inlineStr">
+        <is>
+          <t>6 Mar + 7 Mar</t>
+        </is>
+      </c>
       <c r="P27" s="17" t="inlineStr">
         <is>
-          <t>https://volleyballlife.com/tournament/41709</t>
+          <t>https://volleyballlife.com/tournament/41072</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="11" t="n">
-        <v>46453</v>
+        <v>46467</v>
       </c>
       <c r="B28" s="12" t="inlineStr">
         <is>
@@ -2606,12 +2606,12 @@
       </c>
       <c r="D28" s="12" t="inlineStr">
         <is>
-          <t>California IBVL Winter Series Championships (p1440)</t>
+          <t>Marine Open (Girls p1440)</t>
         </is>
       </c>
       <c r="E28" s="12" t="inlineStr">
         <is>
-          <t>Hermosa Beach Pier</t>
+          <t>Manhattan Beach Lifeguard HQ</t>
         </is>
       </c>
       <c r="F28" s="12" t="inlineStr">
@@ -2630,40 +2630,34 @@
         </is>
       </c>
       <c r="I28" s="12" t="inlineStr"/>
-      <c r="J28" s="14" t="n">
-        <v>8.922000000000001</v>
-      </c>
+      <c r="J28" s="14" t="n"/>
       <c r="K28" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="L28" s="15" t="n">
-        <v>8.333333333333334</v>
-      </c>
-      <c r="M28" s="15" t="n">
-        <v>8</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="L28" s="15" t="n"/>
+      <c r="M28" s="15" t="n"/>
       <c r="N28" s="16">
         <f>IFERROR(M28/L28,"")</f>
         <v/>
       </c>
       <c r="O28" s="12" t="inlineStr">
         <is>
-          <t>6 Mar + 7 Mar</t>
+          <t>20 Mar + 21 Mar</t>
         </is>
       </c>
       <c r="P28" s="17" t="inlineStr">
         <is>
-          <t>https://volleyballlife.com/tournament/41072</t>
+          <t>https://volleyballlife.com/tournament/41074</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="11" t="n">
-        <v>46467</v>
+        <v>46452</v>
       </c>
       <c r="B29" s="12" t="inlineStr">
         <is>
-          <t>posted</t>
+          <t>projected</t>
         </is>
       </c>
       <c r="C29" s="13" t="n">
@@ -2671,12 +2665,12 @@
       </c>
       <c r="D29" s="12" t="inlineStr">
         <is>
-          <t>Marine Open (Girls p1440)</t>
+          <t>CBVA women’s open</t>
         </is>
       </c>
       <c r="E29" s="12" t="inlineStr">
         <is>
-          <t>Manhattan Beach Lifeguard HQ</t>
+          <t>Manhattan Pier, Manhattan Beach</t>
         </is>
       </c>
       <c r="F29" s="12" t="inlineStr">
@@ -2686,39 +2680,45 @@
       </c>
       <c r="G29" s="12" t="inlineStr">
         <is>
-          <t>18U</t>
+          <t>Open</t>
         </is>
       </c>
       <c r="H29" s="12" t="inlineStr">
         <is>
-          <t>Junior circuit</t>
+          <t>Women's open</t>
         </is>
       </c>
       <c r="I29" s="12" t="inlineStr"/>
-      <c r="J29" s="14" t="n"/>
+      <c r="J29" s="14" t="n">
+        <v>9.166499999999999</v>
+      </c>
       <c r="K29" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="L29" s="15" t="n"/>
-      <c r="M29" s="15" t="n"/>
+        <v>6</v>
+      </c>
+      <c r="L29" s="15" t="n">
+        <v>9.266666666666667</v>
+      </c>
+      <c r="M29" s="15" t="n">
+        <v>5.933333333333334</v>
+      </c>
       <c r="N29" s="16">
         <f>IFERROR(M29/L29,"")</f>
         <v/>
       </c>
       <c r="O29" s="12" t="inlineStr">
         <is>
-          <t>20 Mar + 21 Mar</t>
+          <t>6 Mar + 7 Mar</t>
         </is>
       </c>
       <c r="P29" s="17" t="inlineStr">
         <is>
-          <t>https://volleyballlife.com/tournament/41074</t>
+          <t>https://cbva.com/venues/2</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="11" t="n">
-        <v>46452</v>
+        <v>46466</v>
       </c>
       <c r="B30" s="12" t="inlineStr">
         <is>
@@ -2735,7 +2735,7 @@
       </c>
       <c r="E30" s="12" t="inlineStr">
         <is>
-          <t>Manhattan Pier, Manhattan Beach</t>
+          <t>Newland, Huntington Beach</t>
         </is>
       </c>
       <c r="F30" s="12" t="inlineStr">
@@ -2755,16 +2755,16 @@
       </c>
       <c r="I30" s="12" t="inlineStr"/>
       <c r="J30" s="14" t="n">
-        <v>9.166499999999999</v>
+        <v>9.088000000000001</v>
       </c>
       <c r="K30" s="13" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="L30" s="15" t="n">
-        <v>9.266666666666667</v>
+        <v>4.523809523809524</v>
       </c>
       <c r="M30" s="15" t="n">
-        <v>5.933333333333334</v>
+        <v>3.047619047619047</v>
       </c>
       <c r="N30" s="16">
         <f>IFERROR(M30/L30,"")</f>
@@ -2772,18 +2772,18 @@
       </c>
       <c r="O30" s="12" t="inlineStr">
         <is>
-          <t>6 Mar + 7 Mar</t>
+          <t>20 Mar + 21 Mar</t>
         </is>
       </c>
       <c r="P30" s="17" t="inlineStr">
         <is>
-          <t>https://cbva.com/venues/2</t>
+          <t>https://cbva.com/venues/4</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="11" t="n">
-        <v>46466</v>
+        <v>46474</v>
       </c>
       <c r="B31" s="12" t="inlineStr">
         <is>
@@ -2800,7 +2800,7 @@
       </c>
       <c r="E31" s="12" t="inlineStr">
         <is>
-          <t>Newland, Huntington Beach</t>
+          <t>Dockweiler, Los Angeles</t>
         </is>
       </c>
       <c r="F31" s="12" t="inlineStr">
@@ -2820,52 +2820,48 @@
       </c>
       <c r="I31" s="12" t="inlineStr"/>
       <c r="J31" s="14" t="n">
-        <v>9.088000000000001</v>
+        <v>8.755000000000001</v>
       </c>
       <c r="K31" s="13" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="L31" s="15" t="n">
-        <v>4.523809523809524</v>
+        <v>5.25</v>
       </c>
       <c r="M31" s="15" t="n">
-        <v>3.047619047619047</v>
+        <v>0.75</v>
       </c>
       <c r="N31" s="16">
         <f>IFERROR(M31/L31,"")</f>
         <v/>
       </c>
-      <c r="O31" s="12" t="inlineStr">
-        <is>
-          <t>20 Mar + 21 Mar</t>
-        </is>
-      </c>
+      <c r="O31" s="12" t="inlineStr"/>
       <c r="P31" s="17" t="inlineStr">
         <is>
-          <t>https://cbva.com/venues/4</t>
+          <t>https://cbva.com/venues/1</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="11" t="n">
-        <v>46474</v>
+        <v>46480</v>
       </c>
       <c r="B32" s="12" t="inlineStr">
         <is>
-          <t>projected</t>
+          <t>posted</t>
         </is>
       </c>
       <c r="C32" s="13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D32" s="12" t="inlineStr">
         <is>
-          <t>CBVA women’s open</t>
+          <t>Futures Tour 2X: California</t>
         </is>
       </c>
       <c r="E32" s="12" t="inlineStr">
         <is>
-          <t>Dockweiler, Los Angeles</t>
+          <t>North Beach, Santa Monica</t>
         </is>
       </c>
       <c r="F32" s="12" t="inlineStr">
@@ -2875,27 +2871,23 @@
       </c>
       <c r="G32" s="12" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>18U</t>
         </is>
       </c>
       <c r="H32" s="12" t="inlineStr">
         <is>
-          <t>Women's open</t>
-        </is>
-      </c>
-      <c r="I32" s="12" t="inlineStr"/>
-      <c r="J32" s="14" t="n">
-        <v>8.755000000000001</v>
-      </c>
-      <c r="K32" s="13" t="n">
-        <v>2</v>
-      </c>
-      <c r="L32" s="15" t="n">
-        <v>5.25</v>
-      </c>
-      <c r="M32" s="15" t="n">
-        <v>0.75</v>
-      </c>
+          <t>Junior circuit</t>
+        </is>
+      </c>
+      <c r="I32" s="12" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="J32" s="14" t="n"/>
+      <c r="K32" s="13" t="n"/>
+      <c r="L32" s="15" t="n"/>
+      <c r="M32" s="15" t="n"/>
       <c r="N32" s="16">
         <f>IFERROR(M32/L32,"")</f>
         <v/>
@@ -2903,13 +2895,13 @@
       <c r="O32" s="12" t="inlineStr"/>
       <c r="P32" s="17" t="inlineStr">
         <is>
-          <t>https://cbva.com/venues/1</t>
+          <t>https://volleyballlife.com/tournament/41882</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="11" t="n">
-        <v>46480</v>
+        <v>46495</v>
       </c>
       <c r="B33" s="12" t="inlineStr">
         <is>
@@ -2917,16 +2909,16 @@
         </is>
       </c>
       <c r="C33" s="13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D33" s="12" t="inlineStr">
         <is>
-          <t>Futures Tour 2X: California</t>
+          <t>p1440 Hermosa Beach Circuit Championships (2X)</t>
         </is>
       </c>
       <c r="E33" s="12" t="inlineStr">
         <is>
-          <t>North Beach, Santa Monica</t>
+          <t>Hermosa Beach Pier</t>
         </is>
       </c>
       <c r="F33" s="12" t="inlineStr">
@@ -2944,15 +2936,19 @@
           <t>Junior circuit</t>
         </is>
       </c>
-      <c r="I33" s="12" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="J33" s="14" t="n"/>
-      <c r="K33" s="13" t="n"/>
-      <c r="L33" s="15" t="n"/>
-      <c r="M33" s="15" t="n"/>
+      <c r="I33" s="12" t="inlineStr"/>
+      <c r="J33" s="14" t="n">
+        <v>9.414</v>
+      </c>
+      <c r="K33" s="13" t="n">
+        <v>7</v>
+      </c>
+      <c r="L33" s="15" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="M33" s="15" t="n">
+        <v>3.25</v>
+      </c>
       <c r="N33" s="16">
         <f>IFERROR(M33/L33,"")</f>
         <v/>
@@ -2960,17 +2956,17 @@
       <c r="O33" s="12" t="inlineStr"/>
       <c r="P33" s="17" t="inlineStr">
         <is>
-          <t>https://volleyballlife.com/tournament/41882</t>
+          <t>https://volleyballlife.com/tournament/41075</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="11" t="n">
-        <v>46495</v>
+        <v>46488</v>
       </c>
       <c r="B34" s="12" t="inlineStr">
         <is>
-          <t>posted</t>
+          <t>projected</t>
         </is>
       </c>
       <c r="C34" s="13" t="n">
@@ -2978,12 +2974,12 @@
       </c>
       <c r="D34" s="12" t="inlineStr">
         <is>
-          <t>p1440 Hermosa Beach Circuit Championships (2X)</t>
+          <t>CBVA women’s open</t>
         </is>
       </c>
       <c r="E34" s="12" t="inlineStr">
         <is>
-          <t>Hermosa Beach Pier</t>
+          <t>Ocean Park, Santa Monica</t>
         </is>
       </c>
       <c r="F34" s="12" t="inlineStr">
@@ -2993,26 +2989,26 @@
       </c>
       <c r="G34" s="12" t="inlineStr">
         <is>
-          <t>18U</t>
+          <t>Open</t>
         </is>
       </c>
       <c r="H34" s="12" t="inlineStr">
         <is>
-          <t>Junior circuit</t>
+          <t>Women's open</t>
         </is>
       </c>
       <c r="I34" s="12" t="inlineStr"/>
       <c r="J34" s="14" t="n">
-        <v>9.414</v>
+        <v>9.015000000000001</v>
       </c>
       <c r="K34" s="13" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="L34" s="15" t="n">
-        <v>5.25</v>
+        <v>4.266666666666667</v>
       </c>
       <c r="M34" s="15" t="n">
-        <v>3.25</v>
+        <v>2.866666666666667</v>
       </c>
       <c r="N34" s="16">
         <f>IFERROR(M34/L34,"")</f>
@@ -3021,13 +3017,13 @@
       <c r="O34" s="12" t="inlineStr"/>
       <c r="P34" s="17" t="inlineStr">
         <is>
-          <t>https://volleyballlife.com/tournament/41075</t>
+          <t>https://cbva.com/venues/7</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="11" t="n">
-        <v>46488</v>
+        <v>46501</v>
       </c>
       <c r="B35" s="12" t="inlineStr">
         <is>
@@ -3044,7 +3040,7 @@
       </c>
       <c r="E35" s="12" t="inlineStr">
         <is>
-          <t>Ocean Park, Santa Monica</t>
+          <t>Manhattan Pier, Manhattan Beach</t>
         </is>
       </c>
       <c r="F35" s="12" t="inlineStr">
@@ -3064,16 +3060,16 @@
       </c>
       <c r="I35" s="12" t="inlineStr"/>
       <c r="J35" s="14" t="n">
-        <v>9.015000000000001</v>
+        <v>8.885</v>
       </c>
       <c r="K35" s="13" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="L35" s="15" t="n">
-        <v>4.266666666666667</v>
+        <v>3.533333333333333</v>
       </c>
       <c r="M35" s="15" t="n">
-        <v>2.866666666666667</v>
+        <v>1.333333333333333</v>
       </c>
       <c r="N35" s="16">
         <f>IFERROR(M35/L35,"")</f>
@@ -3082,7 +3078,7 @@
       <c r="O35" s="12" t="inlineStr"/>
       <c r="P35" s="17" t="inlineStr">
         <is>
-          <t>https://cbva.com/venues/7</t>
+          <t>https://cbva.com/venues/2</t>
         </is>
       </c>
     </row>
@@ -3105,7 +3101,7 @@
       </c>
       <c r="E36" s="12" t="inlineStr">
         <is>
-          <t>Manhattan Pier, Manhattan Beach</t>
+          <t>Main Beach, Santa Cruz</t>
         </is>
       </c>
       <c r="F36" s="12" t="inlineStr">
@@ -3125,16 +3121,16 @@
       </c>
       <c r="I36" s="12" t="inlineStr"/>
       <c r="J36" s="14" t="n">
-        <v>8.885</v>
+        <v>7.68</v>
       </c>
       <c r="K36" s="13" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="L36" s="15" t="n">
-        <v>3.533333333333333</v>
+        <v>3.666666666666667</v>
       </c>
       <c r="M36" s="15" t="n">
-        <v>1.333333333333333</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="N36" s="16">
         <f>IFERROR(M36/L36,"")</f>
@@ -3143,13 +3139,13 @@
       <c r="O36" s="12" t="inlineStr"/>
       <c r="P36" s="17" t="inlineStr">
         <is>
-          <t>https://cbva.com/venues/2</t>
+          <t>https://cbva.com/venues/8</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="11" t="n">
-        <v>46501</v>
+        <v>46522</v>
       </c>
       <c r="B37" s="12" t="inlineStr">
         <is>
@@ -3166,7 +3162,7 @@
       </c>
       <c r="E37" s="12" t="inlineStr">
         <is>
-          <t>Main Beach, Santa Cruz</t>
+          <t>Ocean Park, Santa Monica</t>
         </is>
       </c>
       <c r="F37" s="12" t="inlineStr">
@@ -3186,31 +3182,35 @@
       </c>
       <c r="I37" s="12" t="inlineStr"/>
       <c r="J37" s="14" t="n">
-        <v>7.68</v>
+        <v>8.757</v>
       </c>
       <c r="K37" s="13" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L37" s="15" t="n">
-        <v>3.666666666666667</v>
+        <v>3.777777777777778</v>
       </c>
       <c r="M37" s="15" t="n">
-        <v>0.6666666666666666</v>
+        <v>2</v>
       </c>
       <c r="N37" s="16">
         <f>IFERROR(M37/L37,"")</f>
         <v/>
       </c>
-      <c r="O37" s="12" t="inlineStr"/>
+      <c r="O37" s="12" t="inlineStr">
+        <is>
+          <t>15 May + 16 May</t>
+        </is>
+      </c>
       <c r="P37" s="17" t="inlineStr">
         <is>
-          <t>https://cbva.com/venues/8</t>
+          <t>https://cbva.com/venues/7</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="11" t="n">
-        <v>46522</v>
+        <v>46523</v>
       </c>
       <c r="B38" s="12" t="inlineStr">
         <is>
@@ -3227,7 +3227,7 @@
       </c>
       <c r="E38" s="12" t="inlineStr">
         <is>
-          <t>Ocean Park, Santa Monica</t>
+          <t>Belmont Shore, Long Beach</t>
         </is>
       </c>
       <c r="F38" s="12" t="inlineStr">
@@ -3250,13 +3250,13 @@
         <v>8.757</v>
       </c>
       <c r="K38" s="13" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L38" s="15" t="n">
-        <v>3.777777777777778</v>
+        <v>4.25</v>
       </c>
       <c r="M38" s="15" t="n">
-        <v>2</v>
+        <v>1.75</v>
       </c>
       <c r="N38" s="16">
         <f>IFERROR(M38/L38,"")</f>
@@ -3269,13 +3269,13 @@
       </c>
       <c r="P38" s="17" t="inlineStr">
         <is>
-          <t>https://cbva.com/venues/7</t>
+          <t>https://cbva.com/venues/3</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="11" t="n">
-        <v>46523</v>
+        <v>46508</v>
       </c>
       <c r="B39" s="12" t="inlineStr">
         <is>
@@ -3292,7 +3292,7 @@
       </c>
       <c r="E39" s="12" t="inlineStr">
         <is>
-          <t>Belmont Shore, Long Beach</t>
+          <t>Manhattan Pier, Manhattan Beach</t>
         </is>
       </c>
       <c r="F39" s="12" t="inlineStr">
@@ -3312,35 +3312,31 @@
       </c>
       <c r="I39" s="12" t="inlineStr"/>
       <c r="J39" s="14" t="n">
-        <v>8.757</v>
+        <v>8.826000000000001</v>
       </c>
       <c r="K39" s="13" t="n">
         <v>4</v>
       </c>
       <c r="L39" s="15" t="n">
-        <v>4.25</v>
+        <v>3.75</v>
       </c>
       <c r="M39" s="15" t="n">
-        <v>1.75</v>
+        <v>1.25</v>
       </c>
       <c r="N39" s="16">
         <f>IFERROR(M39/L39,"")</f>
         <v/>
       </c>
-      <c r="O39" s="12" t="inlineStr">
-        <is>
-          <t>15 May + 16 May</t>
-        </is>
-      </c>
+      <c r="O39" s="12" t="inlineStr"/>
       <c r="P39" s="17" t="inlineStr">
         <is>
-          <t>https://cbva.com/venues/3</t>
+          <t>https://cbva.com/venues/2</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="11" t="n">
-        <v>46508</v>
+        <v>46536</v>
       </c>
       <c r="B40" s="12" t="inlineStr">
         <is>
@@ -3357,7 +3353,7 @@
       </c>
       <c r="E40" s="12" t="inlineStr">
         <is>
-          <t>Manhattan Pier, Manhattan Beach</t>
+          <t>Ocean Beach, San Diego</t>
         </is>
       </c>
       <c r="F40" s="12" t="inlineStr">
@@ -3377,16 +3373,16 @@
       </c>
       <c r="I40" s="12" t="inlineStr"/>
       <c r="J40" s="14" t="n">
-        <v>8.826000000000001</v>
+        <v>7.783</v>
       </c>
       <c r="K40" s="13" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L40" s="15" t="n">
-        <v>3.75</v>
+        <v>3</v>
       </c>
       <c r="M40" s="15" t="n">
-        <v>1.25</v>
+        <v>1</v>
       </c>
       <c r="N40" s="16">
         <f>IFERROR(M40/L40,"")</f>
@@ -3395,13 +3391,13 @@
       <c r="O40" s="12" t="inlineStr"/>
       <c r="P40" s="17" t="inlineStr">
         <is>
-          <t>https://cbva.com/venues/2</t>
+          <t>https://cbva.com/venues/13</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="11" t="n">
-        <v>46536</v>
+        <v>46529</v>
       </c>
       <c r="B41" s="12" t="inlineStr">
         <is>
@@ -3418,7 +3414,7 @@
       </c>
       <c r="E41" s="12" t="inlineStr">
         <is>
-          <t>Ocean Beach, San Diego</t>
+          <t>Hermosa Pier, Hermosa Beach</t>
         </is>
       </c>
       <c r="F41" s="12" t="inlineStr">
@@ -3438,16 +3434,16 @@
       </c>
       <c r="I41" s="12" t="inlineStr"/>
       <c r="J41" s="14" t="n">
-        <v>7.783</v>
+        <v>9.109999999999999</v>
       </c>
       <c r="K41" s="13" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="L41" s="15" t="n">
-        <v>3</v>
+        <v>2.714285714285714</v>
       </c>
       <c r="M41" s="15" t="n">
-        <v>1</v>
+        <v>0.8571428571428571</v>
       </c>
       <c r="N41" s="16">
         <f>IFERROR(M41/L41,"")</f>
@@ -3456,7 +3452,7 @@
       <c r="O41" s="12" t="inlineStr"/>
       <c r="P41" s="17" t="inlineStr">
         <is>
-          <t>https://cbva.com/venues/13</t>
+          <t>https://cbva.com/venues/6</t>
         </is>
       </c>
     </row>
@@ -3479,7 +3475,7 @@
       </c>
       <c r="E42" s="12" t="inlineStr">
         <is>
-          <t>Hermosa Pier, Hermosa Beach</t>
+          <t>Main Beach, Santa Cruz</t>
         </is>
       </c>
       <c r="F42" s="12" t="inlineStr">
@@ -3499,16 +3495,16 @@
       </c>
       <c r="I42" s="12" t="inlineStr"/>
       <c r="J42" s="14" t="n">
-        <v>9.109999999999999</v>
+        <v>7.668</v>
       </c>
       <c r="K42" s="13" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="L42" s="15" t="n">
-        <v>2.714285714285714</v>
+        <v>4</v>
       </c>
       <c r="M42" s="15" t="n">
-        <v>0.8571428571428571</v>
+        <v>0</v>
       </c>
       <c r="N42" s="16">
         <f>IFERROR(M42/L42,"")</f>
@@ -3517,17 +3513,17 @@
       <c r="O42" s="12" t="inlineStr"/>
       <c r="P42" s="17" t="inlineStr">
         <is>
-          <t>https://cbva.com/venues/6</t>
+          <t>https://cbva.com/venues/8</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="11" t="n">
-        <v>46529</v>
+        <v>46543</v>
       </c>
       <c r="B43" s="12" t="inlineStr">
         <is>
-          <t>projected</t>
+          <t>posted</t>
         </is>
       </c>
       <c r="C43" s="13" t="n">
@@ -3535,12 +3531,12 @@
       </c>
       <c r="D43" s="12" t="inlineStr">
         <is>
-          <t>CBVA women’s open</t>
+          <t>Kauai Bikini Open</t>
         </is>
       </c>
       <c r="E43" s="12" t="inlineStr">
         <is>
-          <t>Main Beach, Santa Cruz</t>
+          <t>North Beach, Santa Monica</t>
         </is>
       </c>
       <c r="F43" s="12" t="inlineStr">
@@ -3550,58 +3546,58 @@
       </c>
       <c r="G43" s="12" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>18U</t>
         </is>
       </c>
       <c r="H43" s="12" t="inlineStr">
         <is>
-          <t>Women's open</t>
+          <t>Junior circuit</t>
         </is>
       </c>
       <c r="I43" s="12" t="inlineStr"/>
       <c r="J43" s="14" t="n">
-        <v>7.668</v>
+        <v>6.8205</v>
       </c>
       <c r="K43" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="L43" s="15" t="n">
-        <v>4</v>
-      </c>
-      <c r="M43" s="15" t="n">
         <v>0</v>
       </c>
+      <c r="L43" s="15" t="n"/>
+      <c r="M43" s="15" t="n"/>
       <c r="N43" s="16">
         <f>IFERROR(M43/L43,"")</f>
         <v/>
       </c>
-      <c r="O43" s="12" t="inlineStr"/>
+      <c r="O43" s="12" t="inlineStr">
+        <is>
+          <t>5 Jun + 6 Jun</t>
+        </is>
+      </c>
       <c r="P43" s="17" t="inlineStr">
         <is>
-          <t>https://cbva.com/venues/8</t>
+          <t>https://volleyballlife.com/tournament/41127</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="11" t="n">
-        <v>46543</v>
+        <v>46552</v>
       </c>
       <c r="B44" s="12" t="inlineStr">
         <is>
-          <t>posted</t>
+          <t>estimated</t>
         </is>
       </c>
       <c r="C44" s="13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D44" s="12" t="inlineStr">
         <is>
-          <t>Kauai Bikini Open</t>
+          <t>USAV U19 / U21 Worlds Trials — if the cycle runs</t>
         </is>
       </c>
       <c r="E44" s="12" t="inlineStr">
         <is>
-          <t>North Beach, Santa Monica</t>
+          <t>Hermosa Beach Pier</t>
         </is>
       </c>
       <c r="F44" s="12" t="inlineStr">
@@ -3611,41 +3607,33 @@
       </c>
       <c r="G44" s="12" t="inlineStr">
         <is>
-          <t>18U</t>
+          <t>Open</t>
         </is>
       </c>
       <c r="H44" s="12" t="inlineStr">
         <is>
-          <t>Junior circuit</t>
+          <t>Selection</t>
         </is>
       </c>
       <c r="I44" s="12" t="inlineStr"/>
-      <c r="J44" s="14" t="n">
-        <v>6.8205</v>
-      </c>
-      <c r="K44" s="13" t="n">
-        <v>0</v>
-      </c>
+      <c r="J44" s="14" t="n"/>
+      <c r="K44" s="13" t="n"/>
       <c r="L44" s="15" t="n"/>
       <c r="M44" s="15" t="n"/>
       <c r="N44" s="16">
         <f>IFERROR(M44/L44,"")</f>
         <v/>
       </c>
-      <c r="O44" s="12" t="inlineStr">
-        <is>
-          <t>5 Jun + 6 Jun</t>
-        </is>
-      </c>
+      <c r="O44" s="12" t="inlineStr"/>
       <c r="P44" s="17" t="inlineStr">
         <is>
-          <t>https://volleyballlife.com/tournament/41127</t>
+          <t>https://usavolleyball.org/events/</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="11" t="n">
-        <v>46552</v>
+        <v>46566</v>
       </c>
       <c r="B45" s="12" t="inlineStr">
         <is>
@@ -3657,12 +3645,12 @@
       </c>
       <c r="D45" s="12" t="inlineStr">
         <is>
-          <t>USAV U19 / U21 Worlds Trials — if the cycle runs</t>
+          <t>BVCA Pairs West Coast Championships</t>
         </is>
       </c>
       <c r="E45" s="12" t="inlineStr">
         <is>
-          <t>Hermosa Beach Pier</t>
+          <t>Newland, Huntington Beach</t>
         </is>
       </c>
       <c r="F45" s="12" t="inlineStr">
@@ -3672,19 +3660,27 @@
       </c>
       <c r="G45" s="12" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>18U</t>
         </is>
       </c>
       <c r="H45" s="12" t="inlineStr">
         <is>
-          <t>Selection</t>
+          <t>Junior circuit</t>
         </is>
       </c>
       <c r="I45" s="12" t="inlineStr"/>
-      <c r="J45" s="14" t="n"/>
-      <c r="K45" s="13" t="n"/>
-      <c r="L45" s="15" t="n"/>
-      <c r="M45" s="15" t="n"/>
+      <c r="J45" s="14" t="n">
+        <v>8.1805</v>
+      </c>
+      <c r="K45" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="L45" s="15" t="n">
+        <v>17.4</v>
+      </c>
+      <c r="M45" s="15" t="n">
+        <v>8.4</v>
+      </c>
       <c r="N45" s="16">
         <f>IFERROR(M45/L45,"")</f>
         <v/>
@@ -3692,7 +3688,7 @@
       <c r="O45" s="12" t="inlineStr"/>
       <c r="P45" s="17" t="inlineStr">
         <is>
-          <t>https://usavolleyball.org/events/</t>
+          <t>https://volleyballlife.com/tournament/35588</t>
         </is>
       </c>
     </row>
@@ -3725,7 +3721,7 @@
       </c>
       <c r="G46" s="12" t="inlineStr">
         <is>
-          <t>18U</t>
+          <t>17U</t>
         </is>
       </c>
       <c r="H46" s="12" t="inlineStr">
@@ -3733,19 +3729,19 @@
           <t>Junior circuit</t>
         </is>
       </c>
-      <c r="I46" s="12" t="inlineStr"/>
+      <c r="I46" s="12" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
       <c r="J46" s="14" t="n">
-        <v>8.1805</v>
+        <v>7.398</v>
       </c>
       <c r="K46" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="L46" s="15" t="n">
-        <v>17.4</v>
-      </c>
-      <c r="M46" s="15" t="n">
-        <v>8.4</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="L46" s="15" t="n"/>
+      <c r="M46" s="15" t="n"/>
       <c r="N46" s="16">
         <f>IFERROR(M46/L46,"")</f>
         <v/>
@@ -3763,7 +3759,7 @@
       </c>
       <c r="B47" s="12" t="inlineStr">
         <is>
-          <t>estimated</t>
+          <t>posted</t>
         </is>
       </c>
       <c r="C47" s="13" t="n">
@@ -3771,12 +3767,12 @@
       </c>
       <c r="D47" s="12" t="inlineStr">
         <is>
-          <t>BVCA Pairs West Coast Championships</t>
+          <t>2027 Futures Tour National Championships</t>
         </is>
       </c>
       <c r="E47" s="12" t="inlineStr">
         <is>
-          <t>Newland, Huntington Beach</t>
+          <t>Southern California</t>
         </is>
       </c>
       <c r="F47" s="12" t="inlineStr">
@@ -3786,12 +3782,12 @@
       </c>
       <c r="G47" s="12" t="inlineStr">
         <is>
-          <t>17U</t>
+          <t>18U</t>
         </is>
       </c>
       <c r="H47" s="12" t="inlineStr">
         <is>
-          <t>Junior circuit</t>
+          <t>National junior</t>
         </is>
       </c>
       <c r="I47" s="12" t="inlineStr">
@@ -3800,13 +3796,17 @@
         </is>
       </c>
       <c r="J47" s="14" t="n">
-        <v>7.398</v>
+        <v>8.694500000000001</v>
       </c>
       <c r="K47" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="L47" s="15" t="n"/>
-      <c r="M47" s="15" t="n"/>
+        <v>6</v>
+      </c>
+      <c r="L47" s="15" t="n">
+        <v>15.42857142857143</v>
+      </c>
+      <c r="M47" s="15" t="n">
+        <v>8.142857142857142</v>
+      </c>
       <c r="N47" s="16">
         <f>IFERROR(M47/L47,"")</f>
         <v/>
@@ -3814,30 +3814,30 @@
       <c r="O47" s="12" t="inlineStr"/>
       <c r="P47" s="17" t="inlineStr">
         <is>
-          <t>https://volleyballlife.com/tournament/35588</t>
+          <t>https://volleyballlife.com/tournament/39825</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="11" t="n">
-        <v>46566</v>
+        <v>46544</v>
       </c>
       <c r="B48" s="12" t="inlineStr">
         <is>
-          <t>posted</t>
+          <t>projected</t>
         </is>
       </c>
       <c r="C48" s="13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D48" s="12" t="inlineStr">
         <is>
-          <t>2027 Futures Tour National Championships</t>
+          <t>CBVA women’s open</t>
         </is>
       </c>
       <c r="E48" s="12" t="inlineStr">
         <is>
-          <t>California</t>
+          <t>Dockweiler, Los Angeles</t>
         </is>
       </c>
       <c r="F48" s="12" t="inlineStr">
@@ -3847,45 +3847,45 @@
       </c>
       <c r="G48" s="12" t="inlineStr">
         <is>
-          <t>18U</t>
+          <t>Open</t>
         </is>
       </c>
       <c r="H48" s="12" t="inlineStr">
         <is>
-          <t>National junior</t>
-        </is>
-      </c>
-      <c r="I48" s="12" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+          <t>Women's open</t>
+        </is>
+      </c>
+      <c r="I48" s="12" t="inlineStr"/>
       <c r="J48" s="14" t="n">
-        <v>8.694500000000001</v>
+        <v>8.880000000000001</v>
       </c>
       <c r="K48" s="13" t="n">
         <v>6</v>
       </c>
       <c r="L48" s="15" t="n">
-        <v>15.42857142857143</v>
+        <v>4.428571428571429</v>
       </c>
       <c r="M48" s="15" t="n">
-        <v>8.142857142857142</v>
+        <v>2.714285714285714</v>
       </c>
       <c r="N48" s="16">
         <f>IFERROR(M48/L48,"")</f>
         <v/>
       </c>
-      <c r="O48" s="12" t="inlineStr"/>
+      <c r="O48" s="12" t="inlineStr">
+        <is>
+          <t>5 Jun + 6 Jun</t>
+        </is>
+      </c>
       <c r="P48" s="17" t="inlineStr">
         <is>
-          <t>https://volleyballlife.com/tournament/39825</t>
+          <t>https://cbva.com/venues/1</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="11" t="n">
-        <v>46544</v>
+        <v>46550</v>
       </c>
       <c r="B49" s="12" t="inlineStr">
         <is>
@@ -3902,7 +3902,7 @@
       </c>
       <c r="E49" s="12" t="inlineStr">
         <is>
-          <t>Dockweiler, Los Angeles</t>
+          <t>Mission Beach, San Diego</t>
         </is>
       </c>
       <c r="F49" s="12" t="inlineStr">
@@ -3922,35 +3922,31 @@
       </c>
       <c r="I49" s="12" t="inlineStr"/>
       <c r="J49" s="14" t="n">
-        <v>8.880000000000001</v>
+        <v>7.92</v>
       </c>
       <c r="K49" s="13" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="L49" s="15" t="n">
-        <v>4.428571428571429</v>
+        <v>4.5</v>
       </c>
       <c r="M49" s="15" t="n">
-        <v>2.714285714285714</v>
+        <v>2.333333333333333</v>
       </c>
       <c r="N49" s="16">
         <f>IFERROR(M49/L49,"")</f>
         <v/>
       </c>
-      <c r="O49" s="12" t="inlineStr">
-        <is>
-          <t>5 Jun + 6 Jun</t>
-        </is>
-      </c>
+      <c r="O49" s="12" t="inlineStr"/>
       <c r="P49" s="17" t="inlineStr">
         <is>
-          <t>https://cbva.com/venues/1</t>
+          <t>https://cbva.com/venues/15</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="11" t="n">
-        <v>46550</v>
+        <v>46565</v>
       </c>
       <c r="B50" s="12" t="inlineStr">
         <is>
@@ -3967,7 +3963,7 @@
       </c>
       <c r="E50" s="12" t="inlineStr">
         <is>
-          <t>Mission Beach, San Diego</t>
+          <t>Santa Monica Pier, Santa Monica</t>
         </is>
       </c>
       <c r="F50" s="12" t="inlineStr">
@@ -3987,16 +3983,16 @@
       </c>
       <c r="I50" s="12" t="inlineStr"/>
       <c r="J50" s="14" t="n">
-        <v>7.92</v>
+        <v>9.332000000000001</v>
       </c>
       <c r="K50" s="13" t="n">
-        <v>3</v>
+        <v>22</v>
       </c>
       <c r="L50" s="15" t="n">
-        <v>4.5</v>
+        <v>3.935483870967742</v>
       </c>
       <c r="M50" s="15" t="n">
-        <v>2.333333333333333</v>
+        <v>2.258064516129032</v>
       </c>
       <c r="N50" s="16">
         <f>IFERROR(M50/L50,"")</f>
@@ -4005,13 +4001,13 @@
       <c r="O50" s="12" t="inlineStr"/>
       <c r="P50" s="17" t="inlineStr">
         <is>
-          <t>https://cbva.com/venues/15</t>
+          <t>https://cbva.com/venues/17</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="11" t="n">
-        <v>46565</v>
+        <v>46550</v>
       </c>
       <c r="B51" s="12" t="inlineStr">
         <is>
@@ -4028,7 +4024,7 @@
       </c>
       <c r="E51" s="12" t="inlineStr">
         <is>
-          <t>Santa Monica Pier, Santa Monica</t>
+          <t>Manhattan Pier, Manhattan Beach</t>
         </is>
       </c>
       <c r="F51" s="12" t="inlineStr">
@@ -4048,16 +4044,16 @@
       </c>
       <c r="I51" s="12" t="inlineStr"/>
       <c r="J51" s="14" t="n">
-        <v>9.332000000000001</v>
+        <v>9.210000000000001</v>
       </c>
       <c r="K51" s="13" t="n">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="L51" s="15" t="n">
-        <v>3.935483870967742</v>
+        <v>3.611111111111111</v>
       </c>
       <c r="M51" s="15" t="n">
-        <v>2.258064516129032</v>
+        <v>2</v>
       </c>
       <c r="N51" s="16">
         <f>IFERROR(M51/L51,"")</f>
@@ -4066,13 +4062,13 @@
       <c r="O51" s="12" t="inlineStr"/>
       <c r="P51" s="17" t="inlineStr">
         <is>
-          <t>https://cbva.com/venues/17</t>
+          <t>https://cbva.com/venues/2</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="11" t="n">
-        <v>46550</v>
+        <v>46544</v>
       </c>
       <c r="B52" s="12" t="inlineStr">
         <is>
@@ -4089,7 +4085,7 @@
       </c>
       <c r="E52" s="12" t="inlineStr">
         <is>
-          <t>Manhattan Pier, Manhattan Beach</t>
+          <t>Ocean Park, Santa Monica</t>
         </is>
       </c>
       <c r="F52" s="12" t="inlineStr">
@@ -4109,31 +4105,35 @@
       </c>
       <c r="I52" s="12" t="inlineStr"/>
       <c r="J52" s="14" t="n">
-        <v>9.210000000000001</v>
+        <v>8.798999999999999</v>
       </c>
       <c r="K52" s="13" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="L52" s="15" t="n">
-        <v>3.611111111111111</v>
+        <v>4.375</v>
       </c>
       <c r="M52" s="15" t="n">
-        <v>2</v>
+        <v>1.75</v>
       </c>
       <c r="N52" s="16">
         <f>IFERROR(M52/L52,"")</f>
         <v/>
       </c>
-      <c r="O52" s="12" t="inlineStr"/>
+      <c r="O52" s="12" t="inlineStr">
+        <is>
+          <t>5 Jun + 6 Jun</t>
+        </is>
+      </c>
       <c r="P52" s="17" t="inlineStr">
         <is>
-          <t>https://cbva.com/venues/2</t>
+          <t>https://cbva.com/venues/7</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="11" t="n">
-        <v>46544</v>
+        <v>46557</v>
       </c>
       <c r="B53" s="12" t="inlineStr">
         <is>
@@ -4150,7 +4150,7 @@
       </c>
       <c r="E53" s="12" t="inlineStr">
         <is>
-          <t>Ocean Park, Santa Monica</t>
+          <t>Main Beach, Santa Cruz</t>
         </is>
       </c>
       <c r="F53" s="12" t="inlineStr">
@@ -4170,52 +4170,48 @@
       </c>
       <c r="I53" s="12" t="inlineStr"/>
       <c r="J53" s="14" t="n">
-        <v>8.798999999999999</v>
+        <v>7.668</v>
       </c>
       <c r="K53" s="13" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="L53" s="15" t="n">
-        <v>4.375</v>
+        <v>5.833333333333333</v>
       </c>
       <c r="M53" s="15" t="n">
-        <v>1.75</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="N53" s="16">
         <f>IFERROR(M53/L53,"")</f>
         <v/>
       </c>
-      <c r="O53" s="12" t="inlineStr">
-        <is>
-          <t>5 Jun + 6 Jun</t>
-        </is>
-      </c>
+      <c r="O53" s="12" t="inlineStr"/>
       <c r="P53" s="17" t="inlineStr">
         <is>
-          <t>https://cbva.com/venues/7</t>
+          <t>https://cbva.com/venues/8</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="11" t="n">
-        <v>46557</v>
+        <v>46574</v>
       </c>
       <c r="B54" s="12" t="inlineStr">
         <is>
-          <t>projected</t>
+          <t>estimated</t>
         </is>
       </c>
       <c r="C54" s="13" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D54" s="12" t="inlineStr">
         <is>
-          <t>CBVA women’s open</t>
+          <t>BVCA Individual Pairs National Championship</t>
         </is>
       </c>
       <c r="E54" s="12" t="inlineStr">
         <is>
-          <t>Main Beach, Santa Cruz</t>
+          <t>Hermosa Beach</t>
         </is>
       </c>
       <c r="F54" s="12" t="inlineStr">
@@ -4225,26 +4221,26 @@
       </c>
       <c r="G54" s="12" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>18U</t>
         </is>
       </c>
       <c r="H54" s="12" t="inlineStr">
         <is>
-          <t>Women's open</t>
+          <t>National junior</t>
         </is>
       </c>
       <c r="I54" s="12" t="inlineStr"/>
       <c r="J54" s="14" t="n">
-        <v>7.668</v>
+        <v>7.49</v>
       </c>
       <c r="K54" s="13" t="n">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="L54" s="15" t="n">
-        <v>5.833333333333333</v>
+        <v>17.69230769230769</v>
       </c>
       <c r="M54" s="15" t="n">
-        <v>0.8333333333333334</v>
+        <v>5.461538461538462</v>
       </c>
       <c r="N54" s="16">
         <f>IFERROR(M54/L54,"")</f>
@@ -4253,17 +4249,17 @@
       <c r="O54" s="12" t="inlineStr"/>
       <c r="P54" s="17" t="inlineStr">
         <is>
-          <t>https://cbva.com/venues/8</t>
+          <t>https://volleyballlife.com/tournament/38087</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="11" t="n">
-        <v>46574</v>
+        <v>46582</v>
       </c>
       <c r="B55" s="12" t="inlineStr">
         <is>
-          <t>estimated</t>
+          <t>posted</t>
         </is>
       </c>
       <c r="C55" s="13" t="n">
@@ -4271,12 +4267,12 @@
       </c>
       <c r="D55" s="12" t="inlineStr">
         <is>
-          <t>BVCA Individual Pairs National Championship</t>
+          <t>34th AAU Hermosa Beach National Pairs Championships</t>
         </is>
       </c>
       <c r="E55" s="12" t="inlineStr">
         <is>
-          <t>Hermosa Beach</t>
+          <t>Hermosa Beach Pier</t>
         </is>
       </c>
       <c r="F55" s="12" t="inlineStr">
@@ -4296,16 +4292,16 @@
       </c>
       <c r="I55" s="12" t="inlineStr"/>
       <c r="J55" s="14" t="n">
-        <v>7.49</v>
+        <v>8.285</v>
       </c>
       <c r="K55" s="13" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="L55" s="15" t="n">
-        <v>17.69230769230769</v>
+        <v>19.4</v>
       </c>
       <c r="M55" s="15" t="n">
-        <v>5.461538461538462</v>
+        <v>7.4</v>
       </c>
       <c r="N55" s="16">
         <f>IFERROR(M55/L55,"")</f>
@@ -4314,7 +4310,7 @@
       <c r="O55" s="12" t="inlineStr"/>
       <c r="P55" s="17" t="inlineStr">
         <is>
-          <t>https://volleyballlife.com/tournament/38087</t>
+          <t>https://volleyballlife.com/tournament/40248</t>
         </is>
       </c>
     </row>
@@ -4347,7 +4343,7 @@
       </c>
       <c r="G56" s="12" t="inlineStr">
         <is>
-          <t>18U</t>
+          <t>17U</t>
         </is>
       </c>
       <c r="H56" s="12" t="inlineStr">
@@ -4355,18 +4351,22 @@
           <t>National junior</t>
         </is>
       </c>
-      <c r="I56" s="12" t="inlineStr"/>
+      <c r="I56" s="12" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
       <c r="J56" s="14" t="n">
-        <v>8.285</v>
+        <v>7.0825</v>
       </c>
       <c r="K56" s="13" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="L56" s="15" t="n">
-        <v>19.4</v>
+        <v>19.66666666666667</v>
       </c>
       <c r="M56" s="15" t="n">
-        <v>7.4</v>
+        <v>5</v>
       </c>
       <c r="N56" s="16">
         <f>IFERROR(M56/L56,"")</f>
@@ -4381,11 +4381,11 @@
     </row>
     <row r="57">
       <c r="A57" s="11" t="n">
-        <v>46582</v>
+        <v>46589</v>
       </c>
       <c r="B57" s="12" t="inlineStr">
         <is>
-          <t>posted</t>
+          <t>estimated</t>
         </is>
       </c>
       <c r="C57" s="13" t="n">
@@ -4393,7 +4393,7 @@
       </c>
       <c r="D57" s="12" t="inlineStr">
         <is>
-          <t>34th AAU Hermosa Beach National Pairs Championships</t>
+          <t>AVP Juniors National Championships</t>
         </is>
       </c>
       <c r="E57" s="12" t="inlineStr">
@@ -4408,7 +4408,7 @@
       </c>
       <c r="G57" s="12" t="inlineStr">
         <is>
-          <t>17U</t>
+          <t>18U</t>
         </is>
       </c>
       <c r="H57" s="12" t="inlineStr">
@@ -4416,22 +4416,18 @@
           <t>National junior</t>
         </is>
       </c>
-      <c r="I57" s="12" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="I57" s="12" t="inlineStr"/>
       <c r="J57" s="14" t="n">
-        <v>7.0825</v>
+        <v>8.503499999999999</v>
       </c>
       <c r="K57" s="13" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="L57" s="15" t="n">
-        <v>19.66666666666667</v>
+        <v>24.27272727272727</v>
       </c>
       <c r="M57" s="15" t="n">
-        <v>5</v>
+        <v>13.09090909090909</v>
       </c>
       <c r="N57" s="16">
         <f>IFERROR(M57/L57,"")</f>
@@ -4440,7 +4436,7 @@
       <c r="O57" s="12" t="inlineStr"/>
       <c r="P57" s="17" t="inlineStr">
         <is>
-          <t>https://volleyballlife.com/tournament/40248</t>
+          <t>https://volleyballlife.com/tournament/34243</t>
         </is>
       </c>
     </row>
@@ -4473,7 +4469,7 @@
       </c>
       <c r="G58" s="12" t="inlineStr">
         <is>
-          <t>18U</t>
+          <t>17U</t>
         </is>
       </c>
       <c r="H58" s="12" t="inlineStr">
@@ -4481,18 +4477,22 @@
           <t>National junior</t>
         </is>
       </c>
-      <c r="I58" s="12" t="inlineStr"/>
+      <c r="I58" s="12" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
       <c r="J58" s="14" t="n">
-        <v>8.503499999999999</v>
+        <v>7.146000000000001</v>
       </c>
       <c r="K58" s="13" t="n">
-        <v>18</v>
+        <v>3</v>
       </c>
       <c r="L58" s="15" t="n">
-        <v>24.27272727272727</v>
+        <v>22.5</v>
       </c>
       <c r="M58" s="15" t="n">
-        <v>13.09090909090909</v>
+        <v>7.5</v>
       </c>
       <c r="N58" s="16">
         <f>IFERROR(M58/L58,"")</f>
@@ -4507,7 +4507,7 @@
     </row>
     <row r="59">
       <c r="A59" s="11" t="n">
-        <v>46589</v>
+        <v>46592</v>
       </c>
       <c r="B59" s="12" t="inlineStr">
         <is>
@@ -4515,49 +4515,45 @@
         </is>
       </c>
       <c r="C59" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="D59" s="12" t="inlineStr">
+        <is>
+          <t>Tahoe Championships — grass, separate rating</t>
+        </is>
+      </c>
+      <c r="E59" s="12" t="inlineStr">
+        <is>
+          <t>Kahle Park, South Lake Tahoe</t>
+        </is>
+      </c>
+      <c r="F59" s="12" t="inlineStr">
+        <is>
+          <t>NV</t>
+        </is>
+      </c>
+      <c r="G59" s="12" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="H59" s="12" t="inlineStr">
+        <is>
+          <t>Grass</t>
+        </is>
+      </c>
+      <c r="I59" s="12" t="inlineStr"/>
+      <c r="J59" s="14" t="n">
+        <v>7.509</v>
+      </c>
+      <c r="K59" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="L59" s="15" t="n">
         <v>3</v>
       </c>
-      <c r="D59" s="12" t="inlineStr">
-        <is>
-          <t>AVP Juniors National Championships</t>
-        </is>
-      </c>
-      <c r="E59" s="12" t="inlineStr">
-        <is>
-          <t>Hermosa Beach Pier</t>
-        </is>
-      </c>
-      <c r="F59" s="12" t="inlineStr">
-        <is>
-          <t>CA</t>
-        </is>
-      </c>
-      <c r="G59" s="12" t="inlineStr">
-        <is>
-          <t>17U</t>
-        </is>
-      </c>
-      <c r="H59" s="12" t="inlineStr">
-        <is>
-          <t>National junior</t>
-        </is>
-      </c>
-      <c r="I59" s="12" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="J59" s="14" t="n">
-        <v>7.146000000000001</v>
-      </c>
-      <c r="K59" s="13" t="n">
-        <v>3</v>
-      </c>
-      <c r="L59" s="15" t="n">
-        <v>22.5</v>
-      </c>
       <c r="M59" s="15" t="n">
-        <v>7.5</v>
+        <v>0</v>
       </c>
       <c r="N59" s="16">
         <f>IFERROR(M59/L59,"")</f>
@@ -4566,7 +4562,7 @@
       <c r="O59" s="12" t="inlineStr"/>
       <c r="P59" s="17" t="inlineStr">
         <is>
-          <t>https://volleyballlife.com/tournament/34243</t>
+          <t>https://volleyballlife.com/tournament/30456</t>
         </is>
       </c>
     </row>
@@ -4576,7 +4572,7 @@
       </c>
       <c r="B60" s="12" t="inlineStr">
         <is>
-          <t>estimated</t>
+          <t>projected</t>
         </is>
       </c>
       <c r="C60" s="13" t="n">
@@ -4584,17 +4580,17 @@
       </c>
       <c r="D60" s="12" t="inlineStr">
         <is>
-          <t>Tahoe Championships — grass, separate rating</t>
+          <t>CBVA women’s open</t>
         </is>
       </c>
       <c r="E60" s="12" t="inlineStr">
         <is>
-          <t>Kahle Park, South Lake Tahoe</t>
+          <t>Manhattan Pier, Manhattan Beach</t>
         </is>
       </c>
       <c r="F60" s="12" t="inlineStr">
         <is>
-          <t>NV</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="G60" s="12" t="inlineStr">
@@ -4604,21 +4600,21 @@
       </c>
       <c r="H60" s="12" t="inlineStr">
         <is>
-          <t>Grass</t>
+          <t>Women's open</t>
         </is>
       </c>
       <c r="I60" s="12" t="inlineStr"/>
       <c r="J60" s="14" t="n">
-        <v>7.509</v>
+        <v>9.1815</v>
       </c>
       <c r="K60" s="13" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="L60" s="15" t="n">
-        <v>3</v>
+        <v>5.52</v>
       </c>
       <c r="M60" s="15" t="n">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="N60" s="16">
         <f>IFERROR(M60/L60,"")</f>
@@ -4627,13 +4623,13 @@
       <c r="O60" s="12" t="inlineStr"/>
       <c r="P60" s="17" t="inlineStr">
         <is>
-          <t>https://volleyballlife.com/tournament/30456</t>
+          <t>https://cbva.com/venues/2</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="11" t="n">
-        <v>46592</v>
+        <v>46579</v>
       </c>
       <c r="B61" s="12" t="inlineStr">
         <is>
@@ -4650,7 +4646,7 @@
       </c>
       <c r="E61" s="12" t="inlineStr">
         <is>
-          <t>Manhattan Pier, Manhattan Beach</t>
+          <t>Beach Blvd, Huntington Beach</t>
         </is>
       </c>
       <c r="F61" s="12" t="inlineStr">
@@ -4670,16 +4666,16 @@
       </c>
       <c r="I61" s="12" t="inlineStr"/>
       <c r="J61" s="14" t="n">
-        <v>9.1815</v>
+        <v>8.887</v>
       </c>
       <c r="K61" s="13" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="L61" s="15" t="n">
-        <v>5.52</v>
+        <v>5.133333333333334</v>
       </c>
       <c r="M61" s="15" t="n">
-        <v>3.16</v>
+        <v>2.4</v>
       </c>
       <c r="N61" s="16">
         <f>IFERROR(M61/L61,"")</f>
@@ -4688,13 +4684,13 @@
       <c r="O61" s="12" t="inlineStr"/>
       <c r="P61" s="17" t="inlineStr">
         <is>
-          <t>https://cbva.com/venues/2</t>
+          <t>https://cbva.com/venues/21</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="11" t="n">
-        <v>46579</v>
+        <v>46586</v>
       </c>
       <c r="B62" s="12" t="inlineStr">
         <is>
@@ -4711,7 +4707,7 @@
       </c>
       <c r="E62" s="12" t="inlineStr">
         <is>
-          <t>Beach Blvd, Huntington Beach</t>
+          <t>Ocean Park, Santa Monica</t>
         </is>
       </c>
       <c r="F62" s="12" t="inlineStr">
@@ -4731,16 +4727,16 @@
       </c>
       <c r="I62" s="12" t="inlineStr"/>
       <c r="J62" s="14" t="n">
-        <v>8.887</v>
+        <v>9.269</v>
       </c>
       <c r="K62" s="13" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="L62" s="15" t="n">
-        <v>5.133333333333334</v>
+        <v>4</v>
       </c>
       <c r="M62" s="15" t="n">
-        <v>2.4</v>
+        <v>1.958333333333333</v>
       </c>
       <c r="N62" s="16">
         <f>IFERROR(M62/L62,"")</f>
@@ -4749,13 +4745,13 @@
       <c r="O62" s="12" t="inlineStr"/>
       <c r="P62" s="17" t="inlineStr">
         <is>
-          <t>https://cbva.com/venues/21</t>
+          <t>https://cbva.com/venues/7</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="11" t="n">
-        <v>46586</v>
+        <v>46579</v>
       </c>
       <c r="B63" s="12" t="inlineStr">
         <is>
@@ -4772,7 +4768,7 @@
       </c>
       <c r="E63" s="12" t="inlineStr">
         <is>
-          <t>Ocean Park, Santa Monica</t>
+          <t>East Beach, Santa Barbara</t>
         </is>
       </c>
       <c r="F63" s="12" t="inlineStr">
@@ -4792,16 +4788,16 @@
       </c>
       <c r="I63" s="12" t="inlineStr"/>
       <c r="J63" s="14" t="n">
-        <v>9.269</v>
+        <v>8.298</v>
       </c>
       <c r="K63" s="13" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="L63" s="15" t="n">
-        <v>4</v>
+        <v>4.555555555555555</v>
       </c>
       <c r="M63" s="15" t="n">
-        <v>1.958333333333333</v>
+        <v>1.333333333333333</v>
       </c>
       <c r="N63" s="16">
         <f>IFERROR(M63/L63,"")</f>
@@ -4810,13 +4806,13 @@
       <c r="O63" s="12" t="inlineStr"/>
       <c r="P63" s="17" t="inlineStr">
         <is>
-          <t>https://cbva.com/venues/7</t>
+          <t>https://cbva.com/venues/18</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="11" t="n">
-        <v>46579</v>
+        <v>46585</v>
       </c>
       <c r="B64" s="12" t="inlineStr">
         <is>
@@ -4833,7 +4829,7 @@
       </c>
       <c r="E64" s="12" t="inlineStr">
         <is>
-          <t>East Beach, Santa Barbara</t>
+          <t>Main Beach, Santa Cruz</t>
         </is>
       </c>
       <c r="F64" s="12" t="inlineStr">
@@ -4853,16 +4849,16 @@
       </c>
       <c r="I64" s="12" t="inlineStr"/>
       <c r="J64" s="14" t="n">
-        <v>8.298</v>
+        <v>7.8485</v>
       </c>
       <c r="K64" s="13" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="L64" s="15" t="n">
-        <v>4.555555555555555</v>
+        <v>6</v>
       </c>
       <c r="M64" s="15" t="n">
-        <v>1.333333333333333</v>
+        <v>1</v>
       </c>
       <c r="N64" s="16">
         <f>IFERROR(M64/L64,"")</f>
@@ -4871,30 +4867,30 @@
       <c r="O64" s="12" t="inlineStr"/>
       <c r="P64" s="17" t="inlineStr">
         <is>
-          <t>https://cbva.com/venues/18</t>
+          <t>https://cbva.com/venues/8</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="11" t="n">
-        <v>46585</v>
+        <v>46621</v>
       </c>
       <c r="B65" s="12" t="inlineStr">
         <is>
-          <t>projected</t>
+          <t>estimated</t>
         </is>
       </c>
       <c r="C65" s="13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D65" s="12" t="inlineStr">
         <is>
-          <t>CBVA women’s open</t>
+          <t>Super Girl Pro Invitational</t>
         </is>
       </c>
       <c r="E65" s="12" t="inlineStr">
         <is>
-          <t>Main Beach, Santa Cruz</t>
+          <t>Oceanside Pier</t>
         </is>
       </c>
       <c r="F65" s="12" t="inlineStr">
@@ -4904,27 +4900,23 @@
       </c>
       <c r="G65" s="12" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>18U</t>
         </is>
       </c>
       <c r="H65" s="12" t="inlineStr">
         <is>
-          <t>Women's open</t>
+          <t>Junior circuit</t>
         </is>
       </c>
       <c r="I65" s="12" t="inlineStr"/>
       <c r="J65" s="14" t="n">
-        <v>7.8485</v>
+        <v>7.351</v>
       </c>
       <c r="K65" s="13" t="n">
-        <v>3</v>
-      </c>
-      <c r="L65" s="15" t="n">
-        <v>6</v>
-      </c>
-      <c r="M65" s="15" t="n">
-        <v>1</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="L65" s="15" t="n"/>
+      <c r="M65" s="15" t="n"/>
       <c r="N65" s="16">
         <f>IFERROR(M65/L65,"")</f>
         <v/>
@@ -4932,30 +4924,30 @@
       <c r="O65" s="12" t="inlineStr"/>
       <c r="P65" s="17" t="inlineStr">
         <is>
-          <t>https://cbva.com/venues/8</t>
+          <t>https://volleyballlife.com/tournament/40465</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="11" t="n">
-        <v>46621</v>
+        <v>46607</v>
       </c>
       <c r="B66" s="12" t="inlineStr">
         <is>
-          <t>estimated</t>
+          <t>projected</t>
         </is>
       </c>
       <c r="C66" s="13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D66" s="12" t="inlineStr">
         <is>
-          <t>Super Girl Pro Invitational</t>
+          <t>CBVA women’s open</t>
         </is>
       </c>
       <c r="E66" s="12" t="inlineStr">
         <is>
-          <t>Oceanside Pier</t>
+          <t>Ocean Park, Santa Monica</t>
         </is>
       </c>
       <c r="F66" s="12" t="inlineStr">
@@ -4965,23 +4957,27 @@
       </c>
       <c r="G66" s="12" t="inlineStr">
         <is>
-          <t>18U</t>
+          <t>Open</t>
         </is>
       </c>
       <c r="H66" s="12" t="inlineStr">
         <is>
-          <t>Junior circuit</t>
+          <t>Women's open</t>
         </is>
       </c>
       <c r="I66" s="12" t="inlineStr"/>
       <c r="J66" s="14" t="n">
-        <v>7.351</v>
+        <v>9.487</v>
       </c>
       <c r="K66" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="L66" s="15" t="n"/>
-      <c r="M66" s="15" t="n"/>
+        <v>16</v>
+      </c>
+      <c r="L66" s="15" t="n">
+        <v>3.586206896551724</v>
+      </c>
+      <c r="M66" s="15" t="n">
+        <v>1.96551724137931</v>
+      </c>
       <c r="N66" s="16">
         <f>IFERROR(M66/L66,"")</f>
         <v/>
@@ -4989,13 +4985,13 @@
       <c r="O66" s="12" t="inlineStr"/>
       <c r="P66" s="17" t="inlineStr">
         <is>
-          <t>https://volleyballlife.com/tournament/40465</t>
+          <t>https://cbva.com/venues/7</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="11" t="n">
-        <v>46607</v>
+        <v>46614</v>
       </c>
       <c r="B67" s="12" t="inlineStr">
         <is>
@@ -5012,7 +5008,7 @@
       </c>
       <c r="E67" s="12" t="inlineStr">
         <is>
-          <t>Ocean Park, Santa Monica</t>
+          <t>Hermosa Pier, Hermosa Beach</t>
         </is>
       </c>
       <c r="F67" s="12" t="inlineStr">
@@ -5032,16 +5028,16 @@
       </c>
       <c r="I67" s="12" t="inlineStr"/>
       <c r="J67" s="14" t="n">
-        <v>9.487</v>
+        <v>9.536</v>
       </c>
       <c r="K67" s="13" t="n">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="L67" s="15" t="n">
-        <v>3.586206896551724</v>
+        <v>4.025</v>
       </c>
       <c r="M67" s="15" t="n">
-        <v>1.96551724137931</v>
+        <v>1.925</v>
       </c>
       <c r="N67" s="16">
         <f>IFERROR(M67/L67,"")</f>
@@ -5050,13 +5046,13 @@
       <c r="O67" s="12" t="inlineStr"/>
       <c r="P67" s="17" t="inlineStr">
         <is>
-          <t>https://cbva.com/venues/7</t>
+          <t>https://cbva.com/venues/6</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="11" t="n">
-        <v>46614</v>
+        <v>46613</v>
       </c>
       <c r="B68" s="12" t="inlineStr">
         <is>
@@ -5073,7 +5069,7 @@
       </c>
       <c r="E68" s="12" t="inlineStr">
         <is>
-          <t>Hermosa Pier, Hermosa Beach</t>
+          <t>Main Beach, Santa Cruz</t>
         </is>
       </c>
       <c r="F68" s="12" t="inlineStr">
@@ -5093,16 +5089,16 @@
       </c>
       <c r="I68" s="12" t="inlineStr"/>
       <c r="J68" s="14" t="n">
-        <v>9.536</v>
+        <v>7.6825</v>
       </c>
       <c r="K68" s="13" t="n">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="L68" s="15" t="n">
-        <v>4.025</v>
+        <v>5.166666666666667</v>
       </c>
       <c r="M68" s="15" t="n">
-        <v>1.925</v>
+        <v>1.166666666666667</v>
       </c>
       <c r="N68" s="16">
         <f>IFERROR(M68/L68,"")</f>
@@ -5111,13 +5107,13 @@
       <c r="O68" s="12" t="inlineStr"/>
       <c r="P68" s="17" t="inlineStr">
         <is>
-          <t>https://cbva.com/venues/6</t>
+          <t>https://cbva.com/venues/8</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="11" t="n">
-        <v>46613</v>
+        <v>46620</v>
       </c>
       <c r="B69" s="12" t="inlineStr">
         <is>
@@ -5134,7 +5130,7 @@
       </c>
       <c r="E69" s="12" t="inlineStr">
         <is>
-          <t>Main Beach, Santa Cruz</t>
+          <t>Ocean Beach, San Diego</t>
         </is>
       </c>
       <c r="F69" s="12" t="inlineStr">
@@ -5154,16 +5150,16 @@
       </c>
       <c r="I69" s="12" t="inlineStr"/>
       <c r="J69" s="14" t="n">
-        <v>7.6825</v>
+        <v>8.145</v>
       </c>
       <c r="K69" s="13" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="L69" s="15" t="n">
-        <v>5.166666666666667</v>
+        <v>4</v>
       </c>
       <c r="M69" s="15" t="n">
-        <v>1.166666666666667</v>
+        <v>1.111111111111111</v>
       </c>
       <c r="N69" s="16">
         <f>IFERROR(M69/L69,"")</f>
@@ -5172,13 +5168,13 @@
       <c r="O69" s="12" t="inlineStr"/>
       <c r="P69" s="17" t="inlineStr">
         <is>
-          <t>https://cbva.com/venues/8</t>
+          <t>https://cbva.com/venues/13</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="11" t="n">
-        <v>46620</v>
+        <v>46642</v>
       </c>
       <c r="B70" s="12" t="inlineStr">
         <is>
@@ -5195,7 +5191,7 @@
       </c>
       <c r="E70" s="12" t="inlineStr">
         <is>
-          <t>Ocean Beach, San Diego</t>
+          <t>Ocean Park, Santa Monica</t>
         </is>
       </c>
       <c r="F70" s="12" t="inlineStr">
@@ -5215,16 +5211,16 @@
       </c>
       <c r="I70" s="12" t="inlineStr"/>
       <c r="J70" s="14" t="n">
-        <v>8.145</v>
+        <v>8.936</v>
       </c>
       <c r="K70" s="13" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L70" s="15" t="n">
-        <v>4</v>
+        <v>3.888888888888889</v>
       </c>
       <c r="M70" s="15" t="n">
-        <v>1.111111111111111</v>
+        <v>2.111111111111111</v>
       </c>
       <c r="N70" s="16">
         <f>IFERROR(M70/L70,"")</f>
@@ -5233,13 +5229,13 @@
       <c r="O70" s="12" t="inlineStr"/>
       <c r="P70" s="17" t="inlineStr">
         <is>
-          <t>https://cbva.com/venues/13</t>
+          <t>https://cbva.com/venues/7</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="11" t="n">
-        <v>46642</v>
+        <v>46635</v>
       </c>
       <c r="B71" s="12" t="inlineStr">
         <is>
@@ -5256,7 +5252,7 @@
       </c>
       <c r="E71" s="12" t="inlineStr">
         <is>
-          <t>Ocean Park, Santa Monica</t>
+          <t>Huntington Pier, Huntington Beach</t>
         </is>
       </c>
       <c r="F71" s="12" t="inlineStr">
@@ -5276,16 +5272,16 @@
       </c>
       <c r="I71" s="12" t="inlineStr"/>
       <c r="J71" s="14" t="n">
-        <v>8.936</v>
+        <v>9.334</v>
       </c>
       <c r="K71" s="13" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="L71" s="15" t="n">
-        <v>3.888888888888889</v>
+        <v>4.4</v>
       </c>
       <c r="M71" s="15" t="n">
-        <v>2.111111111111111</v>
+        <v>2.066666666666667</v>
       </c>
       <c r="N71" s="16">
         <f>IFERROR(M71/L71,"")</f>
@@ -5294,13 +5290,13 @@
       <c r="O71" s="12" t="inlineStr"/>
       <c r="P71" s="17" t="inlineStr">
         <is>
-          <t>https://cbva.com/venues/7</t>
+          <t>https://cbva.com/venues/22</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="11" t="n">
-        <v>46635</v>
+        <v>46641</v>
       </c>
       <c r="B72" s="12" t="inlineStr">
         <is>
@@ -5317,7 +5313,7 @@
       </c>
       <c r="E72" s="12" t="inlineStr">
         <is>
-          <t>Huntington Pier, Huntington Beach</t>
+          <t>Main Beach, Santa Cruz</t>
         </is>
       </c>
       <c r="F72" s="12" t="inlineStr">
@@ -5337,16 +5333,16 @@
       </c>
       <c r="I72" s="12" t="inlineStr"/>
       <c r="J72" s="14" t="n">
-        <v>9.334</v>
+        <v>7.668</v>
       </c>
       <c r="K72" s="13" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="L72" s="15" t="n">
-        <v>4.4</v>
+        <v>2.5</v>
       </c>
       <c r="M72" s="15" t="n">
-        <v>2.066666666666667</v>
+        <v>0</v>
       </c>
       <c r="N72" s="16">
         <f>IFERROR(M72/L72,"")</f>
@@ -5355,30 +5351,30 @@
       <c r="O72" s="12" t="inlineStr"/>
       <c r="P72" s="17" t="inlineStr">
         <is>
-          <t>https://cbva.com/venues/22</t>
+          <t>https://cbva.com/venues/8</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="11" t="n">
-        <v>46641</v>
+        <v>46661</v>
       </c>
       <c r="B73" s="12" t="inlineStr">
         <is>
-          <t>projected</t>
+          <t>estimated</t>
         </is>
       </c>
       <c r="C73" s="13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D73" s="12" t="inlineStr">
         <is>
-          <t>CBVA women’s open</t>
+          <t>The Santa Barbara Open (AVP Next)</t>
         </is>
       </c>
       <c r="E73" s="12" t="inlineStr">
         <is>
-          <t>Main Beach, Santa Cruz</t>
+          <t>East Beach, Santa Barbara</t>
         </is>
       </c>
       <c r="F73" s="12" t="inlineStr">
@@ -5393,21 +5389,21 @@
       </c>
       <c r="H73" s="12" t="inlineStr">
         <is>
-          <t>Women's open</t>
+          <t>Pro-am open</t>
         </is>
       </c>
       <c r="I73" s="12" t="inlineStr"/>
       <c r="J73" s="14" t="n">
-        <v>7.668</v>
+        <v>9.6455</v>
       </c>
       <c r="K73" s="13" t="n">
-        <v>1</v>
+        <v>27</v>
       </c>
       <c r="L73" s="15" t="n">
-        <v>2.5</v>
+        <v>11.33333333333333</v>
       </c>
       <c r="M73" s="15" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="N73" s="16">
         <f>IFERROR(M73/L73,"")</f>
@@ -5416,30 +5412,30 @@
       <c r="O73" s="12" t="inlineStr"/>
       <c r="P73" s="17" t="inlineStr">
         <is>
-          <t>https://cbva.com/venues/8</t>
+          <t>https://volleyballlife.com/tournament/28899</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="11" t="n">
-        <v>46661</v>
+        <v>46669</v>
       </c>
       <c r="B74" s="12" t="inlineStr">
         <is>
-          <t>estimated</t>
+          <t>projected</t>
         </is>
       </c>
       <c r="C74" s="13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D74" s="12" t="inlineStr">
         <is>
-          <t>The Santa Barbara Open (AVP Next)</t>
+          <t>CBVA women’s open</t>
         </is>
       </c>
       <c r="E74" s="12" t="inlineStr">
         <is>
-          <t>East Beach, Santa Barbara</t>
+          <t>Belmont Shore, Long Beach</t>
         </is>
       </c>
       <c r="F74" s="12" t="inlineStr">
@@ -5454,21 +5450,21 @@
       </c>
       <c r="H74" s="12" t="inlineStr">
         <is>
-          <t>Pro-am open</t>
+          <t>Women's open</t>
         </is>
       </c>
       <c r="I74" s="12" t="inlineStr"/>
       <c r="J74" s="14" t="n">
-        <v>9.6455</v>
+        <v>8.905000000000001</v>
       </c>
       <c r="K74" s="13" t="n">
-        <v>27</v>
+        <v>4</v>
       </c>
       <c r="L74" s="15" t="n">
-        <v>11.33333333333333</v>
+        <v>4.363636363636363</v>
       </c>
       <c r="M74" s="15" t="n">
-        <v>5</v>
+        <v>2.727272727272727</v>
       </c>
       <c r="N74" s="16">
         <f>IFERROR(M74/L74,"")</f>
@@ -5477,13 +5473,13 @@
       <c r="O74" s="12" t="inlineStr"/>
       <c r="P74" s="17" t="inlineStr">
         <is>
-          <t>https://volleyballlife.com/tournament/28899</t>
+          <t>https://cbva.com/venues/3</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="11" t="n">
-        <v>46669</v>
+        <v>46683</v>
       </c>
       <c r="B75" s="12" t="inlineStr">
         <is>
@@ -5500,7 +5496,7 @@
       </c>
       <c r="E75" s="12" t="inlineStr">
         <is>
-          <t>Belmont Shore, Long Beach</t>
+          <t>Main Beach, Santa Cruz</t>
         </is>
       </c>
       <c r="F75" s="12" t="inlineStr">
@@ -5520,16 +5516,16 @@
       </c>
       <c r="I75" s="12" t="inlineStr"/>
       <c r="J75" s="14" t="n">
-        <v>8.905000000000001</v>
+        <v>7.573</v>
       </c>
       <c r="K75" s="13" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="L75" s="15" t="n">
-        <v>4.363636363636363</v>
+        <v>4.666666666666667</v>
       </c>
       <c r="M75" s="15" t="n">
-        <v>2.727272727272727</v>
+        <v>0</v>
       </c>
       <c r="N75" s="16">
         <f>IFERROR(M75/L75,"")</f>
@@ -5538,30 +5534,30 @@
       <c r="O75" s="12" t="inlineStr"/>
       <c r="P75" s="17" t="inlineStr">
         <is>
-          <t>https://cbva.com/venues/3</t>
+          <t>https://cbva.com/venues/8</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="11" t="n">
-        <v>46683</v>
+        <v>46697</v>
       </c>
       <c r="B76" s="12" t="inlineStr">
         <is>
-          <t>projected</t>
+          <t>estimated</t>
         </is>
       </c>
       <c r="C76" s="13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D76" s="12" t="inlineStr">
         <is>
-          <t>CBVA women’s open</t>
+          <t>AVP Juniors West Coast Championships</t>
         </is>
       </c>
       <c r="E76" s="12" t="inlineStr">
         <is>
-          <t>Main Beach, Santa Cruz</t>
+          <t>Manhattan Beach</t>
         </is>
       </c>
       <c r="F76" s="12" t="inlineStr">
@@ -5571,26 +5567,26 @@
       </c>
       <c r="G76" s="12" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>18U</t>
         </is>
       </c>
       <c r="H76" s="12" t="inlineStr">
         <is>
-          <t>Women's open</t>
+          <t>National junior</t>
         </is>
       </c>
       <c r="I76" s="12" t="inlineStr"/>
       <c r="J76" s="14" t="n">
-        <v>7.573</v>
+        <v>9.5015</v>
       </c>
       <c r="K76" s="13" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="L76" s="15" t="n">
-        <v>4.666666666666667</v>
+        <v>14.66666666666667</v>
       </c>
       <c r="M76" s="15" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="N76" s="16">
         <f>IFERROR(M76/L76,"")</f>
@@ -5599,7 +5595,7 @@
       <c r="O76" s="12" t="inlineStr"/>
       <c r="P76" s="17" t="inlineStr">
         <is>
-          <t>https://cbva.com/venues/8</t>
+          <t>https://volleyballlife.com/tournament/25578</t>
         </is>
       </c>
     </row>
@@ -5632,7 +5628,7 @@
       </c>
       <c r="G77" s="12" t="inlineStr">
         <is>
-          <t>18U</t>
+          <t>17U</t>
         </is>
       </c>
       <c r="H77" s="12" t="inlineStr">
@@ -5640,18 +5636,22 @@
           <t>National junior</t>
         </is>
       </c>
-      <c r="I77" s="12" t="inlineStr"/>
+      <c r="I77" s="12" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
       <c r="J77" s="14" t="n">
-        <v>9.5015</v>
+        <v>7.714</v>
       </c>
       <c r="K77" s="13" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="L77" s="15" t="n">
-        <v>14.66666666666667</v>
+        <v>15</v>
       </c>
       <c r="M77" s="15" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="N77" s="16">
         <f>IFERROR(M77/L77,"")</f>
@@ -5670,20 +5670,20 @@
       </c>
       <c r="B78" s="12" t="inlineStr">
         <is>
-          <t>estimated</t>
+          <t>projected</t>
         </is>
       </c>
       <c r="C78" s="13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D78" s="12" t="inlineStr">
         <is>
-          <t>AVP Juniors West Coast Championships</t>
+          <t>CBVA women’s open</t>
         </is>
       </c>
       <c r="E78" s="12" t="inlineStr">
         <is>
-          <t>Manhattan Beach</t>
+          <t>Newland, Huntington Beach</t>
         </is>
       </c>
       <c r="F78" s="12" t="inlineStr">
@@ -5693,30 +5693,26 @@
       </c>
       <c r="G78" s="12" t="inlineStr">
         <is>
-          <t>17U</t>
+          <t>Open</t>
         </is>
       </c>
       <c r="H78" s="12" t="inlineStr">
         <is>
-          <t>National junior</t>
-        </is>
-      </c>
-      <c r="I78" s="12" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+          <t>Women's open</t>
+        </is>
+      </c>
+      <c r="I78" s="12" t="inlineStr"/>
       <c r="J78" s="14" t="n">
-        <v>7.714</v>
+        <v>8.769</v>
       </c>
       <c r="K78" s="13" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="L78" s="15" t="n">
-        <v>15</v>
+        <v>4.0625</v>
       </c>
       <c r="M78" s="15" t="n">
-        <v>5</v>
+        <v>1.8125</v>
       </c>
       <c r="N78" s="16">
         <f>IFERROR(M78/L78,"")</f>
@@ -5725,17 +5721,17 @@
       <c r="O78" s="12" t="inlineStr"/>
       <c r="P78" s="17" t="inlineStr">
         <is>
-          <t>https://volleyballlife.com/tournament/25578</t>
+          <t>https://cbva.com/venues/4</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="11" t="n">
-        <v>46697</v>
+        <v>46732</v>
       </c>
       <c r="B79" s="12" t="inlineStr">
         <is>
-          <t>projected</t>
+          <t>estimated</t>
         </is>
       </c>
       <c r="C79" s="13" t="n">
@@ -5743,42 +5739,38 @@
       </c>
       <c r="D79" s="12" t="inlineStr">
         <is>
-          <t>CBVA women’s open</t>
+          <t>AVP Winter Las Vegas</t>
         </is>
       </c>
       <c r="E79" s="12" t="inlineStr">
         <is>
-          <t>Newland, Huntington Beach</t>
+          <t>Sunset Park, Las Vegas</t>
         </is>
       </c>
       <c r="F79" s="12" t="inlineStr">
         <is>
-          <t>CA</t>
+          <t>NV</t>
         </is>
       </c>
       <c r="G79" s="12" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>18U</t>
         </is>
       </c>
       <c r="H79" s="12" t="inlineStr">
         <is>
-          <t>Women's open</t>
+          <t>Junior circuit</t>
         </is>
       </c>
       <c r="I79" s="12" t="inlineStr"/>
       <c r="J79" s="14" t="n">
-        <v>8.769</v>
+        <v>6.2515</v>
       </c>
       <c r="K79" s="13" t="n">
-        <v>6</v>
-      </c>
-      <c r="L79" s="15" t="n">
-        <v>4.0625</v>
-      </c>
-      <c r="M79" s="15" t="n">
-        <v>1.8125</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="L79" s="15" t="n"/>
+      <c r="M79" s="15" t="n"/>
       <c r="N79" s="16">
         <f>IFERROR(M79/L79,"")</f>
         <v/>
@@ -5786,80 +5778,23 @@
       <c r="O79" s="12" t="inlineStr"/>
       <c r="P79" s="17" t="inlineStr">
         <is>
-          <t>https://cbva.com/venues/4</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" s="11" t="n">
-        <v>46732</v>
-      </c>
-      <c r="B80" s="12" t="inlineStr">
-        <is>
-          <t>estimated</t>
-        </is>
-      </c>
-      <c r="C80" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="D80" s="12" t="inlineStr">
-        <is>
-          <t>AVP Winter Las Vegas</t>
-        </is>
-      </c>
-      <c r="E80" s="12" t="inlineStr">
-        <is>
-          <t>Sunset Park, Las Vegas</t>
-        </is>
-      </c>
-      <c r="F80" s="12" t="inlineStr">
-        <is>
-          <t>NV</t>
-        </is>
-      </c>
-      <c r="G80" s="12" t="inlineStr">
-        <is>
-          <t>18U</t>
-        </is>
-      </c>
-      <c r="H80" s="12" t="inlineStr">
-        <is>
-          <t>Junior circuit</t>
-        </is>
-      </c>
-      <c r="I80" s="12" t="inlineStr"/>
-      <c r="J80" s="14" t="n">
-        <v>6.2515</v>
-      </c>
-      <c r="K80" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="L80" s="15" t="n"/>
-      <c r="M80" s="15" t="n"/>
-      <c r="N80" s="16">
-        <f>IFERROR(M80/L80,"")</f>
-        <v/>
-      </c>
-      <c r="O80" s="12" t="inlineStr"/>
-      <c r="P80" s="17" t="inlineStr">
-        <is>
           <t>https://volleyballlife.com/tournament/41138</t>
         </is>
       </c>
     </row>
-    <row r="81"/>
-    <row r="82">
-      <c r="A82" s="9" t="inlineStr">
+    <row r="80"/>
+    <row r="81">
+      <c r="A81" s="9" t="inlineStr">
         <is>
           <t>Date: a posted date is the organiser's; an estimated date is last year's edition moved into 2027; a projected date is a CBVA slot placed by its own history (exact 45% of the time, within a week 91%) -- the page shows those as a month rather than a day, because the day is a projection. Days is how long her own draw runs, counted from the dates her division actually played at the most recent edition, not how long the event around it runs. Field median, above her, sets and contested all describe that most recent edition, not the 2027 one.</t>
         </is>
       </c>
     </row>
+    <row r="82"/>
     <row r="83"/>
-    <row r="84"/>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A82:H84"/>
+    <mergeCell ref="A81:H83"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">

--- a/docs/plan-2027.xlsx
+++ b/docs/plan-2027.xlsx
@@ -645,7 +645,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Built 20 October 2026 from the Volleyball Life crawl and CBVA’s tournament database.</t>
+          <t>Built 22 October 2026 from the Volleyball Life crawl and CBVA’s tournament database.</t>
         </is>
       </c>
     </row>
@@ -1130,10 +1130,10 @@
         <v>17</v>
       </c>
       <c r="L3" s="15" t="n">
-        <v>14.66666666666667</v>
+        <v>11.11111111111111</v>
       </c>
       <c r="M3" s="15" t="n">
-        <v>7</v>
+        <v>5.555555555555555</v>
       </c>
       <c r="N3" s="16">
         <f>IFERROR(M3/L3,"")</f>
@@ -1195,10 +1195,10 @@
         <v>0</v>
       </c>
       <c r="L4" s="15" t="n">
-        <v>15</v>
+        <v>9.666666666666666</v>
       </c>
       <c r="M4" s="15" t="n">
-        <v>5</v>
+        <v>3.333333333333333</v>
       </c>
       <c r="N4" s="16">
         <f>IFERROR(M4/L4,"")</f>
@@ -1840,7 +1840,7 @@
         <v>6</v>
       </c>
       <c r="L15" s="15" t="n">
-        <v>2.5</v>
+        <v>2.25</v>
       </c>
       <c r="M15" s="15" t="n">
         <v>1</v>
@@ -1962,10 +1962,10 @@
         <v>8</v>
       </c>
       <c r="L17" s="15" t="n">
-        <v>7.75</v>
+        <v>6.25</v>
       </c>
       <c r="M17" s="15" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N17" s="16">
         <f>IFERROR(M17/L17,"")</f>
@@ -2076,10 +2076,10 @@
         <v>8</v>
       </c>
       <c r="L19" s="15" t="n">
-        <v>7.75</v>
+        <v>6.25</v>
       </c>
       <c r="M19" s="15" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N19" s="16">
         <f>IFERROR(M19/L19,"")</f>
@@ -2141,10 +2141,10 @@
         <v>9</v>
       </c>
       <c r="L20" s="15" t="n">
-        <v>21</v>
+        <v>16.125</v>
       </c>
       <c r="M20" s="15" t="n">
-        <v>8.25</v>
+        <v>7</v>
       </c>
       <c r="N20" s="16">
         <f>IFERROR(M20/L20,"")</f>
@@ -2202,10 +2202,10 @@
         <v>4</v>
       </c>
       <c r="L21" s="15" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="M21" s="15" t="n">
-        <v>11</v>
+        <v>9.333333333333334</v>
       </c>
       <c r="N21" s="16">
         <f>IFERROR(M21/L21,"")</f>
@@ -2267,10 +2267,10 @@
         <v>4</v>
       </c>
       <c r="L22" s="15" t="n">
-        <v>12.5</v>
+        <v>8.666666666666666</v>
       </c>
       <c r="M22" s="15" t="n">
-        <v>9.5</v>
+        <v>6.666666666666667</v>
       </c>
       <c r="N22" s="16">
         <f>IFERROR(M22/L22,"")</f>
@@ -2393,10 +2393,10 @@
         <v>4</v>
       </c>
       <c r="L24" s="15" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="M24" s="15" t="n">
-        <v>11</v>
+        <v>9.333333333333334</v>
       </c>
       <c r="N24" s="16">
         <f>IFERROR(M24/L24,"")</f>
@@ -2511,10 +2511,10 @@
         <v>17</v>
       </c>
       <c r="L26" s="15" t="n">
-        <v>5.5</v>
+        <v>4.5</v>
       </c>
       <c r="M26" s="15" t="n">
-        <v>3.25</v>
+        <v>3</v>
       </c>
       <c r="N26" s="16">
         <f>IFERROR(M26/L26,"")</f>
@@ -2572,10 +2572,10 @@
         <v>1</v>
       </c>
       <c r="L27" s="15" t="n">
-        <v>8.333333333333334</v>
+        <v>6.333333333333333</v>
       </c>
       <c r="M27" s="15" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="N27" s="16">
         <f>IFERROR(M27/L27,"")</f>
@@ -2696,10 +2696,10 @@
         <v>6</v>
       </c>
       <c r="L29" s="15" t="n">
-        <v>9.266666666666667</v>
+        <v>7.133333333333334</v>
       </c>
       <c r="M29" s="15" t="n">
-        <v>5.933333333333334</v>
+        <v>4.533333333333333</v>
       </c>
       <c r="N29" s="16">
         <f>IFERROR(M29/L29,"")</f>
@@ -2826,7 +2826,7 @@
         <v>2</v>
       </c>
       <c r="L31" s="15" t="n">
-        <v>5.25</v>
+        <v>4.75</v>
       </c>
       <c r="M31" s="15" t="n">
         <v>0.75</v>
@@ -3676,10 +3676,10 @@
         <v>1</v>
       </c>
       <c r="L45" s="15" t="n">
-        <v>17.4</v>
+        <v>13.2</v>
       </c>
       <c r="M45" s="15" t="n">
-        <v>8.4</v>
+        <v>7.2</v>
       </c>
       <c r="N45" s="16">
         <f>IFERROR(M45/L45,"")</f>
@@ -3802,10 +3802,10 @@
         <v>6</v>
       </c>
       <c r="L47" s="15" t="n">
-        <v>15.42857142857143</v>
+        <v>11.85714285714286</v>
       </c>
       <c r="M47" s="15" t="n">
-        <v>8.142857142857142</v>
+        <v>6.714285714285714</v>
       </c>
       <c r="N47" s="16">
         <f>IFERROR(M47/L47,"")</f>
@@ -4237,10 +4237,10 @@
         <v>14</v>
       </c>
       <c r="L54" s="15" t="n">
-        <v>17.69230769230769</v>
+        <v>13.15384615384615</v>
       </c>
       <c r="M54" s="15" t="n">
-        <v>5.461538461538462</v>
+        <v>4.384615384615385</v>
       </c>
       <c r="N54" s="16">
         <f>IFERROR(M54/L54,"")</f>
@@ -4298,10 +4298,10 @@
         <v>7</v>
       </c>
       <c r="L55" s="15" t="n">
-        <v>19.4</v>
+        <v>15</v>
       </c>
       <c r="M55" s="15" t="n">
-        <v>7.4</v>
+        <v>6.2</v>
       </c>
       <c r="N55" s="16">
         <f>IFERROR(M55/L55,"")</f>
@@ -4363,10 +4363,10 @@
         <v>0</v>
       </c>
       <c r="L56" s="15" t="n">
-        <v>19.66666666666667</v>
+        <v>14.33333333333333</v>
       </c>
       <c r="M56" s="15" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N56" s="16">
         <f>IFERROR(M56/L56,"")</f>
@@ -4424,10 +4424,10 @@
         <v>18</v>
       </c>
       <c r="L57" s="15" t="n">
-        <v>24.27272727272727</v>
+        <v>18</v>
       </c>
       <c r="M57" s="15" t="n">
-        <v>13.09090909090909</v>
+        <v>10.45454545454546</v>
       </c>
       <c r="N57" s="16">
         <f>IFERROR(M57/L57,"")</f>
@@ -4489,10 +4489,10 @@
         <v>3</v>
       </c>
       <c r="L58" s="15" t="n">
-        <v>22.5</v>
+        <v>15</v>
       </c>
       <c r="M58" s="15" t="n">
-        <v>7.5</v>
+        <v>5.25</v>
       </c>
       <c r="N58" s="16">
         <f>IFERROR(M58/L58,"")</f>
@@ -4550,7 +4550,7 @@
         <v>1</v>
       </c>
       <c r="L59" s="15" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M59" s="15" t="n">
         <v>0</v>
@@ -4611,10 +4611,10 @@
         <v>20</v>
       </c>
       <c r="L60" s="15" t="n">
-        <v>5.52</v>
+        <v>5.04</v>
       </c>
       <c r="M60" s="15" t="n">
-        <v>3.16</v>
+        <v>2.96</v>
       </c>
       <c r="N60" s="16">
         <f>IFERROR(M60/L60,"")</f>
@@ -5400,10 +5400,10 @@
         <v>27</v>
       </c>
       <c r="L73" s="15" t="n">
-        <v>11.33333333333333</v>
+        <v>9</v>
       </c>
       <c r="M73" s="15" t="n">
-        <v>5</v>
+        <v>4.111111111111111</v>
       </c>
       <c r="N73" s="16">
         <f>IFERROR(M73/L73,"")</f>
@@ -5583,10 +5583,10 @@
         <v>17</v>
       </c>
       <c r="L76" s="15" t="n">
-        <v>14.66666666666667</v>
+        <v>11.11111111111111</v>
       </c>
       <c r="M76" s="15" t="n">
-        <v>7</v>
+        <v>5.555555555555555</v>
       </c>
       <c r="N76" s="16">
         <f>IFERROR(M76/L76,"")</f>
@@ -5648,10 +5648,10 @@
         <v>0</v>
       </c>
       <c r="L77" s="15" t="n">
-        <v>15</v>
+        <v>9.666666666666666</v>
       </c>
       <c r="M77" s="15" t="n">
-        <v>5</v>
+        <v>3.333333333333333</v>
       </c>
       <c r="N77" s="16">
         <f>IFERROR(M77/L77,"")</f>
@@ -5970,7 +5970,7 @@
       </c>
       <c r="I3" s="18" t="n"/>
       <c r="J3" s="18" t="n">
-        <v>11</v>
+        <v>9.333333333333334</v>
       </c>
       <c r="K3" s="18">
         <f>SUM(I3:J3)</f>
@@ -6016,10 +6016,10 @@
         <v>10</v>
       </c>
       <c r="I4" s="18" t="n">
-        <v>5.933333333333334</v>
+        <v>4.533333333333333</v>
       </c>
       <c r="J4" s="18" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="K4" s="18">
         <f>SUM(I4:J4)</f>
@@ -6365,10 +6365,10 @@
         <v>17</v>
       </c>
       <c r="I2" s="18" t="n">
-        <v>6.166666666666667</v>
+        <v>5.333333333333333</v>
       </c>
       <c r="J2" s="18" t="n">
-        <v>3.333333333333333</v>
+        <v>3</v>
       </c>
       <c r="K2" s="20">
         <f>IFERROR(J2/I2,"")</f>
@@ -6415,10 +6415,10 @@
         <v>18</v>
       </c>
       <c r="I3" s="18" t="n">
-        <v>10</v>
+        <v>8.75</v>
       </c>
       <c r="J3" s="18" t="n">
-        <v>3.75</v>
+        <v>3.25</v>
       </c>
       <c r="K3" s="20">
         <f>IFERROR(J3/I3,"")</f>
@@ -6465,10 +6465,10 @@
         <v>16</v>
       </c>
       <c r="I4" s="18" t="n">
-        <v>9.857142857142858</v>
+        <v>7</v>
       </c>
       <c r="J4" s="18" t="n">
-        <v>4.285714285714286</v>
+        <v>2.857142857142857</v>
       </c>
       <c r="K4" s="20">
         <f>IFERROR(J4/I4,"")</f>
@@ -6515,10 +6515,10 @@
         <v>27</v>
       </c>
       <c r="I5" s="18" t="n">
-        <v>11.33333333333333</v>
+        <v>9</v>
       </c>
       <c r="J5" s="18" t="n">
-        <v>5</v>
+        <v>4.111111111111111</v>
       </c>
       <c r="K5" s="20">
         <f>IFERROR(J5/I5,"")</f>
@@ -6565,10 +6565,10 @@
         <v>18</v>
       </c>
       <c r="I6" s="18" t="n">
-        <v>7.166666666666667</v>
+        <v>6.166666666666667</v>
       </c>
       <c r="J6" s="18" t="n">
-        <v>3.833333333333333</v>
+        <v>3.333333333333333</v>
       </c>
       <c r="K6" s="20">
         <f>IFERROR(J6/I6,"")</f>
@@ -6615,10 +6615,10 @@
         <v>13</v>
       </c>
       <c r="I7" s="18" t="n">
-        <v>12</v>
+        <v>10.2</v>
       </c>
       <c r="J7" s="18" t="n">
-        <v>6.6</v>
+        <v>5.8</v>
       </c>
       <c r="K7" s="20">
         <f>IFERROR(J7/I7,"")</f>
@@ -6665,10 +6665,10 @@
         <v>17</v>
       </c>
       <c r="I8" s="18" t="n">
-        <v>5.5</v>
+        <v>4.5</v>
       </c>
       <c r="J8" s="18" t="n">
-        <v>3.25</v>
+        <v>3</v>
       </c>
       <c r="K8" s="20">
         <f>IFERROR(J8/I8,"")</f>
@@ -6715,10 +6715,10 @@
         <v>10</v>
       </c>
       <c r="I9" s="18" t="n">
-        <v>11.4</v>
+        <v>8.6</v>
       </c>
       <c r="J9" s="18" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="K9" s="20">
         <f>IFERROR(J9/I9,"")</f>
@@ -6765,10 +6765,10 @@
         <v>7</v>
       </c>
       <c r="I10" s="18" t="n">
-        <v>10.33333333333333</v>
+        <v>7.333333333333333</v>
       </c>
       <c r="J10" s="18" t="n">
-        <v>5</v>
+        <v>3.666666666666667</v>
       </c>
       <c r="K10" s="20">
         <f>IFERROR(J10/I10,"")</f>
@@ -6861,10 +6861,10 @@
         <v>2</v>
       </c>
       <c r="I12" s="18" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="J12" s="18" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="K12" s="20">
         <f>IFERROR(J12/I12,"")</f>
@@ -6911,7 +6911,7 @@
         <v>14</v>
       </c>
       <c r="I13" s="18" t="n">
-        <v>5.5</v>
+        <v>4.75</v>
       </c>
       <c r="J13" s="18" t="n">
         <v>2.25</v>
@@ -6961,7 +6961,7 @@
         <v>5</v>
       </c>
       <c r="I14" s="18" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="J14" s="18" t="n">
         <v>5</v>
@@ -7011,7 +7011,7 @@
         <v>0</v>
       </c>
       <c r="I15" s="18" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="J15" s="18" t="n">
         <v>0</v>
@@ -7061,10 +7061,10 @@
         <v>16</v>
       </c>
       <c r="I16" s="18" t="n">
-        <v>8.800000000000001</v>
+        <v>7.2</v>
       </c>
       <c r="J16" s="18" t="n">
-        <v>6</v>
+        <v>5.2</v>
       </c>
       <c r="K16" s="20">
         <f>IFERROR(J16/I16,"")</f>

--- a/docs/plan-2027.xlsx
+++ b/docs/plan-2027.xlsx
@@ -255,8 +255,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="SeasonCalendar" displayName="SeasonCalendar" ref="A1:P79" headerRowCount="1">
-  <autoFilter ref="A1:P79"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="SeasonCalendar" displayName="SeasonCalendar" ref="A1:P80" headerRowCount="1">
+  <autoFilter ref="A1:P80"/>
   <tableColumns count="16">
     <tableColumn id="1" name="Date"/>
     <tableColumn id="2" name="Date is"/>
@@ -645,7 +645,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Built 22 October 2026 from the Volleyball Life crawl and CBVA’s tournament database.</t>
+          <t>Built 24 October 2026 from the Volleyball Life crawl and CBVA’s tournament database.</t>
         </is>
       </c>
     </row>
@@ -721,7 +721,7 @@
         </is>
       </c>
       <c r="B8" s="6" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
@@ -929,7 +929,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P83"/>
+  <dimension ref="A1:P84"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -3121,13 +3121,13 @@
       </c>
       <c r="I36" s="12" t="inlineStr"/>
       <c r="J36" s="14" t="n">
-        <v>7.68</v>
+        <v>7.721</v>
       </c>
       <c r="K36" s="13" t="n">
         <v>1</v>
       </c>
       <c r="L36" s="15" t="n">
-        <v>3.666666666666667</v>
+        <v>4</v>
       </c>
       <c r="M36" s="15" t="n">
         <v>0.6666666666666666</v>
@@ -3495,13 +3495,13 @@
       </c>
       <c r="I42" s="12" t="inlineStr"/>
       <c r="J42" s="14" t="n">
-        <v>7.668</v>
+        <v>7.673</v>
       </c>
       <c r="K42" s="13" t="n">
         <v>1</v>
       </c>
       <c r="L42" s="15" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M42" s="15" t="n">
         <v>0</v>
@@ -3863,7 +3863,7 @@
         <v>6</v>
       </c>
       <c r="L48" s="15" t="n">
-        <v>4.428571428571429</v>
+        <v>4.571428571428571</v>
       </c>
       <c r="M48" s="15" t="n">
         <v>2.714285714285714</v>
@@ -3983,7 +3983,7 @@
       </c>
       <c r="I50" s="12" t="inlineStr"/>
       <c r="J50" s="14" t="n">
-        <v>9.332000000000001</v>
+        <v>9.334</v>
       </c>
       <c r="K50" s="13" t="n">
         <v>22</v>
@@ -4105,13 +4105,13 @@
       </c>
       <c r="I52" s="12" t="inlineStr"/>
       <c r="J52" s="14" t="n">
-        <v>8.798999999999999</v>
+        <v>8.805</v>
       </c>
       <c r="K52" s="13" t="n">
         <v>7</v>
       </c>
       <c r="L52" s="15" t="n">
-        <v>4.375</v>
+        <v>4.25</v>
       </c>
       <c r="M52" s="15" t="n">
         <v>1.75</v>
@@ -4170,13 +4170,13 @@
       </c>
       <c r="I53" s="12" t="inlineStr"/>
       <c r="J53" s="14" t="n">
-        <v>7.668</v>
+        <v>7.686</v>
       </c>
       <c r="K53" s="13" t="n">
         <v>3</v>
       </c>
       <c r="L53" s="15" t="n">
-        <v>5.833333333333333</v>
+        <v>6</v>
       </c>
       <c r="M53" s="15" t="n">
         <v>0.8333333333333334</v>
@@ -4666,7 +4666,7 @@
       </c>
       <c r="I61" s="12" t="inlineStr"/>
       <c r="J61" s="14" t="n">
-        <v>8.887</v>
+        <v>8.884</v>
       </c>
       <c r="K61" s="13" t="n">
         <v>15</v>
@@ -4727,13 +4727,13 @@
       </c>
       <c r="I62" s="12" t="inlineStr"/>
       <c r="J62" s="14" t="n">
-        <v>9.269</v>
+        <v>9.292</v>
       </c>
       <c r="K62" s="13" t="n">
         <v>11</v>
       </c>
       <c r="L62" s="15" t="n">
-        <v>4</v>
+        <v>3.958333333333333</v>
       </c>
       <c r="M62" s="15" t="n">
         <v>1.958333333333333</v>
@@ -4849,7 +4849,7 @@
       </c>
       <c r="I64" s="12" t="inlineStr"/>
       <c r="J64" s="14" t="n">
-        <v>7.8485</v>
+        <v>7.875</v>
       </c>
       <c r="K64" s="13" t="n">
         <v>3</v>
@@ -4973,7 +4973,7 @@
         <v>16</v>
       </c>
       <c r="L66" s="15" t="n">
-        <v>3.586206896551724</v>
+        <v>3.551724137931035</v>
       </c>
       <c r="M66" s="15" t="n">
         <v>1.96551724137931</v>
@@ -5028,13 +5028,13 @@
       </c>
       <c r="I67" s="12" t="inlineStr"/>
       <c r="J67" s="14" t="n">
-        <v>9.536</v>
+        <v>9.5335</v>
       </c>
       <c r="K67" s="13" t="n">
         <v>25</v>
       </c>
       <c r="L67" s="15" t="n">
-        <v>4.025</v>
+        <v>4.05</v>
       </c>
       <c r="M67" s="15" t="n">
         <v>1.925</v>
@@ -5089,13 +5089,13 @@
       </c>
       <c r="I68" s="12" t="inlineStr"/>
       <c r="J68" s="14" t="n">
-        <v>7.6825</v>
+        <v>7.7065</v>
       </c>
       <c r="K68" s="13" t="n">
         <v>2</v>
       </c>
       <c r="L68" s="15" t="n">
-        <v>5.166666666666667</v>
+        <v>5.333333333333333</v>
       </c>
       <c r="M68" s="15" t="n">
         <v>1.166666666666667</v>
@@ -5150,7 +5150,7 @@
       </c>
       <c r="I69" s="12" t="inlineStr"/>
       <c r="J69" s="14" t="n">
-        <v>8.145</v>
+        <v>8.151499999999999</v>
       </c>
       <c r="K69" s="13" t="n">
         <v>5</v>
@@ -5174,7 +5174,7 @@
     </row>
     <row r="70">
       <c r="A70" s="11" t="n">
-        <v>46642</v>
+        <v>46655</v>
       </c>
       <c r="B70" s="12" t="inlineStr">
         <is>
@@ -5191,7 +5191,7 @@
       </c>
       <c r="E70" s="12" t="inlineStr">
         <is>
-          <t>Ocean Park, Santa Monica</t>
+          <t>Dockweiler, Los Angeles</t>
         </is>
       </c>
       <c r="F70" s="12" t="inlineStr">
@@ -5211,16 +5211,16 @@
       </c>
       <c r="I70" s="12" t="inlineStr"/>
       <c r="J70" s="14" t="n">
-        <v>8.936</v>
+        <v>8.769500000000001</v>
       </c>
       <c r="K70" s="13" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="L70" s="15" t="n">
-        <v>3.888888888888889</v>
+        <v>8.333333333333334</v>
       </c>
       <c r="M70" s="15" t="n">
-        <v>2.111111111111111</v>
+        <v>3.666666666666667</v>
       </c>
       <c r="N70" s="16">
         <f>IFERROR(M70/L70,"")</f>
@@ -5229,13 +5229,13 @@
       <c r="O70" s="12" t="inlineStr"/>
       <c r="P70" s="17" t="inlineStr">
         <is>
-          <t>https://cbva.com/venues/7</t>
+          <t>https://cbva.com/venues/1</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="11" t="n">
-        <v>46635</v>
+        <v>46642</v>
       </c>
       <c r="B71" s="12" t="inlineStr">
         <is>
@@ -5252,7 +5252,7 @@
       </c>
       <c r="E71" s="12" t="inlineStr">
         <is>
-          <t>Huntington Pier, Huntington Beach</t>
+          <t>Ocean Park, Santa Monica</t>
         </is>
       </c>
       <c r="F71" s="12" t="inlineStr">
@@ -5272,16 +5272,16 @@
       </c>
       <c r="I71" s="12" t="inlineStr"/>
       <c r="J71" s="14" t="n">
-        <v>9.334</v>
+        <v>8.936</v>
       </c>
       <c r="K71" s="13" t="n">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="L71" s="15" t="n">
-        <v>4.4</v>
+        <v>3.888888888888889</v>
       </c>
       <c r="M71" s="15" t="n">
-        <v>2.066666666666667</v>
+        <v>2.111111111111111</v>
       </c>
       <c r="N71" s="16">
         <f>IFERROR(M71/L71,"")</f>
@@ -5290,13 +5290,13 @@
       <c r="O71" s="12" t="inlineStr"/>
       <c r="P71" s="17" t="inlineStr">
         <is>
-          <t>https://cbva.com/venues/22</t>
+          <t>https://cbva.com/venues/7</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="11" t="n">
-        <v>46641</v>
+        <v>46635</v>
       </c>
       <c r="B72" s="12" t="inlineStr">
         <is>
@@ -5313,7 +5313,7 @@
       </c>
       <c r="E72" s="12" t="inlineStr">
         <is>
-          <t>Main Beach, Santa Cruz</t>
+          <t>Huntington Pier, Huntington Beach</t>
         </is>
       </c>
       <c r="F72" s="12" t="inlineStr">
@@ -5333,16 +5333,16 @@
       </c>
       <c r="I72" s="12" t="inlineStr"/>
       <c r="J72" s="14" t="n">
-        <v>7.668</v>
+        <v>9.334</v>
       </c>
       <c r="K72" s="13" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="L72" s="15" t="n">
-        <v>2.5</v>
+        <v>4.4</v>
       </c>
       <c r="M72" s="15" t="n">
-        <v>0</v>
+        <v>2.066666666666667</v>
       </c>
       <c r="N72" s="16">
         <f>IFERROR(M72/L72,"")</f>
@@ -5351,30 +5351,30 @@
       <c r="O72" s="12" t="inlineStr"/>
       <c r="P72" s="17" t="inlineStr">
         <is>
-          <t>https://cbva.com/venues/8</t>
+          <t>https://cbva.com/venues/22</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="11" t="n">
-        <v>46661</v>
+        <v>46641</v>
       </c>
       <c r="B73" s="12" t="inlineStr">
         <is>
-          <t>estimated</t>
+          <t>projected</t>
         </is>
       </c>
       <c r="C73" s="13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D73" s="12" t="inlineStr">
         <is>
-          <t>The Santa Barbara Open (AVP Next)</t>
+          <t>CBVA women’s open</t>
         </is>
       </c>
       <c r="E73" s="12" t="inlineStr">
         <is>
-          <t>East Beach, Santa Barbara</t>
+          <t>Main Beach, Santa Cruz</t>
         </is>
       </c>
       <c r="F73" s="12" t="inlineStr">
@@ -5389,21 +5389,21 @@
       </c>
       <c r="H73" s="12" t="inlineStr">
         <is>
-          <t>Pro-am open</t>
+          <t>Women's open</t>
         </is>
       </c>
       <c r="I73" s="12" t="inlineStr"/>
       <c r="J73" s="14" t="n">
-        <v>9.6455</v>
+        <v>7.668</v>
       </c>
       <c r="K73" s="13" t="n">
-        <v>27</v>
+        <v>1</v>
       </c>
       <c r="L73" s="15" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="M73" s="15" t="n">
-        <v>4.111111111111111</v>
+        <v>0</v>
       </c>
       <c r="N73" s="16">
         <f>IFERROR(M73/L73,"")</f>
@@ -5412,30 +5412,30 @@
       <c r="O73" s="12" t="inlineStr"/>
       <c r="P73" s="17" t="inlineStr">
         <is>
-          <t>https://volleyballlife.com/tournament/28899</t>
+          <t>https://cbva.com/venues/8</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="11" t="n">
-        <v>46669</v>
+        <v>46661</v>
       </c>
       <c r="B74" s="12" t="inlineStr">
         <is>
-          <t>projected</t>
+          <t>estimated</t>
         </is>
       </c>
       <c r="C74" s="13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D74" s="12" t="inlineStr">
         <is>
-          <t>CBVA women’s open</t>
+          <t>The Santa Barbara Open (AVP Next)</t>
         </is>
       </c>
       <c r="E74" s="12" t="inlineStr">
         <is>
-          <t>Belmont Shore, Long Beach</t>
+          <t>East Beach, Santa Barbara</t>
         </is>
       </c>
       <c r="F74" s="12" t="inlineStr">
@@ -5450,21 +5450,21 @@
       </c>
       <c r="H74" s="12" t="inlineStr">
         <is>
-          <t>Women's open</t>
+          <t>Pro-am open</t>
         </is>
       </c>
       <c r="I74" s="12" t="inlineStr"/>
       <c r="J74" s="14" t="n">
-        <v>8.905000000000001</v>
+        <v>9.6455</v>
       </c>
       <c r="K74" s="13" t="n">
-        <v>4</v>
+        <v>27</v>
       </c>
       <c r="L74" s="15" t="n">
-        <v>4.363636363636363</v>
+        <v>9</v>
       </c>
       <c r="M74" s="15" t="n">
-        <v>2.727272727272727</v>
+        <v>4.111111111111111</v>
       </c>
       <c r="N74" s="16">
         <f>IFERROR(M74/L74,"")</f>
@@ -5473,13 +5473,13 @@
       <c r="O74" s="12" t="inlineStr"/>
       <c r="P74" s="17" t="inlineStr">
         <is>
-          <t>https://cbva.com/venues/3</t>
+          <t>https://volleyballlife.com/tournament/28899</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="11" t="n">
-        <v>46683</v>
+        <v>46669</v>
       </c>
       <c r="B75" s="12" t="inlineStr">
         <is>
@@ -5496,7 +5496,7 @@
       </c>
       <c r="E75" s="12" t="inlineStr">
         <is>
-          <t>Main Beach, Santa Cruz</t>
+          <t>Belmont Shore, Long Beach</t>
         </is>
       </c>
       <c r="F75" s="12" t="inlineStr">
@@ -5516,16 +5516,16 @@
       </c>
       <c r="I75" s="12" t="inlineStr"/>
       <c r="J75" s="14" t="n">
-        <v>7.573</v>
+        <v>8.976000000000001</v>
       </c>
       <c r="K75" s="13" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L75" s="15" t="n">
-        <v>4.666666666666667</v>
+        <v>4.928571428571429</v>
       </c>
       <c r="M75" s="15" t="n">
-        <v>0</v>
+        <v>3.071428571428572</v>
       </c>
       <c r="N75" s="16">
         <f>IFERROR(M75/L75,"")</f>
@@ -5534,30 +5534,30 @@
       <c r="O75" s="12" t="inlineStr"/>
       <c r="P75" s="17" t="inlineStr">
         <is>
-          <t>https://cbva.com/venues/8</t>
+          <t>https://cbva.com/venues/3</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="11" t="n">
-        <v>46697</v>
+        <v>46683</v>
       </c>
       <c r="B76" s="12" t="inlineStr">
         <is>
-          <t>estimated</t>
+          <t>projected</t>
         </is>
       </c>
       <c r="C76" s="13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D76" s="12" t="inlineStr">
         <is>
-          <t>AVP Juniors West Coast Championships</t>
+          <t>CBVA women’s open</t>
         </is>
       </c>
       <c r="E76" s="12" t="inlineStr">
         <is>
-          <t>Manhattan Beach</t>
+          <t>Main Beach, Santa Cruz</t>
         </is>
       </c>
       <c r="F76" s="12" t="inlineStr">
@@ -5567,26 +5567,26 @@
       </c>
       <c r="G76" s="12" t="inlineStr">
         <is>
-          <t>18U</t>
+          <t>Open</t>
         </is>
       </c>
       <c r="H76" s="12" t="inlineStr">
         <is>
-          <t>National junior</t>
+          <t>Women's open</t>
         </is>
       </c>
       <c r="I76" s="12" t="inlineStr"/>
       <c r="J76" s="14" t="n">
-        <v>9.5015</v>
+        <v>7.65</v>
       </c>
       <c r="K76" s="13" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="L76" s="15" t="n">
-        <v>11.11111111111111</v>
+        <v>4.666666666666667</v>
       </c>
       <c r="M76" s="15" t="n">
-        <v>5.555555555555555</v>
+        <v>0</v>
       </c>
       <c r="N76" s="16">
         <f>IFERROR(M76/L76,"")</f>
@@ -5595,7 +5595,7 @@
       <c r="O76" s="12" t="inlineStr"/>
       <c r="P76" s="17" t="inlineStr">
         <is>
-          <t>https://volleyballlife.com/tournament/25578</t>
+          <t>https://cbva.com/venues/8</t>
         </is>
       </c>
     </row>
@@ -5628,7 +5628,7 @@
       </c>
       <c r="G77" s="12" t="inlineStr">
         <is>
-          <t>17U</t>
+          <t>18U</t>
         </is>
       </c>
       <c r="H77" s="12" t="inlineStr">
@@ -5636,22 +5636,18 @@
           <t>National junior</t>
         </is>
       </c>
-      <c r="I77" s="12" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="I77" s="12" t="inlineStr"/>
       <c r="J77" s="14" t="n">
-        <v>7.714</v>
+        <v>9.5015</v>
       </c>
       <c r="K77" s="13" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="L77" s="15" t="n">
-        <v>9.666666666666666</v>
+        <v>11.11111111111111</v>
       </c>
       <c r="M77" s="15" t="n">
-        <v>3.333333333333333</v>
+        <v>5.555555555555555</v>
       </c>
       <c r="N77" s="16">
         <f>IFERROR(M77/L77,"")</f>
@@ -5670,20 +5666,20 @@
       </c>
       <c r="B78" s="12" t="inlineStr">
         <is>
-          <t>projected</t>
+          <t>estimated</t>
         </is>
       </c>
       <c r="C78" s="13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D78" s="12" t="inlineStr">
         <is>
-          <t>CBVA women’s open</t>
+          <t>AVP Juniors West Coast Championships</t>
         </is>
       </c>
       <c r="E78" s="12" t="inlineStr">
         <is>
-          <t>Newland, Huntington Beach</t>
+          <t>Manhattan Beach</t>
         </is>
       </c>
       <c r="F78" s="12" t="inlineStr">
@@ -5693,26 +5689,30 @@
       </c>
       <c r="G78" s="12" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>17U</t>
         </is>
       </c>
       <c r="H78" s="12" t="inlineStr">
         <is>
-          <t>Women's open</t>
-        </is>
-      </c>
-      <c r="I78" s="12" t="inlineStr"/>
+          <t>National junior</t>
+        </is>
+      </c>
+      <c r="I78" s="12" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
       <c r="J78" s="14" t="n">
-        <v>8.769</v>
+        <v>7.714</v>
       </c>
       <c r="K78" s="13" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="L78" s="15" t="n">
-        <v>4.0625</v>
+        <v>9.666666666666666</v>
       </c>
       <c r="M78" s="15" t="n">
-        <v>1.8125</v>
+        <v>3.333333333333333</v>
       </c>
       <c r="N78" s="16">
         <f>IFERROR(M78/L78,"")</f>
@@ -5721,17 +5721,17 @@
       <c r="O78" s="12" t="inlineStr"/>
       <c r="P78" s="17" t="inlineStr">
         <is>
-          <t>https://cbva.com/venues/4</t>
+          <t>https://volleyballlife.com/tournament/25578</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="11" t="n">
-        <v>46732</v>
+        <v>46697</v>
       </c>
       <c r="B79" s="12" t="inlineStr">
         <is>
-          <t>estimated</t>
+          <t>projected</t>
         </is>
       </c>
       <c r="C79" s="13" t="n">
@@ -5739,38 +5739,42 @@
       </c>
       <c r="D79" s="12" t="inlineStr">
         <is>
-          <t>AVP Winter Las Vegas</t>
+          <t>CBVA women’s open</t>
         </is>
       </c>
       <c r="E79" s="12" t="inlineStr">
         <is>
-          <t>Sunset Park, Las Vegas</t>
+          <t>Newland, Huntington Beach</t>
         </is>
       </c>
       <c r="F79" s="12" t="inlineStr">
         <is>
-          <t>NV</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="G79" s="12" t="inlineStr">
         <is>
-          <t>18U</t>
+          <t>Open</t>
         </is>
       </c>
       <c r="H79" s="12" t="inlineStr">
         <is>
-          <t>Junior circuit</t>
+          <t>Women's open</t>
         </is>
       </c>
       <c r="I79" s="12" t="inlineStr"/>
       <c r="J79" s="14" t="n">
-        <v>6.2515</v>
+        <v>8.769</v>
       </c>
       <c r="K79" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="L79" s="15" t="n"/>
-      <c r="M79" s="15" t="n"/>
+        <v>6</v>
+      </c>
+      <c r="L79" s="15" t="n">
+        <v>4.0625</v>
+      </c>
+      <c r="M79" s="15" t="n">
+        <v>1.8125</v>
+      </c>
       <c r="N79" s="16">
         <f>IFERROR(M79/L79,"")</f>
         <v/>
@@ -5778,23 +5782,80 @@
       <c r="O79" s="12" t="inlineStr"/>
       <c r="P79" s="17" t="inlineStr">
         <is>
+          <t>https://cbva.com/venues/4</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="11" t="n">
+        <v>46732</v>
+      </c>
+      <c r="B80" s="12" t="inlineStr">
+        <is>
+          <t>estimated</t>
+        </is>
+      </c>
+      <c r="C80" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="D80" s="12" t="inlineStr">
+        <is>
+          <t>AVP Winter Las Vegas</t>
+        </is>
+      </c>
+      <c r="E80" s="12" t="inlineStr">
+        <is>
+          <t>Sunset Park, Las Vegas</t>
+        </is>
+      </c>
+      <c r="F80" s="12" t="inlineStr">
+        <is>
+          <t>NV</t>
+        </is>
+      </c>
+      <c r="G80" s="12" t="inlineStr">
+        <is>
+          <t>18U</t>
+        </is>
+      </c>
+      <c r="H80" s="12" t="inlineStr">
+        <is>
+          <t>Junior circuit</t>
+        </is>
+      </c>
+      <c r="I80" s="12" t="inlineStr"/>
+      <c r="J80" s="14" t="n">
+        <v>6.2515</v>
+      </c>
+      <c r="K80" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="L80" s="15" t="n"/>
+      <c r="M80" s="15" t="n"/>
+      <c r="N80" s="16">
+        <f>IFERROR(M80/L80,"")</f>
+        <v/>
+      </c>
+      <c r="O80" s="12" t="inlineStr"/>
+      <c r="P80" s="17" t="inlineStr">
+        <is>
           <t>https://volleyballlife.com/tournament/41138</t>
         </is>
       </c>
     </row>
-    <row r="80"/>
-    <row r="81">
-      <c r="A81" s="9" t="inlineStr">
+    <row r="81"/>
+    <row r="82">
+      <c r="A82" s="9" t="inlineStr">
         <is>
           <t>Date: a posted date is the organiser's; an estimated date is last year's edition moved into 2027; a projected date is a CBVA slot placed by its own history (exact 45% of the time, within a week 91%) -- the page shows those as a month rather than a day, because the day is a projection. Days is how long her own draw runs, counted from the dates her division actually played at the most recent edition, not how long the event around it runs. Field median, above her, sets and contested all describe that most recent edition, not the 2027 one.</t>
         </is>
       </c>
     </row>
-    <row r="82"/>
     <row r="83"/>
+    <row r="84"/>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A81:H83"/>
+    <mergeCell ref="A82:H84"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">
